--- a/data/data_analysis/procurement.xlsx
+++ b/data/data_analysis/procurement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{420429BB-30CA-4F50-9BFC-D75327A0F4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10C2556-FB06-4929-9D11-22CBAB2A4225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
   </bookViews>
@@ -36,43 +36,56 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="12">
   <si>
     <t>Scenario</t>
-  </si>
-  <si>
-    <t>Subsidy</t>
   </si>
   <si>
     <t>Year</t>
   </si>
   <si>
-    <t>Procurement</t>
+    <t>Baseline</t>
   </si>
   <si>
-    <t>Price</t>
+    <t>Procurement Error</t>
   </si>
   <si>
-    <t>Yes</t>
+    <t>Govt Percentage of CDR Market</t>
   </si>
   <si>
-    <t>s1l_low</t>
+    <t>Total Size of CDR market</t>
   </si>
   <si>
-    <t>No</t>
+    <t>Low</t>
   </si>
   <si>
-    <t>s1n_nothing</t>
+    <t>EFI $3.3B</t>
   </si>
   <si>
-    <t>s1h_high</t>
+    <t>Rhodium $100B</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Original Size</t>
+  </si>
+  <si>
+    <t>Nothing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,14 +111,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -134,67 +152,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>$3.3 </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t>B/yr Procurement Estimates from GCAM With and Without Subsidy Costs</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
@@ -205,11 +163,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$D$22</c:f>
+              <c:f>Sheet1!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Yes</c:v>
+                  <c:v>Procurement Error</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -236,101 +194,139 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$E$21:$V$21</c:f>
+              <c:f>Sheet1!$F$2:$F$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>9.18</c:v>
+                  <c:v>22.652770490000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.3</c:v>
+                  <c:v>38.92435596</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.47</c:v>
+                  <c:v>72.101540779999993</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.18</c:v>
+                  <c:v>13.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.3</c:v>
+                  <c:v>95.2150848</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>15.47</c:v>
+                  <c:v>214.75016840000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.17</c:v>
+                  <c:v>360.96804700000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10.32</c:v>
+                  <c:v>623.27188550000005</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>13.16</c:v>
+                  <c:v>974.18677479999997</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9.17</c:v>
+                  <c:v>22.652770490000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>10.32</c:v>
+                  <c:v>45.75593121</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>13.16</c:v>
+                  <c:v>103.695629</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.18</c:v>
+                  <c:v>13.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>11.29</c:v>
+                  <c:v>102.04666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15.34</c:v>
+                  <c:v>246.34425669999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.18</c:v>
+                  <c:v>470.9906421</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>11.29</c:v>
+                  <c:v>965.18417420000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>15.34</c:v>
+                  <c:v>1974.1867749999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$22:$V$22</c:f>
+              <c:f>Sheet1!$G$2:$G$28</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>4796</c:v>
+                  <c:v>5.9999999999999995E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8828</c:v>
+                  <c:v>8.9999999999999993E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24198</c:v>
+                  <c:v>-2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.7999999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.7300000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4792</c:v>
+                  <c:v>4.19E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6056</c:v>
+                  <c:v>2.4799999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>15336</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4796</c:v>
+                  <c:v>-2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.9999999999999995E-4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0%">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9629</c:v>
+                  <c:v>8.3499999999999998E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>33064</c:v>
+                  <c:v>4.3700000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.11899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.16400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -338,149 +334,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4CE5-45A6-A5FB-B75FF1E1A719}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$23</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>No</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="38100" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$E$21:$V$21</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>9.18</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>11.3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>15.47</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>9.18</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>11.3</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>15.47</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>9.17</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>10.32</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>13.16</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9.17</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10.32</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>13.16</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9.18</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>11.29</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15.34</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>9.18</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>11.29</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>15.34</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$E$23:$V$23</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="3">
-                  <c:v>3259</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>154</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2441</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2435</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-343</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-490</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>3259</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>-358</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1867</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4CE5-45A6-A5FB-B75FF1E1A719}"/>
+              <c16:uniqueId val="{00000000-D3F1-45E8-BE09-8DA55D2C16C6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -492,14 +346,13 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="710424528"/>
-        <c:axId val="710426448"/>
+        <c:axId val="1135939536"/>
+        <c:axId val="1135940016"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="710424528"/>
+        <c:axId val="1135939536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="8"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -538,7 +391,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Mt CO2 Procured</a:t>
+                  <a:t>Size of the CDR Market (including procurement)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -609,12 +462,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="710426448"/>
+        <c:crossAx val="1135940016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="710426448"/>
+        <c:axId val="1135940016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -655,11 +508,11 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Cost</a:t>
+                  <a:t>Percentage Error in Price of Procurement</a:t>
                 </a:r>
                 <a:r>
                   <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> (Million USD)</a:t>
+                  <a:t> </a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
@@ -675,6 +528,411 @@
           </c:spPr>
           <c:txPr>
             <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1135939536"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Procurement Error</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$2:$H$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27.80103828</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>57.251683640000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>27.80103828</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>57.251683640000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>117.9004628</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>242.7966874</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>34.63261353</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>88.845771859999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>34.63261353</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>88.845771859999999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>227.9230579</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>584.70897609999997</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20.149627169999999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>30.074627790000001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>20.149627169999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>30.074627790000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>44.888336090000003</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>66.998758269999996</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$2:$G$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>5.9999999999999995E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.7999999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.7300000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.19E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.4799999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.9999999999999995E-4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.3499999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.3700000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.11899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.16400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.108</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D581-40F9-AC51-A489DFC6E37D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1135961136"/>
+        <c:axId val="1135944816"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1135961136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Size of the Voluntary</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> CDR market</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -731,7 +989,129 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="710424528"/>
+        <c:crossAx val="1135944816"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1135944816"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Percentage Error in  Price</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> of Procurement</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1135961136"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -743,9 +1123,525 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Govt Percentage of CDR Market</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$28</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>0.40404640545139786</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2857675459404056</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.20595755623739934</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.7080185525392716</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.73340331201342146</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.67337701001551531</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.61044819596631716</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.48675139825969232</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.40404640545139786</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.24310111030084311</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.14320620148801064</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.66061982302997468</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.63934303543273963</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.51607731125237999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.39419958208013484</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.24019347156248674</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$2:$G$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>5.9999999999999995E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.7999999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.7300000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.19E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.4799999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.9999999999999995E-4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.3499999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.3700000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.11899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.16400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.108</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9826-4C4B-9A48-52F977E43A8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1135961136"/>
+        <c:axId val="1135944816"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1135961136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Govt Procurement as Percentage of Total</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> CDR Market</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1135944816"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1135944816"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Percentage Error in  Price</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> of Procurement</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1135961136"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -753,37 +1649,10 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
+    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -858,6 +1727,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1374,27 +2323,1059 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>133348</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>52386</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F99FF6E-274E-D9FC-C76B-255C05BA573B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F4667FD-EA57-6D7F-89EF-EB72C3158B43}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1407,6 +3388,80 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2666747-893C-8DED-79A2-778C000AB62E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0E0FD68-43CA-4CB2-A0F8-CB9CD47E1B21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1732,461 +3787,628 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B537AA0D-F5C4-4357-8465-DF25FED59988}">
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
       </c>
       <c r="C2">
         <v>2025</v>
       </c>
-      <c r="D2">
-        <v>9.18</v>
-      </c>
-      <c r="E2">
-        <v>4796</v>
+      <c r="E2" s="3">
+        <f>(F2-H2)/F2</f>
+        <v>0.40404640545139786</v>
+      </c>
+      <c r="F2">
+        <v>22.652770490000002</v>
+      </c>
+      <c r="G2" s="1">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="H2">
+        <v>13.5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
       <c r="C3">
         <v>2030</v>
       </c>
-      <c r="D3">
-        <v>11.3</v>
-      </c>
-      <c r="E3">
-        <v>8828</v>
+      <c r="E3" s="3">
+        <f t="shared" ref="E3:E28" si="0">(F3-H3)/F3</f>
+        <v>0.2857675459404056</v>
+      </c>
+      <c r="F3">
+        <v>38.92435596</v>
+      </c>
+      <c r="G3" s="1">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="H3">
+        <v>27.80103828</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
       </c>
       <c r="C4">
         <v>2035</v>
       </c>
-      <c r="D4">
-        <v>15.47</v>
-      </c>
-      <c r="E4">
-        <v>24198</v>
+      <c r="E4" s="3">
+        <f t="shared" si="0"/>
+        <v>0.20595755623739934</v>
+      </c>
+      <c r="F4">
+        <v>72.101540779999993</v>
+      </c>
+      <c r="G4" s="1">
+        <v>-2.1999999999999999E-2</v>
+      </c>
+      <c r="H4">
+        <v>57.251683640000003</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
         <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
       </c>
       <c r="C5">
         <v>2025</v>
       </c>
-      <c r="D5">
-        <v>9.18</v>
-      </c>
-      <c r="E5">
-        <v>3259</v>
+      <c r="E5" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>13.5</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>13.5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
         <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
       </c>
       <c r="C6">
         <v>2030</v>
       </c>
-      <c r="D6">
-        <v>11.3</v>
-      </c>
-      <c r="E6">
-        <v>154</v>
+      <c r="E6" s="3">
+        <f t="shared" si="0"/>
+        <v>0.7080185525392716</v>
+      </c>
+      <c r="F6">
+        <v>95.2150848</v>
+      </c>
+      <c r="G6" s="1">
+        <v>7.7999999999999996E-3</v>
+      </c>
+      <c r="H6">
+        <v>27.80103828</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
         <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
       </c>
       <c r="C7">
         <v>2035</v>
       </c>
-      <c r="D7">
-        <v>15.47</v>
-      </c>
-      <c r="E7">
-        <v>2441</v>
+      <c r="E7" s="3">
+        <f t="shared" si="0"/>
+        <v>0.73340331201342146</v>
+      </c>
+      <c r="F7">
+        <v>214.75016840000001</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2.7300000000000001E-2</v>
+      </c>
+      <c r="H7">
+        <v>57.251683640000003</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>2025</v>
-      </c>
-      <c r="D8">
-        <v>9.17</v>
-      </c>
-      <c r="E8">
-        <v>4792</v>
+        <v>2040</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="0"/>
+        <v>0.67337701001551531</v>
+      </c>
+      <c r="F8">
+        <v>360.96804700000001</v>
+      </c>
+      <c r="G8" s="1">
+        <v>4.19E-2</v>
+      </c>
+      <c r="H8">
+        <v>117.9004628</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>2030</v>
-      </c>
-      <c r="D9">
-        <v>10.32</v>
-      </c>
-      <c r="E9">
-        <v>6056</v>
+        <v>2045</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="0"/>
+        <v>0.61044819596631716</v>
+      </c>
+      <c r="F9">
+        <v>623.27188550000005</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2.4799999999999999E-2</v>
+      </c>
+      <c r="H9">
+        <v>242.7966874</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>2035</v>
-      </c>
-      <c r="D10">
-        <v>13.16</v>
-      </c>
-      <c r="E10">
-        <v>15336</v>
+        <v>2050</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="0"/>
+        <v>0.48675139825969232</v>
+      </c>
+      <c r="F10">
+        <v>974.18677479999997</v>
+      </c>
+      <c r="G10" s="1">
+        <v>-2.3E-2</v>
+      </c>
+      <c r="H10">
+        <v>500</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C11">
         <v>2025</v>
       </c>
-      <c r="D11">
-        <v>9.17</v>
-      </c>
-      <c r="E11">
-        <v>2435</v>
+      <c r="E11" s="3">
+        <f t="shared" si="0"/>
+        <v>0.40404640545139786</v>
+      </c>
+      <c r="F11">
+        <v>22.652770490000002</v>
+      </c>
+      <c r="G11" s="1">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="H11">
+        <v>13.5</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C12">
         <v>2030</v>
       </c>
-      <c r="D12">
-        <v>10.32</v>
-      </c>
-      <c r="E12">
-        <v>-343</v>
+      <c r="E12" s="3">
+        <f t="shared" si="0"/>
+        <v>0.24310111030084311</v>
+      </c>
+      <c r="F12">
+        <v>45.75593121</v>
+      </c>
+      <c r="H12">
+        <v>34.63261353</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C13">
         <v>2035</v>
       </c>
-      <c r="D13">
-        <v>13.16</v>
-      </c>
-      <c r="E13">
-        <v>-490</v>
+      <c r="E13" s="3">
+        <f t="shared" si="0"/>
+        <v>0.14320620148801064</v>
+      </c>
+      <c r="F13">
+        <v>103.695629</v>
+      </c>
+      <c r="G13" s="1">
+        <v>-2.4E-2</v>
+      </c>
+      <c r="H13">
+        <v>88.845771859999999</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
         <v>9</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
       </c>
       <c r="C14">
         <v>2025</v>
       </c>
-      <c r="D14">
-        <v>9.18</v>
-      </c>
-      <c r="E14">
-        <v>4796</v>
+      <c r="E14" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>13.5</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>13.5</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
         <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
       </c>
       <c r="C15">
         <v>2030</v>
       </c>
-      <c r="D15">
-        <v>11.29</v>
-      </c>
-      <c r="E15">
-        <v>9629</v>
+      <c r="E15" s="3">
+        <f t="shared" si="0"/>
+        <v>0.66061982302997468</v>
+      </c>
+      <c r="F15">
+        <v>102.04666</v>
+      </c>
+      <c r="G15" s="1">
+        <v>8.3499999999999998E-3</v>
+      </c>
+      <c r="H15">
+        <v>34.63261353</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
         <v>9</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
       </c>
       <c r="C16">
         <v>2035</v>
       </c>
-      <c r="D16">
-        <v>15.34</v>
-      </c>
-      <c r="E16">
-        <v>33064</v>
+      <c r="E16" s="3">
+        <f t="shared" si="0"/>
+        <v>0.63934303543273963</v>
+      </c>
+      <c r="F16">
+        <v>246.34425669999999</v>
+      </c>
+      <c r="G16" s="1">
+        <v>4.3700000000000003E-2</v>
+      </c>
+      <c r="H16">
+        <v>88.845771859999999</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
         <v>9</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17">
+        <v>2040</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="0"/>
+        <v>0.51607731125237999</v>
+      </c>
+      <c r="F17">
+        <v>470.9906421</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="H17">
+        <v>227.9230579</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18">
+        <v>2045</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="0"/>
+        <v>0.39419958208013484</v>
+      </c>
+      <c r="F18">
+        <v>965.18417420000003</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="H18">
+        <v>584.70897609999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19">
+        <v>2050</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="0"/>
+        <v>0.24019347156248674</v>
+      </c>
+      <c r="F19">
+        <v>1974.1867749999999</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.108</v>
+      </c>
+      <c r="H19">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>7</v>
       </c>
-      <c r="C17">
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20">
         <v>2025</v>
       </c>
-      <c r="D17">
-        <v>9.18</v>
-      </c>
-      <c r="E17">
-        <v>3259</v>
+      <c r="E20" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H20">
+        <v>13.5</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>7</v>
       </c>
-      <c r="C18">
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21">
         <v>2030</v>
       </c>
-      <c r="D18">
-        <v>11.29</v>
-      </c>
-      <c r="E18">
-        <v>-358</v>
+      <c r="E21" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H21">
+        <v>20.149627169999999</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>7</v>
       </c>
-      <c r="C19">
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22">
         <v>2035</v>
       </c>
-      <c r="D19">
-        <v>15.34</v>
-      </c>
-      <c r="E19">
-        <v>1867</v>
+      <c r="E22" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H22">
+        <v>30.074627790000001</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="E20" t="s">
-        <v>3</v>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23">
+        <v>2025</v>
+      </c>
+      <c r="E23" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H23">
+        <v>13.5</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>9.18</v>
-      </c>
-      <c r="F21">
-        <v>11.3</v>
-      </c>
-      <c r="G21">
-        <v>15.47</v>
-      </c>
-      <c r="H21">
-        <v>9.18</v>
-      </c>
-      <c r="I21">
-        <v>11.3</v>
-      </c>
-      <c r="J21">
-        <v>15.47</v>
-      </c>
-      <c r="K21">
-        <v>9.17</v>
-      </c>
-      <c r="L21">
-        <v>10.32</v>
-      </c>
-      <c r="M21">
-        <v>13.16</v>
-      </c>
-      <c r="N21">
-        <v>9.17</v>
-      </c>
-      <c r="O21">
-        <v>10.32</v>
-      </c>
-      <c r="P21">
-        <v>13.16</v>
-      </c>
-      <c r="Q21">
-        <v>9.18</v>
-      </c>
-      <c r="R21">
-        <v>11.29</v>
-      </c>
-      <c r="S21">
-        <v>15.34</v>
-      </c>
-      <c r="T21">
-        <v>9.18</v>
-      </c>
-      <c r="U21">
-        <v>11.29</v>
-      </c>
-      <c r="V21">
-        <v>15.34</v>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24">
+        <v>2030</v>
+      </c>
+      <c r="E24" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H24">
+        <v>20.149627169999999</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D22" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22">
-        <v>4796</v>
-      </c>
-      <c r="F22">
-        <v>8828</v>
-      </c>
-      <c r="G22">
-        <v>24198</v>
-      </c>
-      <c r="K22">
-        <v>4792</v>
-      </c>
-      <c r="L22">
-        <v>6056</v>
-      </c>
-      <c r="M22">
-        <v>15336</v>
-      </c>
-      <c r="Q22">
-        <v>4796</v>
-      </c>
-      <c r="R22">
-        <v>9629</v>
-      </c>
-      <c r="S22">
-        <v>33064</v>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25">
+        <v>2035</v>
+      </c>
+      <c r="E25" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H25">
+        <v>30.074627790000001</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D23" t="s">
-        <v>7</v>
-      </c>
-      <c r="H23">
-        <v>3259</v>
-      </c>
-      <c r="I23">
-        <v>154</v>
-      </c>
-      <c r="J23">
-        <v>2441</v>
-      </c>
-      <c r="N23">
-        <v>2435</v>
-      </c>
-      <c r="O23">
-        <v>-343</v>
-      </c>
-      <c r="P23">
-        <v>-490</v>
-      </c>
-      <c r="T23">
-        <v>3259</v>
-      </c>
-      <c r="U23">
-        <v>-358</v>
-      </c>
-      <c r="V23">
-        <v>1867</v>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26">
+        <v>2040</v>
+      </c>
+      <c r="E26" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H26">
+        <v>44.888336090000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27">
+        <v>2045</v>
+      </c>
+      <c r="E27" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H27">
+        <v>66.998758269999996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28">
+        <v>2050</v>
+      </c>
+      <c r="E28" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H28">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_analysis/procurement.xlsx
+++ b/data/data_analysis/procurement.xlsx
@@ -8,13 +8,60 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10C2556-FB06-4929-9D11-22CBAB2A4225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F459CE0-8CD8-425B-B2A1-6746A1CF1DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="2" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Scaling" sheetId="1" r:id="rId1"/>
+    <sheet name="45Q" sheetId="2" r:id="rId2"/>
+    <sheet name="Marginal Supply" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">'45Q'!$B$2:$B$13</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'45Q'!$D$1</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">'45Q'!$G$1</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">'45Q'!$G$2:$G$13</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">'45Q'!$B$2:$B$13</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">'45Q'!$D$1</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">'45Q'!$D$2:$D$13</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">'45Q'!$G$1</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">'45Q'!$G$2:$G$13</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">'45Q'!$B$2:$B$13</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">'45Q'!$D$1</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">'45Q'!$D$2:$D$13</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'45Q'!$D$2:$D$13</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">'45Q'!$G$1</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">'45Q'!$G$2:$G$13</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">'45Q'!$D$1</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">'45Q'!$D$2:$D$13</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">'45Q'!$G$1</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">'45Q'!$G$2:$G$13</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">'45Q'!$D$1</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">'45Q'!$D$2:$D$13</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">'45Q'!$E$1</definedName>
+    <definedName name="_xlchart.v1.29" hidden="1">'45Q'!$E$2:$E$13</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'45Q'!$G$1</definedName>
+    <definedName name="_xlchart.v1.30" hidden="1">'45Q'!$F$1</definedName>
+    <definedName name="_xlchart.v1.31" hidden="1">'45Q'!$F$2:$F$13</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">'45Q'!$G$1</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">'45Q'!$G$2:$G$13</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">'45Q'!$D$1</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">'45Q'!$D$1:$D$13</definedName>
+    <definedName name="_xlchart.v1.36" hidden="1">'45Q'!$D$2:$D$13</definedName>
+    <definedName name="_xlchart.v1.37" hidden="1">'45Q'!$E$1</definedName>
+    <definedName name="_xlchart.v1.38" hidden="1">'45Q'!$E$2:$E$13</definedName>
+    <definedName name="_xlchart.v1.39" hidden="1">'45Q'!$F$1</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'45Q'!$G$2:$G$13</definedName>
+    <definedName name="_xlchart.v1.40" hidden="1">'45Q'!$F$2:$F$13</definedName>
+    <definedName name="_xlchart.v1.41" hidden="1">'45Q'!$G$1</definedName>
+    <definedName name="_xlchart.v1.42" hidden="1">'45Q'!$G$2:$G$13</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'45Q'!$B$1:$B$13</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">'45Q'!$B$2:$B$13</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">'45Q'!$D$1</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">'45Q'!$D$1:$D$13</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">'45Q'!$D$2:$D$13</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="34">
   <si>
     <t>Scenario</t>
   </si>
@@ -73,12 +120,78 @@
   <si>
     <t>Nothing</t>
   </si>
+  <si>
+    <t>Rhodium $ 100B</t>
+  </si>
+  <si>
+    <t>Scaling</t>
+  </si>
+  <si>
+    <t>Subsidy Procurement</t>
+  </si>
+  <si>
+    <t>No Subsidy Procurement</t>
+  </si>
+  <si>
+    <t>Procurement Budget (Million USD/yr)</t>
+  </si>
+  <si>
+    <t>Additional 45Q (Million USD)</t>
+  </si>
+  <si>
+    <t>Procurement (Mt)</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Percent of Procurement Budget Spent on 45Q</t>
+  </si>
+  <si>
+    <t>Tech</t>
+  </si>
+  <si>
+    <t>BECCS</t>
+  </si>
+  <si>
+    <t>DAC</t>
+  </si>
+  <si>
+    <t>OEW</t>
+  </si>
+  <si>
+    <t>TEW</t>
+  </si>
+  <si>
+    <t>Baseline Scenario</t>
+  </si>
+  <si>
+    <t>EFI $3B</t>
+  </si>
+  <si>
+    <t>Difference - EFI</t>
+  </si>
+  <si>
+    <t>Difference - Scaling</t>
+  </si>
+  <si>
+    <t>Difference - Rhodium</t>
+  </si>
+  <si>
+    <t>% - EFI</t>
+  </si>
+  <si>
+    <t>% - Scaling</t>
+  </si>
+  <si>
+    <t>% - Rhodium</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,6 +205,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FFA9B7C6"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -115,11 +234,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -163,7 +286,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$G$1</c:f>
+              <c:f>Scaling!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -210,7 +333,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$28</c:f>
+              <c:f>Scaling!$F$2:$F$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="27"/>
@@ -273,7 +396,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$28</c:f>
+              <c:f>Scaling!$G$2:$G$28</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="27"/>
@@ -658,7 +781,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$G$1</c:f>
+              <c:f>Scaling!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -705,7 +828,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$H$2:$H$28</c:f>
+              <c:f>Scaling!$H$2:$H$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="27"/>
@@ -795,7 +918,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$28</c:f>
+              <c:f>Scaling!$G$2:$G$28</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="27"/>
@@ -1185,7 +1308,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$E$1</c:f>
+              <c:f>Scaling!$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1232,7 +1355,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$28</c:f>
+              <c:f>Scaling!$E$2:$E$28</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="27"/>
@@ -1322,7 +1445,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$28</c:f>
+              <c:f>Scaling!$G$2:$G$28</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="27"/>
@@ -1687,6 +1810,77 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.36</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.42</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Percentage of Procurement Budget Spent on 45Q</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+            </a:rPr>
+            <a:t>Percentage of Procurement Budget Spent on 45Q</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{5F8C8374-44F7-452F-BFFD-4FAF44BD728B}" formatIdx="3">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.41</cx:f>
+              <cx:v>Percent of Procurement Budget Spent on 45Q</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1807,6 +2001,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3351,6 +3585,521 @@
         <a:noFill/>
       </a:ln>
     </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -3465,6 +4214,89 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1847850</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1447800</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Chart 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21BA8017-080A-86DA-77CA-497F39B7F6D1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6629400" y="2624137"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3788,7 +4620,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B537AA0D-F5C4-4357-8465-DF25FED59988}">
   <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -3797,7 +4629,7 @@
     <col min="5" max="5" width="28.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3820,7 +4652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3844,7 +4676,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -3868,7 +4700,7 @@
         <v>27.80103828</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -3892,7 +4724,7 @@
         <v>57.251683640000003</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -3916,7 +4748,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -3940,7 +4772,7 @@
         <v>27.80103828</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -3964,7 +4796,7 @@
         <v>57.251683640000003</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -3988,7 +4820,7 @@
         <v>117.9004628</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -4012,7 +4844,7 @@
         <v>242.7966874</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -4036,7 +4868,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -4060,7 +4892,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -4081,7 +4913,7 @@
         <v>34.63261353</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -4105,7 +4937,7 @@
         <v>88.845771859999999</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -4129,7 +4961,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -4153,7 +4985,7 @@
         <v>34.63261353</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -4177,7 +5009,7 @@
         <v>88.845771859999999</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -4201,7 +5033,7 @@
         <v>227.9230579</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -4225,7 +5057,7 @@
         <v>584.70897609999997</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -4249,7 +5081,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -4267,7 +5099,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -4285,7 +5117,7 @@
         <v>20.149627169999999</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -4303,7 +5135,7 @@
         <v>30.074627790000001</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -4321,7 +5153,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -4339,7 +5171,7 @@
         <v>20.149627169999999</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -4357,7 +5189,7 @@
         <v>30.074627790000001</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -4375,7 +5207,7 @@
         <v>44.888336090000003</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -4393,7 +5225,7 @@
         <v>66.998758269999996</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -4415,4 +5247,2963 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3A5A500-B443-4A7A-9013-C11AEE955A78}">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4">
+        <v>9.1497691446116427</v>
+      </c>
+      <c r="D2">
+        <v>2025</v>
+      </c>
+      <c r="E2">
+        <f>H2-I2</f>
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>3300</v>
+      </c>
+      <c r="G2" s="3">
+        <f>E2/F2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4">
+        <v>10.257766689126317</v>
+      </c>
+      <c r="D3">
+        <v>2030</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E13" si="0">H3-I3</f>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>3300</v>
+      </c>
+      <c r="G3" s="3">
+        <f t="shared" ref="G3:G13" si="1">E3/F3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="4">
+        <v>67.381687905293646</v>
+      </c>
+      <c r="D4">
+        <v>2030</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>20000</v>
+      </c>
+      <c r="G4" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="4">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>2030</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1608</v>
+      </c>
+      <c r="G5" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4">
+        <v>9.1527704871198079</v>
+      </c>
+      <c r="D6">
+        <v>2025</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>1521.9699999999998</v>
+      </c>
+      <c r="F6">
+        <v>3300</v>
+      </c>
+      <c r="G6" s="3">
+        <f t="shared" si="1"/>
+        <v>0.46120303030303023</v>
+      </c>
+      <c r="H6" s="5">
+        <v>3302.97</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4">
+        <v>11.123317675046577</v>
+      </c>
+      <c r="D7">
+        <v>2030</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>1195</v>
+      </c>
+      <c r="F7">
+        <v>3300</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" si="1"/>
+        <v>0.36212121212121212</v>
+      </c>
+      <c r="H7" s="5">
+        <v>3330</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="4">
+        <v>67.381687905293646</v>
+      </c>
+      <c r="D8">
+        <v>2030</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>7135</v>
+      </c>
+      <c r="F8">
+        <v>20000</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="1"/>
+        <v>0.35675000000000001</v>
+      </c>
+      <c r="H8" s="5">
+        <v>20155</v>
+      </c>
+      <c r="I8" s="5">
+        <v>13020</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="4">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>2030</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>549.20000000000005</v>
+      </c>
+      <c r="F9">
+        <v>1484</v>
+      </c>
+      <c r="G9" s="3">
+        <f t="shared" si="1"/>
+        <v>0.37008086253369277</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1480</v>
+      </c>
+      <c r="I9" s="5">
+        <v>930.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="4">
+        <v>11.123317675046577</v>
+      </c>
+      <c r="D10">
+        <v>2025</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>1521.3599999999997</v>
+      </c>
+      <c r="F10">
+        <v>3300</v>
+      </c>
+      <c r="G10" s="3">
+        <f t="shared" si="1"/>
+        <v>0.46101818181818172</v>
+      </c>
+      <c r="H10" s="5">
+        <v>3302.74</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1781.38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="4">
+        <v>14.849857137390348</v>
+      </c>
+      <c r="D11">
+        <v>2030</v>
+      </c>
+      <c r="E11" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F11">
+        <v>3300</v>
+      </c>
+      <c r="G11" s="3" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="4">
+        <v>67.41404651543381</v>
+      </c>
+      <c r="D12">
+        <v>2030</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>7172.6200000000008</v>
+      </c>
+      <c r="F12">
+        <v>20000</v>
+      </c>
+      <c r="G12" s="3">
+        <f t="shared" si="1"/>
+        <v>0.35863100000000003</v>
+      </c>
+      <c r="H12" s="5">
+        <v>20167</v>
+      </c>
+      <c r="I12" s="5">
+        <v>12994.38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="4">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>2030</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>560.15999999999985</v>
+      </c>
+      <c r="F13">
+        <v>1483</v>
+      </c>
+      <c r="G13" s="3">
+        <f t="shared" si="1"/>
+        <v>0.37772083614295338</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1502.36</v>
+      </c>
+      <c r="I13" s="5">
+        <v>942.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB97F9D7-BF24-4FBB-A24F-14025D988DE1}">
+  <dimension ref="A1:N73"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>2025</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="4">
+        <f>E2-$D2</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="3">
+        <f>I2/SUM(I2:I5)</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>2025</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="4">
+        <v>12.302540506666601</v>
+      </c>
+      <c r="E3" s="4">
+        <v>20.75363917</v>
+      </c>
+      <c r="F3" s="4">
+        <v>12.38344833</v>
+      </c>
+      <c r="G3" s="4">
+        <v>12.337415273333299</v>
+      </c>
+      <c r="I3" s="4">
+        <f t="shared" ref="I3:I25" si="0">E3-$D3</f>
+        <v>8.4510986633333989</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="3">
+        <f>I3/SUM(I2:I5)</f>
+        <v>0.91515732423128149</v>
+      </c>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>2025</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.75969476000000002</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1.26107314666666</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.74495450333333302</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.74290502000000003</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" si="0"/>
+        <v>0.50137838666666001</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="3">
+        <f>I4/SUM(I2:I5)</f>
+        <v>5.4293544667750375E-2</v>
+      </c>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2025</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.17843507</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.46054363666666598</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.174611396666666</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.173851956666666</v>
+      </c>
+      <c r="I5" s="4">
+        <f t="shared" si="0"/>
+        <v>0.28210856666666595</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="3">
+        <f>I5/SUM(I2:I5)</f>
+        <v>3.0549131100968078E-2</v>
+      </c>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2030</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="4">
+        <v>8.65097456666666</v>
+      </c>
+      <c r="E6" s="4">
+        <v>11.925114263333301</v>
+      </c>
+      <c r="F6" s="4">
+        <v>10.037346550000001</v>
+      </c>
+      <c r="G6" s="4">
+        <v>29.0249384333333</v>
+      </c>
+      <c r="I6" s="4">
+        <f t="shared" si="0"/>
+        <v>3.2741396966666407</v>
+      </c>
+      <c r="J6" s="4">
+        <f t="shared" ref="J2:K17" si="1">F6-$D6</f>
+        <v>1.3863719833333406</v>
+      </c>
+      <c r="K6" s="4">
+        <f t="shared" si="1"/>
+        <v>20.373963866666642</v>
+      </c>
+      <c r="L6" s="3">
+        <f>I6/SUM(I6:I9)</f>
+        <v>0.29026154892397193</v>
+      </c>
+      <c r="M6" s="3">
+        <f>J6/SUM(J6:J9)</f>
+        <v>0.27495341571805787</v>
+      </c>
+      <c r="N6" s="3">
+        <f>K6/SUM(K6:K9)</f>
+        <v>0.30065410025493072</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2030</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4">
+        <v>15.9532513066666</v>
+      </c>
+      <c r="E7" s="4">
+        <v>22.5884521133333</v>
+      </c>
+      <c r="F7" s="4">
+        <v>19.007243493333299</v>
+      </c>
+      <c r="G7" s="4">
+        <v>55.595604350000002</v>
+      </c>
+      <c r="I7" s="4">
+        <f t="shared" si="0"/>
+        <v>6.6352008066667008</v>
+      </c>
+      <c r="J7" s="4">
+        <f t="shared" si="1"/>
+        <v>3.053992186666699</v>
+      </c>
+      <c r="K7" s="4">
+        <f t="shared" si="1"/>
+        <v>39.642353043333401</v>
+      </c>
+      <c r="L7" s="3">
+        <f>I7/SUM(I6:I9)</f>
+        <v>0.58822892179140773</v>
+      </c>
+      <c r="M7" s="3">
+        <f>J7/SUM(J6:J9)</f>
+        <v>0.60568562650935354</v>
+      </c>
+      <c r="N7" s="3">
+        <f>K7/SUM(K6:K9)</f>
+        <v>0.58499347815824465</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>2030</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1.8031504333333299</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2.57378616</v>
+      </c>
+      <c r="F8" s="4">
+        <v>2.1532217299999998</v>
+      </c>
+      <c r="G8" s="4">
+        <v>6.3818963266666602</v>
+      </c>
+      <c r="I8" s="4">
+        <f t="shared" si="0"/>
+        <v>0.77063572666667013</v>
+      </c>
+      <c r="J8" s="4">
+        <f t="shared" si="1"/>
+        <v>0.35007129666666992</v>
+      </c>
+      <c r="K8" s="4">
+        <f t="shared" si="1"/>
+        <v>4.5787458933333305</v>
+      </c>
+      <c r="L8" s="3">
+        <f>I8/SUM(I6:I9)</f>
+        <v>6.8318990758442624E-2</v>
+      </c>
+      <c r="M8" s="3">
+        <f>J8/SUM(J6:J9)</f>
+        <v>6.9428190933231826E-2</v>
+      </c>
+      <c r="N8" s="3">
+        <f>K8/SUM(K6:K9)</f>
+        <v>6.7567545317401126E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>2030</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.93724469666666599</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1.53723203333333</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1.1890160333333299</v>
+      </c>
+      <c r="G9" s="4">
+        <v>4.1076434300000004</v>
+      </c>
+      <c r="I9" s="4">
+        <f t="shared" si="0"/>
+        <v>0.59998733666666404</v>
+      </c>
+      <c r="J9" s="4">
+        <f t="shared" si="1"/>
+        <v>0.25177133666666396</v>
+      </c>
+      <c r="K9" s="4">
+        <f t="shared" si="1"/>
+        <v>3.1703987333333346</v>
+      </c>
+      <c r="L9" s="3">
+        <f>I9/SUM(I6:I9)</f>
+        <v>5.3190538526177646E-2</v>
+      </c>
+      <c r="M9" s="3">
+        <f>J9/SUM(J6:J9)</f>
+        <v>4.993276683935681E-2</v>
+      </c>
+      <c r="N9" s="3">
+        <f>K9/SUM(K6:K9)</f>
+        <v>4.6784876269423577E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>2035</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="4">
+        <v>32.8174128333333</v>
+      </c>
+      <c r="E10" s="4">
+        <v>40.421700000000001</v>
+      </c>
+      <c r="F10" s="4">
+        <v>37.7868285666666</v>
+      </c>
+      <c r="G10" s="4">
+        <v>114.596670466666</v>
+      </c>
+      <c r="I10" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6042871666667011</v>
+      </c>
+      <c r="J10" s="4">
+        <f t="shared" si="1"/>
+        <v>4.9694157333332996</v>
+      </c>
+      <c r="K10" s="4">
+        <f t="shared" si="1"/>
+        <v>81.779257633332691</v>
+      </c>
+      <c r="L10" s="3">
+        <f>I10/SUM(I10:I13)</f>
+        <v>0.51139464221983688</v>
+      </c>
+      <c r="M10" s="3">
+        <f>J10/SUM(J10:J13)</f>
+        <v>0.49509882031009567</v>
+      </c>
+      <c r="N10" s="3">
+        <f>K10/SUM(K10:K13)</f>
+        <v>0.51852648076029639</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>2035</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4">
+        <v>6.3966195333333298</v>
+      </c>
+      <c r="E11" s="4">
+        <v>8.06076223333333</v>
+      </c>
+      <c r="F11" s="4">
+        <v>7.4923460333333303</v>
+      </c>
+      <c r="G11" s="4">
+        <v>26.1684194933333</v>
+      </c>
+      <c r="I11" s="4">
+        <f t="shared" si="0"/>
+        <v>1.6641427000000002</v>
+      </c>
+      <c r="J11" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0957265000000005</v>
+      </c>
+      <c r="K11" s="4">
+        <f t="shared" si="1"/>
+        <v>19.771799959999971</v>
+      </c>
+      <c r="L11" s="3">
+        <f>I11/SUM(I10:I13)</f>
+        <v>0.11191498190648941</v>
+      </c>
+      <c r="M11" s="3">
+        <f>J11/SUM(J10:J13)</f>
+        <v>0.10916633396027549</v>
+      </c>
+      <c r="N11" s="3">
+        <f>K11/SUM(K10:K13)</f>
+        <v>0.12536433012784678</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>2035</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="4">
+        <v>8.9131753333333297</v>
+      </c>
+      <c r="E12" s="4">
+        <v>11.88907687</v>
+      </c>
+      <c r="F12" s="4">
+        <v>11.058108819999999</v>
+      </c>
+      <c r="G12" s="4">
+        <v>38.070494366666601</v>
+      </c>
+      <c r="I12" s="4">
+        <f t="shared" si="0"/>
+        <v>2.9759015366666706</v>
+      </c>
+      <c r="J12" s="4">
+        <f t="shared" si="1"/>
+        <v>2.1449334866666696</v>
+      </c>
+      <c r="K12" s="4">
+        <f t="shared" si="1"/>
+        <v>29.157319033333273</v>
+      </c>
+      <c r="L12" s="3">
+        <f>I12/SUM(I10:I13)</f>
+        <v>0.20013185565849878</v>
+      </c>
+      <c r="M12" s="3">
+        <f>J12/SUM(J10:J13)</f>
+        <v>0.21369796689961559</v>
+      </c>
+      <c r="N12" s="3">
+        <f>K12/SUM(K10:K13)</f>
+        <v>0.1848737988616464</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>2035</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="4">
+        <v>8.8559258333333304</v>
+      </c>
+      <c r="E13" s="4">
+        <v>11.481298839999999</v>
+      </c>
+      <c r="F13" s="4">
+        <v>10.683070016666599</v>
+      </c>
+      <c r="G13" s="4">
+        <v>35.862267099999997</v>
+      </c>
+      <c r="I13" s="4">
+        <f t="shared" si="0"/>
+        <v>2.6253730066666687</v>
+      </c>
+      <c r="J13" s="4">
+        <f t="shared" si="1"/>
+        <v>1.8271441833332691</v>
+      </c>
+      <c r="K13" s="4">
+        <f t="shared" si="1"/>
+        <v>27.006341266666666</v>
+      </c>
+      <c r="L13" s="3">
+        <f>I13/SUM(I10:I13)</f>
+        <v>0.17655852021517499</v>
+      </c>
+      <c r="M13" s="3">
+        <f>J13/SUM(J10:J13)</f>
+        <v>0.18203687883001313</v>
+      </c>
+      <c r="N13" s="3">
+        <f>K13/SUM(K10:K13)</f>
+        <v>0.17123539025021053</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14">
+        <v>2040</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="4">
+        <v>59.1438998333333</v>
+      </c>
+      <c r="E14" s="4">
+        <v>56.976563966666603</v>
+      </c>
+      <c r="F14" s="4">
+        <v>56.951071833333302</v>
+      </c>
+      <c r="G14" s="4">
+        <v>154.085919166666</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4">
+        <f t="shared" si="1"/>
+        <v>94.942019333332695</v>
+      </c>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3">
+        <f>K14/SUM(K14:K17)</f>
+        <v>0.39032213669832749</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15">
+        <v>2040</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="4">
+        <v>11.3755561333333</v>
+      </c>
+      <c r="E15" s="4">
+        <v>11.1483247333333</v>
+      </c>
+      <c r="F15" s="4">
+        <v>11.153745166666599</v>
+      </c>
+      <c r="G15" s="4">
+        <v>39.758809566666599</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4">
+        <f t="shared" si="1"/>
+        <v>28.383253433333302</v>
+      </c>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3">
+        <f>K15/SUM(K14:K17)</f>
+        <v>0.1166881872151129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16">
+        <v>2040</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="4">
+        <v>19.689983866666601</v>
+      </c>
+      <c r="E16" s="4">
+        <v>21.142851033333301</v>
+      </c>
+      <c r="F16" s="4">
+        <v>21.151816766666599</v>
+      </c>
+      <c r="G16" s="4">
+        <v>74.714340066666594</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4">
+        <f t="shared" si="1"/>
+        <v>55.024356199999993</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3">
+        <f>K16/SUM(K14:K17)</f>
+        <v>0.22621410870806635</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17">
+        <v>2040</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="4">
+        <v>27.481140133333302</v>
+      </c>
+      <c r="E17" s="4">
+        <v>28.4615771</v>
+      </c>
+      <c r="F17" s="4">
+        <v>28.472625499999999</v>
+      </c>
+      <c r="G17" s="4">
+        <v>92.371672066666605</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4">
+        <f t="shared" si="1"/>
+        <v>64.890531933333307</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3">
+        <f>K17/SUM(K14:K17)</f>
+        <v>0.26677556737849328</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18">
+        <v>2045</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="4">
+        <v>110.52516749999999</v>
+      </c>
+      <c r="E18" s="4">
+        <v>105.954286533333</v>
+      </c>
+      <c r="F18" s="4">
+        <v>105.939343766666</v>
+      </c>
+      <c r="G18" s="4">
+        <v>242.41138166666599</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4">
+        <f t="shared" ref="K18:K25" si="2">G18-$D18</f>
+        <v>131.88621416666598</v>
+      </c>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3">
+        <f>K18/SUM(K18:K21)</f>
+        <v>0.34646965147739606</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19">
+        <v>2045</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="4">
+        <v>22.4968641333333</v>
+      </c>
+      <c r="E19" s="4">
+        <v>21.9651751</v>
+      </c>
+      <c r="F19" s="4">
+        <v>21.967353466666601</v>
+      </c>
+      <c r="G19" s="4">
+        <v>63.072072800000001</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4">
+        <f t="shared" si="2"/>
+        <v>40.575208666666697</v>
+      </c>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3">
+        <f>K19/SUM(K18:K21)</f>
+        <v>0.10659247817665984</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20">
+        <v>2045</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="4">
+        <v>33.472099466666599</v>
+      </c>
+      <c r="E20" s="4">
+        <v>35.921076766666602</v>
+      </c>
+      <c r="F20" s="4">
+        <v>35.926912266666598</v>
+      </c>
+      <c r="G20" s="4">
+        <v>111.966809166666</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4">
+        <f t="shared" si="2"/>
+        <v>78.49470969999939</v>
+      </c>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3">
+        <f>K20/SUM(K18:K21)</f>
+        <v>0.20620832044060539</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21">
+        <v>2045</v>
+      </c>
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="4">
+        <v>76.120413600000006</v>
+      </c>
+      <c r="E21" s="4">
+        <v>78.775144066666599</v>
+      </c>
+      <c r="F21" s="4">
+        <v>78.782043999999999</v>
+      </c>
+      <c r="G21" s="4">
+        <v>205.82161600000001</v>
+      </c>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4">
+        <f t="shared" si="2"/>
+        <v>129.7012024</v>
+      </c>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3">
+        <f>K21/SUM(K18:K21)</f>
+        <v>0.34072954990533866</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22">
+        <v>2050</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="4">
+        <v>206.888348333333</v>
+      </c>
+      <c r="E22" s="4">
+        <v>198.573914</v>
+      </c>
+      <c r="F22" s="4">
+        <v>198.586344</v>
+      </c>
+      <c r="G22" s="4">
+        <v>297.99930599999999</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4">
+        <f t="shared" si="2"/>
+        <v>91.110957666666991</v>
+      </c>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3">
+        <f>K22/SUM(K22:K25)</f>
+        <v>0.19206759514842348</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23">
+        <v>2050</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="4">
+        <v>49.988974566666599</v>
+      </c>
+      <c r="E23" s="4">
+        <v>48.593891499999998</v>
+      </c>
+      <c r="F23" s="4">
+        <v>48.593863266666602</v>
+      </c>
+      <c r="G23" s="4">
+        <v>119.52430123333301</v>
+      </c>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4">
+        <f t="shared" si="2"/>
+        <v>69.535326666666407</v>
+      </c>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3">
+        <f>K23/SUM(K22:K25)</f>
+        <v>0.14658481606118351</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24">
+        <v>2050</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="4">
+        <v>65.061545266666599</v>
+      </c>
+      <c r="E24" s="4">
+        <v>69.434285799999998</v>
+      </c>
+      <c r="F24" s="4">
+        <v>69.436308333333301</v>
+      </c>
+      <c r="G24" s="4">
+        <v>182.065700666666</v>
+      </c>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4">
+        <f t="shared" si="2"/>
+        <v>117.00415539999941</v>
+      </c>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3">
+        <f>K24/SUM(K22:K25)</f>
+        <v>0.2466520748499603</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25">
+        <v>2050</v>
+      </c>
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="4">
+        <v>177.878598333333</v>
+      </c>
+      <c r="E25" s="4">
+        <v>183.20800850000001</v>
+      </c>
+      <c r="F25" s="4">
+        <v>183.19356916666601</v>
+      </c>
+      <c r="G25" s="4">
+        <v>374.59739093333297</v>
+      </c>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4">
+        <f t="shared" si="2"/>
+        <v>196.71879259999997</v>
+      </c>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3">
+        <f>K25/SUM(K22:K25)</f>
+        <v>0.41469551394043275</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26">
+        <v>2025</v>
+      </c>
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="4">
+        <f>E26-$D26</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="3">
+        <f>I26/SUM(I26:I29)</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27">
+        <v>2025</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27">
+        <v>12.3018890866666</v>
+      </c>
+      <c r="E27">
+        <v>20.753885093333299</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="I27" s="4">
+        <f t="shared" ref="I27:I49" si="3">E27-$D27</f>
+        <v>8.4519960066666986</v>
+      </c>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="3">
+        <f>I27/SUM(I26:I29)</f>
+        <v>0.91523639156372061</v>
+      </c>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28">
+        <v>2025</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28">
+        <v>0.76009263000000005</v>
+      </c>
+      <c r="E28">
+        <v>1.2608490400000001</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="I28" s="4">
+        <f t="shared" si="3"/>
+        <v>0.50075641000000004</v>
+      </c>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="3">
+        <f>I28/SUM(I26:I29)</f>
+        <v>5.4225119058184668E-2</v>
+      </c>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29">
+        <v>2025</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29">
+        <v>0.17853032999999999</v>
+      </c>
+      <c r="E29">
+        <v>0.46054620333333302</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="I29" s="4">
+        <f t="shared" si="3"/>
+        <v>0.282015873333333</v>
+      </c>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="3">
+        <f>I29/SUM(I26:I29)</f>
+        <v>3.0538489378094842E-2</v>
+      </c>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30">
+        <v>2030</v>
+      </c>
+      <c r="C30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30">
+        <v>10.8468415733333</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30">
+        <v>12.15459806</v>
+      </c>
+      <c r="G30">
+        <v>30.969142233333301</v>
+      </c>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4">
+        <f t="shared" ref="J30:J45" si="4">F30-$D30</f>
+        <v>1.3077564866666993</v>
+      </c>
+      <c r="K30" s="4">
+        <f t="shared" ref="K30:K49" si="5">G30-$D30</f>
+        <v>20.122300660000001</v>
+      </c>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3">
+        <f>J30/SUM(J30:J33)</f>
+        <v>0.25618436552952295</v>
+      </c>
+      <c r="N30" s="3">
+        <f>K30/SUM(K30:K33)</f>
+        <v>0.29717517114896358</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31">
+        <v>2030</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31">
+        <v>19.872583573333301</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31">
+        <v>22.984575606666599</v>
+      </c>
+      <c r="G31">
+        <v>59.723357540000002</v>
+      </c>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4">
+        <f t="shared" si="4"/>
+        <v>3.1119920333332978</v>
+      </c>
+      <c r="K31" s="4">
+        <f t="shared" si="5"/>
+        <v>39.850773966666701</v>
+      </c>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3">
+        <f>J31/SUM(J30:J33)</f>
+        <v>0.6096270312713119</v>
+      </c>
+      <c r="N31" s="3">
+        <f>K31/SUM(K30:K33)</f>
+        <v>0.5885341231136757</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32">
+        <v>2030</v>
+      </c>
+      <c r="C32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32">
+        <v>2.2453959733333302</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32">
+        <v>2.6211905500000001</v>
+      </c>
+      <c r="G32">
+        <v>6.8402470766666603</v>
+      </c>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4">
+        <f t="shared" si="4"/>
+        <v>0.37579457666666993</v>
+      </c>
+      <c r="K32" s="4">
+        <f t="shared" si="5"/>
+        <v>4.5948511033333297</v>
+      </c>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3">
+        <f>J32/SUM(J30:J33)</f>
+        <v>7.3616683361420784E-2</v>
+      </c>
+      <c r="N32" s="3">
+        <f>K32/SUM(K30:K33)</f>
+        <v>6.7858824202514739E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33">
+        <v>2030</v>
+      </c>
+      <c r="C33" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33">
+        <v>1.25755285333333</v>
+      </c>
+      <c r="E33" s="4"/>
+      <c r="F33">
+        <v>1.56675720666666</v>
+      </c>
+      <c r="G33">
+        <v>4.4015445833333304</v>
+      </c>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4">
+        <f t="shared" si="4"/>
+        <v>0.30920435333332996</v>
+      </c>
+      <c r="K33" s="4">
+        <f t="shared" si="5"/>
+        <v>3.1439917300000007</v>
+      </c>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3">
+        <f>J33/SUM(J30:J33)</f>
+        <v>6.0571919837744403E-2</v>
+      </c>
+      <c r="N33" s="3">
+        <f>K33/SUM(K30:K33)</f>
+        <v>4.6431881534846134E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34">
+        <v>2035</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34">
+        <v>50.522071966666601</v>
+      </c>
+      <c r="E34">
+        <v>57.598385899999997</v>
+      </c>
+      <c r="F34">
+        <v>54.909849133333303</v>
+      </c>
+      <c r="G34">
+        <v>128.53779913333301</v>
+      </c>
+      <c r="I34" s="4">
+        <f t="shared" si="3"/>
+        <v>7.0763139333333953</v>
+      </c>
+      <c r="J34" s="4">
+        <f t="shared" si="4"/>
+        <v>4.3877771666667016</v>
+      </c>
+      <c r="K34" s="4">
+        <f t="shared" si="5"/>
+        <v>78.015727166666409</v>
+      </c>
+      <c r="L34" s="3">
+        <f>I34/SUM(I34:I37)</f>
+        <v>0.47639036558750303</v>
+      </c>
+      <c r="M34" s="3">
+        <f>J34/SUM(J34:J37)</f>
+        <v>0.4382677662628251</v>
+      </c>
+      <c r="N34" s="3">
+        <f>K34/SUM(K34:K37)</f>
+        <v>0.49492086132824242</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35">
+        <v>2035</v>
+      </c>
+      <c r="C35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35">
+        <v>10.102477916666601</v>
+      </c>
+      <c r="E35">
+        <v>11.817029399999999</v>
+      </c>
+      <c r="F35">
+        <v>11.2481988666666</v>
+      </c>
+      <c r="G35">
+        <v>30.917709349999999</v>
+      </c>
+      <c r="I35" s="4">
+        <f t="shared" si="3"/>
+        <v>1.7145514833333984</v>
+      </c>
+      <c r="J35" s="4">
+        <f t="shared" si="4"/>
+        <v>1.1457209499999994</v>
+      </c>
+      <c r="K35" s="4">
+        <f t="shared" si="5"/>
+        <v>20.815231433333398</v>
+      </c>
+      <c r="L35" s="3">
+        <f>I35/SUM(I34:I37)</f>
+        <v>0.11542673426573519</v>
+      </c>
+      <c r="M35" s="3">
+        <f>J35/SUM(J34:J37)</f>
+        <v>0.11443893854310765</v>
+      </c>
+      <c r="N35" s="3">
+        <f>K35/SUM(K34:K37)</f>
+        <v>0.13204891685139269</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36">
+        <v>2035</v>
+      </c>
+      <c r="C36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36">
+        <v>14.10962531</v>
+      </c>
+      <c r="E36">
+        <v>17.396169633333301</v>
+      </c>
+      <c r="F36">
+        <v>16.589683036666599</v>
+      </c>
+      <c r="G36">
+        <v>44.909156233333299</v>
+      </c>
+      <c r="I36" s="4">
+        <f t="shared" si="3"/>
+        <v>3.2865443233333007</v>
+      </c>
+      <c r="J36" s="4">
+        <f t="shared" si="4"/>
+        <v>2.4800577266665993</v>
+      </c>
+      <c r="K36" s="4">
+        <f t="shared" si="5"/>
+        <v>30.7995309233333</v>
+      </c>
+      <c r="L36" s="3">
+        <f>I36/SUM(I34:I37)</f>
+        <v>0.22125616054667455</v>
+      </c>
+      <c r="M36" s="3">
+        <f>J36/SUM(J34:J37)</f>
+        <v>0.24771753869505342</v>
+      </c>
+      <c r="N36" s="3">
+        <f>K36/SUM(K34:K37)</f>
+        <v>0.19538791634303879</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37">
+        <v>2035</v>
+      </c>
+      <c r="C37" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37">
+        <v>13.9483635866666</v>
+      </c>
+      <c r="E37">
+        <v>16.724977866666599</v>
+      </c>
+      <c r="F37">
+        <v>15.946443333333301</v>
+      </c>
+      <c r="G37">
+        <v>41.950605400000001</v>
+      </c>
+      <c r="I37" s="4">
+        <f t="shared" si="3"/>
+        <v>2.7766142799999987</v>
+      </c>
+      <c r="J37" s="4">
+        <f t="shared" si="4"/>
+        <v>1.9980797466667006</v>
+      </c>
+      <c r="K37" s="4">
+        <f t="shared" si="5"/>
+        <v>28.002241813333399</v>
+      </c>
+      <c r="L37" s="3">
+        <f>I37/SUM(I34:I37)</f>
+        <v>0.18692673960008727</v>
+      </c>
+      <c r="M37" s="3">
+        <f>J37/SUM(J34:J37)</f>
+        <v>0.1995757564990138</v>
+      </c>
+      <c r="N37" s="3">
+        <f>K37/SUM(K34:K37)</f>
+        <v>0.17764230547732618</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38">
+        <v>2040</v>
+      </c>
+      <c r="C38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38">
+        <v>111.1385561</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38">
+        <v>174.47395166666601</v>
+      </c>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4">
+        <f t="shared" si="5"/>
+        <v>63.335395566666008</v>
+      </c>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3">
+        <f>K38/SUM(K38:K41)</f>
+        <v>0.26041637593067141</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39">
+        <v>2040</v>
+      </c>
+      <c r="C39" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39">
+        <v>23.141853900000001</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39">
+        <v>57.606192233333303</v>
+      </c>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4">
+        <f t="shared" si="5"/>
+        <v>34.464338333333302</v>
+      </c>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3">
+        <f>K39/SUM(K38:K41)</f>
+        <v>0.14170714506974419</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40">
+        <v>2040</v>
+      </c>
+      <c r="C40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40">
+        <v>39.859757299999998</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40">
+        <v>110.0637945</v>
+      </c>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4">
+        <f t="shared" si="5"/>
+        <v>70.204037200000002</v>
+      </c>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3">
+        <f>K40/SUM(K38:K41)</f>
+        <v>0.28865819467539838</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41">
+        <v>2040</v>
+      </c>
+      <c r="C41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41">
+        <v>53.642280266666603</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41">
+        <v>128.84669966666601</v>
+      </c>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4">
+        <f t="shared" si="5"/>
+        <v>75.204419399999409</v>
+      </c>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3">
+        <f>K41/SUM(K38:K41)</f>
+        <v>0.30921828432418608</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42">
+        <v>2045</v>
+      </c>
+      <c r="C42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42">
+        <v>238.62236933333301</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42">
+        <v>296.78645699999998</v>
+      </c>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4">
+        <f t="shared" si="5"/>
+        <v>58.164087666666973</v>
+      </c>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3">
+        <f>K42/SUM(K42:K45)</f>
+        <v>0.15285316937789162</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43">
+        <v>2045</v>
+      </c>
+      <c r="C43" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43">
+        <v>60.299173000000003</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43">
+        <v>116.07340139999999</v>
+      </c>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4">
+        <f t="shared" si="5"/>
+        <v>55.774228399999991</v>
+      </c>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3">
+        <f>K43/SUM(K42:K45)</f>
+        <v>0.14657270357963723</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44">
+        <v>2045</v>
+      </c>
+      <c r="C44" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44">
+        <v>97.315895233333293</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44">
+        <v>214.53541633333299</v>
+      </c>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4">
+        <f t="shared" si="5"/>
+        <v>117.2195210999997</v>
+      </c>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3">
+        <f>K44/SUM(K42:K45)</f>
+        <v>0.30804876396886721</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45">
+        <v>2045</v>
+      </c>
+      <c r="C45" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45">
+        <v>188.42416009999999</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45">
+        <v>337.78893756666599</v>
+      </c>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4">
+        <f t="shared" si="5"/>
+        <v>149.364777466666</v>
+      </c>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3">
+        <f>K45/SUM(K42:K45)</f>
+        <v>0.39252536307360403</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46">
+        <v>2050</v>
+      </c>
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46">
+        <v>348.79311866666598</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46">
+        <v>386.37448666666597</v>
+      </c>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4">
+        <f t="shared" si="5"/>
+        <v>37.581367999999998</v>
+      </c>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3">
+        <f>K46/SUM(K46:K49)</f>
+        <v>7.9254516693036001E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47">
+        <v>2050</v>
+      </c>
+      <c r="C47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47">
+        <v>229.705339966666</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47">
+        <v>321.027063133333</v>
+      </c>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4">
+        <f t="shared" si="5"/>
+        <v>91.321723166666999</v>
+      </c>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3">
+        <f>K47/SUM(K46:K49)</f>
+        <v>0.19258636442264218</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48">
+        <v>2050</v>
+      </c>
+      <c r="C48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48">
+        <v>345.10346199999998</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48">
+        <v>518.30884966666599</v>
+      </c>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4">
+        <f t="shared" si="5"/>
+        <v>173.20538766666601</v>
+      </c>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3">
+        <f>K48/SUM(K46:K49)</f>
+        <v>0.36526901543742513</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49">
+        <v>2050</v>
+      </c>
+      <c r="C49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49">
+        <v>576.39836760000003</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49">
+        <v>748.47570893333295</v>
+      </c>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4">
+        <f t="shared" si="5"/>
+        <v>172.07734133333292</v>
+      </c>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3">
+        <f>K49/SUM(K46:K49)</f>
+        <v>0.36289010344689659</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50">
+        <v>2025</v>
+      </c>
+      <c r="C50" t="s">
+        <v>22</v>
+      </c>
+      <c r="I50" s="4">
+        <f>E50-$D50</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="3" t="e">
+        <f>I50/SUM(I50:I53)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51">
+        <v>2025</v>
+      </c>
+      <c r="C51" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="I51" s="4">
+        <f t="shared" ref="I51:I73" si="6">E51-$D51</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="3" t="e">
+        <f>I51/SUM(I50:I53)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52">
+        <v>2025</v>
+      </c>
+      <c r="C52" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="I52" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="3" t="e">
+        <f>I52/SUM(I50:I53)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53">
+        <v>2025</v>
+      </c>
+      <c r="C53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="I53" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="3" t="e">
+        <f>I53/SUM(I50:I53)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54">
+        <v>2030</v>
+      </c>
+      <c r="C54" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="I54" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="4">
+        <f t="shared" ref="J54:J69" si="7">F54-$D54</f>
+        <v>0</v>
+      </c>
+      <c r="K54" s="4">
+        <f t="shared" ref="K54:K73" si="8">G54-$D54</f>
+        <v>0</v>
+      </c>
+      <c r="L54" s="3" t="e">
+        <f>I54/SUM(I54:I57)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M54" s="3" t="e">
+        <f>J54/SUM(J54:J57)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N54" s="3" t="e">
+        <f>K54/SUM(K54:K57)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55">
+        <v>2030</v>
+      </c>
+      <c r="C55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="I55" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="3" t="e">
+        <f>I55/SUM(I54:I57)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M55" s="3" t="e">
+        <f>J55/SUM(J54:J57)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N55" s="3" t="e">
+        <f>K55/SUM(K54:K57)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56">
+        <v>2030</v>
+      </c>
+      <c r="C56" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="I56" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L56" s="3" t="e">
+        <f>I56/SUM(I54:I57)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M56" s="3" t="e">
+        <f>J56/SUM(J54:J57)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N56" s="3" t="e">
+        <f>K56/SUM(K54:K57)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57">
+        <v>2030</v>
+      </c>
+      <c r="C57" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="I57" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L57" s="3" t="e">
+        <f>I57/SUM(I54:I57)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M57" s="3" t="e">
+        <f>J57/SUM(J54:J57)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N57" s="3" t="e">
+        <f>K57/SUM(K54:K57)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58">
+        <v>2035</v>
+      </c>
+      <c r="C58" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="I58" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="e">
+        <f>I58/SUM(I58:I61)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M58" s="3" t="e">
+        <f>J58/SUM(J58:J61)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N58" s="3" t="e">
+        <f>K58/SUM(K58:K61)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59">
+        <v>2035</v>
+      </c>
+      <c r="C59" t="s">
+        <v>23</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="I59" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L59" s="3" t="e">
+        <f>I59/SUM(I58:I61)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M59" s="3" t="e">
+        <f>J59/SUM(J58:J61)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N59" s="3" t="e">
+        <f>K59/SUM(K58:K61)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60">
+        <v>2035</v>
+      </c>
+      <c r="C60" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="I60" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K60" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L60" s="3" t="e">
+        <f>I60/SUM(I58:I61)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M60" s="3" t="e">
+        <f>J60/SUM(J58:J61)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N60" s="3" t="e">
+        <f>K60/SUM(K58:K61)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61">
+        <v>2035</v>
+      </c>
+      <c r="C61" t="s">
+        <v>25</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="I61" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K61" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L61" s="3" t="e">
+        <f>I61/SUM(I58:I61)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M61" s="3" t="e">
+        <f>J61/SUM(J58:J61)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N61" s="3" t="e">
+        <f>K61/SUM(K58:K61)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62">
+        <v>2040</v>
+      </c>
+      <c r="C62" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3" t="e">
+        <f>K62/SUM(K62:K65)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63">
+        <v>2040</v>
+      </c>
+      <c r="C63" t="s">
+        <v>23</v>
+      </c>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3" t="e">
+        <f>K63/SUM(K62:K65)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64">
+        <v>2040</v>
+      </c>
+      <c r="C64" t="s">
+        <v>24</v>
+      </c>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3" t="e">
+        <f>K64/SUM(K62:K65)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65">
+        <v>2040</v>
+      </c>
+      <c r="C65" t="s">
+        <v>25</v>
+      </c>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3" t="e">
+        <f>K65/SUM(K62:K65)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66">
+        <v>2045</v>
+      </c>
+      <c r="C66" t="s">
+        <v>22</v>
+      </c>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3" t="e">
+        <f>K66/SUM(K66:K69)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
+      <c r="A67" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67">
+        <v>2045</v>
+      </c>
+      <c r="C67" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3" t="e">
+        <f>K67/SUM(K66:K69)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68">
+        <v>2045</v>
+      </c>
+      <c r="C68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3" t="e">
+        <f>K68/SUM(K66:K69)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69">
+        <v>2045</v>
+      </c>
+      <c r="C69" t="s">
+        <v>25</v>
+      </c>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3" t="e">
+        <f>K69/SUM(K66:K69)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="A70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70">
+        <v>2050</v>
+      </c>
+      <c r="C70" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3" t="e">
+        <f>K70/SUM(K70:K73)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71">
+        <v>2050</v>
+      </c>
+      <c r="C71" t="s">
+        <v>23</v>
+      </c>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3" t="e">
+        <f>K71/SUM(K70:K73)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
+      <c r="A72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72">
+        <v>2050</v>
+      </c>
+      <c r="C72" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3" t="e">
+        <f>K72/SUM(K70:K73)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
+      <c r="A73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73">
+        <v>2050</v>
+      </c>
+      <c r="C73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3" t="e">
+        <f>K73/SUM(K70:K73)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/data_analysis/procurement.xlsx
+++ b/data/data_analysis/procurement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F459CE0-8CD8-425B-B2A1-6746A1CF1DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73714347-D291-4BBE-8147-B9C03C7D0B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="2" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
   </bookViews>
   <sheets>
     <sheet name="Scaling" sheetId="1" r:id="rId1"/>
@@ -18,49 +18,9 @@
     <sheet name="Marginal Supply" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'45Q'!$B$2:$B$13</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'45Q'!$D$1</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'45Q'!$G$1</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'45Q'!$G$2:$G$13</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">'45Q'!$B$2:$B$13</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">'45Q'!$D$1</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">'45Q'!$D$2:$D$13</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">'45Q'!$G$1</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">'45Q'!$G$2:$G$13</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">'45Q'!$B$2:$B$13</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">'45Q'!$D$1</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">'45Q'!$D$2:$D$13</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'45Q'!$D$2:$D$13</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">'45Q'!$G$1</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">'45Q'!$G$2:$G$13</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">'45Q'!$D$1</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">'45Q'!$D$2:$D$13</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">'45Q'!$G$1</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">'45Q'!$G$2:$G$13</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">'45Q'!$D$1</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">'45Q'!$D$2:$D$13</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">'45Q'!$E$1</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">'45Q'!$E$2:$E$13</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'45Q'!$G$1</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">'45Q'!$F$1</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">'45Q'!$F$2:$F$13</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">'45Q'!$G$1</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">'45Q'!$G$2:$G$13</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">'45Q'!$D$1</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">'45Q'!$D$1:$D$13</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">'45Q'!$D$2:$D$13</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">'45Q'!$E$1</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">'45Q'!$E$2:$E$13</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">'45Q'!$F$1</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'45Q'!$G$2:$G$13</definedName>
-    <definedName name="_xlchart.v1.40" hidden="1">'45Q'!$F$2:$F$13</definedName>
-    <definedName name="_xlchart.v1.41" hidden="1">'45Q'!$G$1</definedName>
-    <definedName name="_xlchart.v1.42" hidden="1">'45Q'!$G$2:$G$13</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'45Q'!$B$1:$B$13</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'45Q'!$B$2:$B$13</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">'45Q'!$D$1</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">'45Q'!$D$1:$D$13</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">'45Q'!$D$2:$D$13</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">'45Q'!$D$2:$D$13</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'45Q'!$G$1</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'45Q'!$G$2:$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1815,10 +1775,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.36</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.42</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1856,7 +1816,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{5F8C8374-44F7-452F-BFFD-4FAF44BD728B}" formatIdx="3">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.41</cx:f>
+              <cx:f>_xlchart.v1.1</cx:f>
               <cx:v>Percent of Procurement Budget Spent on 45Q</cx:v>
             </cx:txData>
           </cx:tx>
@@ -5753,7 +5713,7 @@
         <v>12.337415273333299</v>
       </c>
       <c r="I3" s="4">
-        <f t="shared" ref="I3:I25" si="0">E3-$D3</f>
+        <f t="shared" ref="I3:I13" si="0">E3-$D3</f>
         <v>8.4510986633333989</v>
       </c>
       <c r="J3" s="4"/>
@@ -5862,7 +5822,7 @@
         <v>3.2741396966666407</v>
       </c>
       <c r="J6" s="4">
-        <f t="shared" ref="J2:K17" si="1">F6-$D6</f>
+        <f t="shared" ref="J6:K17" si="1">F6-$D6</f>
         <v>1.3863719833333406</v>
       </c>
       <c r="K6" s="4">
@@ -6673,7 +6633,7 @@
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="I27" s="4">
-        <f t="shared" ref="I27:I49" si="3">E27-$D27</f>
+        <f t="shared" ref="I27:I37" si="3">E27-$D27</f>
         <v>8.4519960066666986</v>
       </c>
       <c r="J27" s="4"/>
@@ -6769,7 +6729,7 @@
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4">
-        <f t="shared" ref="J30:J45" si="4">F30-$D30</f>
+        <f t="shared" ref="J30:J37" si="4">F30-$D30</f>
         <v>1.3077564866666993</v>
       </c>
       <c r="K30" s="4">
@@ -7501,7 +7461,7 @@
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="I51" s="4">
-        <f t="shared" ref="I51:I73" si="6">E51-$D51</f>
+        <f t="shared" ref="I51:I61" si="6">E51-$D51</f>
         <v>0</v>
       </c>
       <c r="J51" s="4"/>
@@ -7586,7 +7546,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="4">
-        <f t="shared" ref="J54:J69" si="7">F54-$D54</f>
+        <f t="shared" ref="J54:J61" si="7">F54-$D54</f>
         <v>0</v>
       </c>
       <c r="K54" s="4">

--- a/data/data_analysis/procurement.xlsx
+++ b/data/data_analysis/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73714347-D291-4BBE-8147-B9C03C7D0B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900AB2ED-63F6-4C3D-B752-BC0BE94C09A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
   </bookViews>
@@ -19,8 +19,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">'45Q'!$D$2:$D$13</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'45Q'!$G$1</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'45Q'!$G$2:$G$13</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'45Q'!$D$6:$D$13</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'45Q'!$G$1</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'45Q'!$G$2:$G$13</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'45Q'!$G$6:$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="33">
   <si>
     <t>Scenario</t>
   </si>
@@ -100,9 +102,6 @@
   </si>
   <si>
     <t>Procurement (Mt)</t>
-  </si>
-  <si>
-    <t>NA</t>
   </si>
   <si>
     <t>Percent of Procurement Budget Spent on 45Q</t>
@@ -1775,10 +1774,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.0</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.2</cx:f>
+        <cx:f>_xlchart.v1.4</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1816,7 +1815,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{5F8C8374-44F7-452F-BFFD-4FAF44BD728B}" formatIdx="3">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:f>_xlchart.v1.2</cx:f>
               <cx:v>Percent of Procurement Budget Spent on 45Q</cx:v>
             </cx:txData>
           </cx:tx>
@@ -5244,7 +5243,7 @@
         <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H1" t="s">
         <v>14</v>
@@ -5521,23 +5520,9 @@
       <c r="D11">
         <v>2030</v>
       </c>
-      <c r="E11" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F11">
-        <v>3300</v>
-      </c>
-      <c r="G11" s="3" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
@@ -5634,13 +5619,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
         <v>26</v>
-      </c>
-      <c r="E1" t="s">
-        <v>27</v>
       </c>
       <c r="F1" t="s">
         <v>13</v>
@@ -5649,22 +5634,22 @@
         <v>8</v>
       </c>
       <c r="I1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>31</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>32</v>
-      </c>
-      <c r="N1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -5675,7 +5660,7 @@
         <v>2025</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I2" s="4">
         <f>E2-$D2</f>
@@ -5698,7 +5683,7 @@
         <v>2025</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" s="4">
         <v>12.302540506666601</v>
@@ -5733,7 +5718,7 @@
         <v>2025</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" s="4">
         <v>0.75969476000000002</v>
@@ -5768,7 +5753,7 @@
         <v>2025</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="4">
         <v>0.17843507</v>
@@ -5803,7 +5788,7 @@
         <v>2030</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" s="4">
         <v>8.65097456666666</v>
@@ -5850,7 +5835,7 @@
         <v>2030</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" s="4">
         <v>15.9532513066666</v>
@@ -5897,7 +5882,7 @@
         <v>2030</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" s="4">
         <v>1.8031504333333299</v>
@@ -5944,7 +5929,7 @@
         <v>2030</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" s="4">
         <v>0.93724469666666599</v>
@@ -5991,7 +5976,7 @@
         <v>2035</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" s="4">
         <v>32.8174128333333</v>
@@ -6038,7 +6023,7 @@
         <v>2035</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" s="4">
         <v>6.3966195333333298</v>
@@ -6085,7 +6070,7 @@
         <v>2035</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="4">
         <v>8.9131753333333297</v>
@@ -6132,7 +6117,7 @@
         <v>2035</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="4">
         <v>8.8559258333333304</v>
@@ -6179,7 +6164,7 @@
         <v>2040</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" s="4">
         <v>59.1438998333333</v>
@@ -6214,7 +6199,7 @@
         <v>2040</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" s="4">
         <v>11.3755561333333</v>
@@ -6249,7 +6234,7 @@
         <v>2040</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" s="4">
         <v>19.689983866666601</v>
@@ -6284,7 +6269,7 @@
         <v>2040</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" s="4">
         <v>27.481140133333302</v>
@@ -6319,7 +6304,7 @@
         <v>2045</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" s="4">
         <v>110.52516749999999</v>
@@ -6354,7 +6339,7 @@
         <v>2045</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" s="4">
         <v>22.4968641333333</v>
@@ -6389,7 +6374,7 @@
         <v>2045</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" s="4">
         <v>33.472099466666599</v>
@@ -6424,7 +6409,7 @@
         <v>2045</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="4">
         <v>76.120413600000006</v>
@@ -6459,7 +6444,7 @@
         <v>2050</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22" s="4">
         <v>206.888348333333</v>
@@ -6494,7 +6479,7 @@
         <v>2050</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D23" s="4">
         <v>49.988974566666599</v>
@@ -6529,7 +6514,7 @@
         <v>2050</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D24" s="4">
         <v>65.061545266666599</v>
@@ -6564,7 +6549,7 @@
         <v>2050</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25" s="4">
         <v>177.878598333333</v>
@@ -6599,7 +6584,7 @@
         <v>2025</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I26" s="4">
         <f>E26-$D26</f>
@@ -6622,7 +6607,7 @@
         <v>2025</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D27">
         <v>12.3018890866666</v>
@@ -6653,7 +6638,7 @@
         <v>2025</v>
       </c>
       <c r="C28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D28">
         <v>0.76009263000000005</v>
@@ -6684,7 +6669,7 @@
         <v>2025</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D29">
         <v>0.17853032999999999</v>
@@ -6715,7 +6700,7 @@
         <v>2030</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D30">
         <v>10.8468415733333</v>
@@ -6754,7 +6739,7 @@
         <v>2030</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D31">
         <v>19.872583573333301</v>
@@ -6793,7 +6778,7 @@
         <v>2030</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D32">
         <v>2.2453959733333302</v>
@@ -6832,7 +6817,7 @@
         <v>2030</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D33">
         <v>1.25755285333333</v>
@@ -6871,7 +6856,7 @@
         <v>2035</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D34">
         <v>50.522071966666601</v>
@@ -6918,7 +6903,7 @@
         <v>2035</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D35">
         <v>10.102477916666601</v>
@@ -6965,7 +6950,7 @@
         <v>2035</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D36">
         <v>14.10962531</v>
@@ -7012,7 +6997,7 @@
         <v>2035</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D37">
         <v>13.9483635866666</v>
@@ -7059,7 +7044,7 @@
         <v>2040</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D38">
         <v>111.1385561</v>
@@ -7090,7 +7075,7 @@
         <v>2040</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D39">
         <v>23.141853900000001</v>
@@ -7121,7 +7106,7 @@
         <v>2040</v>
       </c>
       <c r="C40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D40">
         <v>39.859757299999998</v>
@@ -7152,7 +7137,7 @@
         <v>2040</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D41">
         <v>53.642280266666603</v>
@@ -7183,7 +7168,7 @@
         <v>2045</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D42">
         <v>238.62236933333301</v>
@@ -7214,7 +7199,7 @@
         <v>2045</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D43">
         <v>60.299173000000003</v>
@@ -7245,7 +7230,7 @@
         <v>2045</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D44">
         <v>97.315895233333293</v>
@@ -7276,7 +7261,7 @@
         <v>2045</v>
       </c>
       <c r="C45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D45">
         <v>188.42416009999999</v>
@@ -7307,7 +7292,7 @@
         <v>2050</v>
       </c>
       <c r="C46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D46">
         <v>348.79311866666598</v>
@@ -7338,7 +7323,7 @@
         <v>2050</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D47">
         <v>229.705339966666</v>
@@ -7369,7 +7354,7 @@
         <v>2050</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D48">
         <v>345.10346199999998</v>
@@ -7400,7 +7385,7 @@
         <v>2050</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D49">
         <v>576.39836760000003</v>
@@ -7431,7 +7416,7 @@
         <v>2025</v>
       </c>
       <c r="C50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I50" s="4">
         <f>E50-$D50</f>
@@ -7454,7 +7439,7 @@
         <v>2025</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -7481,7 +7466,7 @@
         <v>2025</v>
       </c>
       <c r="C52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -7508,7 +7493,7 @@
         <v>2025</v>
       </c>
       <c r="C53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -7535,7 +7520,7 @@
         <v>2030</v>
       </c>
       <c r="C54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -7574,7 +7559,7 @@
         <v>2030</v>
       </c>
       <c r="C55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -7613,7 +7598,7 @@
         <v>2030</v>
       </c>
       <c r="C56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -7652,7 +7637,7 @@
         <v>2030</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -7691,7 +7676,7 @@
         <v>2035</v>
       </c>
       <c r="C58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -7730,7 +7715,7 @@
         <v>2035</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -7769,7 +7754,7 @@
         <v>2035</v>
       </c>
       <c r="C60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -7808,7 +7793,7 @@
         <v>2035</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -7847,7 +7832,7 @@
         <v>2040</v>
       </c>
       <c r="C62" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -7874,7 +7859,7 @@
         <v>2040</v>
       </c>
       <c r="C63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -7901,7 +7886,7 @@
         <v>2040</v>
       </c>
       <c r="C64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -7928,7 +7913,7 @@
         <v>2040</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -7955,7 +7940,7 @@
         <v>2045</v>
       </c>
       <c r="C66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -7982,7 +7967,7 @@
         <v>2045</v>
       </c>
       <c r="C67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
@@ -8009,7 +7994,7 @@
         <v>2045</v>
       </c>
       <c r="C68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -8036,7 +8021,7 @@
         <v>2045</v>
       </c>
       <c r="C69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -8063,7 +8048,7 @@
         <v>2050</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -8090,7 +8075,7 @@
         <v>2050</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -8117,7 +8102,7 @@
         <v>2050</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -8144,7 +8129,7 @@
         <v>2050</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>

--- a/data/data_analysis/procurement.xlsx
+++ b/data/data_analysis/procurement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900AB2ED-63F6-4C3D-B752-BC0BE94C09A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464EF09C-85D1-4F3F-A239-B0215EDB7C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
   </bookViews>
   <sheets>
     <sheet name="Scaling" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="33">
   <si>
     <t>Scenario</t>
   </si>
@@ -193,10 +193,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -292,10 +291,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Scaling!$F$2:$F$28</c:f>
+              <c:f>Scaling!$F$2:$F$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>22.652770490000002</c:v>
                 </c:pt>
@@ -306,59 +305,74 @@
                   <c:v>72.101540779999993</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13.5</c:v>
+                  <c:v>95.2150848</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>95.2150848</c:v>
+                  <c:v>214.75016840000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>214.75016840000001</c:v>
+                  <c:v>360.96804700000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>360.96804700000001</c:v>
+                  <c:v>623.27188550000005</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>623.27188550000005</c:v>
+                  <c:v>974.18677479999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>974.18677479999997</c:v>
+                  <c:v>22.652770490000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>22.652770490000002</c:v>
+                  <c:v>103.695629</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>45.75593121</c:v>
+                  <c:v>102.04666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>103.695629</c:v>
+                  <c:v>246.34425669999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13.5</c:v>
+                  <c:v>470.9906421</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>102.04666</c:v>
+                  <c:v>965.18417420000003</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>246.34425669999999</c:v>
+                  <c:v>1974.1867749999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>470.9906421</c:v>
+                  <c:v>22.64976914</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>965.18417420000003</c:v>
+                  <c:v>30.407393859999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1974.1867749999999</c:v>
+                  <c:v>44.248195699999997</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>82.317910130000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>180.40034800000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>275.22336999999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>461.18036599999999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>691.29305280000005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Scaling!$G$2:$G$28</c:f>
+              <c:f>Scaling!$G$2:$G$24</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>5.9999999999999995E-4</c:v>
                 </c:pt>
@@ -368,47 +382,65 @@
                 <c:pt idx="2">
                   <c:v>-2.1999999999999999E-2</c:v>
                 </c:pt>
-                <c:pt idx="3" formatCode="0%">
+                <c:pt idx="3">
+                  <c:v>7.7999999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.7300000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.19E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.4799999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.9999999999999995E-4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.3499999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.3700000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.11899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.16400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.108</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.7999999999999996E-3</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.7300000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4.19E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.4799999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-2.3E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>5.9999999999999995E-4</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-2.4E-2</c:v>
-                </c:pt>
-                <c:pt idx="12" formatCode="0%">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>8.3499999999999998E-3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4.3700000000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.11899999999999999</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.16400000000000001</c:v>
+                  <c:v>-7.4999999999999997E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.108</c:v>
+                  <c:v>0.17300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-2.15E-3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.4999999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.0599999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.1055</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -787,10 +819,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Scaling!$H$2:$H$28</c:f>
+              <c:f>Scaling!$H$2:$H$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>13.5</c:v>
                 </c:pt>
@@ -801,25 +833,25 @@
                   <c:v>57.251683640000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>27.80103828</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>57.251683640000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>117.9004628</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>242.7966874</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>13.5</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>27.80103828</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>57.251683640000003</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>117.9004628</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>242.7966874</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>500</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>13.5</c:v>
+                  <c:v>88.845771859999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>34.63261353</c:v>
@@ -828,48 +860,36 @@
                   <c:v>88.845771859999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>227.9230579</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>584.70897609999997</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>13.5</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>34.63261353</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>88.845771859999999</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>227.9230579</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>584.70897609999997</c:v>
+                  <c:v>20.149627169999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1500</c:v>
+                  <c:v>30.074627790000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>13.5</c:v>
+                  <c:v>20.149627169999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>20.149627169999999</c:v>
+                  <c:v>30.074627790000001</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>30.074627790000001</c:v>
+                  <c:v>44.888336090000003</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>13.5</c:v>
+                  <c:v>66.998758269999996</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>20.149627169999999</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>30.074627790000001</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>44.888336090000003</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>66.998758269999996</c:v>
-                </c:pt>
-                <c:pt idx="26">
                   <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
@@ -877,10 +897,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Scaling!$G$2:$G$28</c:f>
+              <c:f>Scaling!$G$2:$G$24</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>5.9999999999999995E-4</c:v>
                 </c:pt>
@@ -890,47 +910,65 @@
                 <c:pt idx="2">
                   <c:v>-2.1999999999999999E-2</c:v>
                 </c:pt>
-                <c:pt idx="3" formatCode="0%">
+                <c:pt idx="3">
+                  <c:v>7.7999999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.7300000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.19E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.4799999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.9999999999999995E-4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.3499999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.3700000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.11899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.16400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.108</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.7999999999999996E-3</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.7300000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4.19E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.4799999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-2.3E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>5.9999999999999995E-4</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-2.4E-2</c:v>
-                </c:pt>
-                <c:pt idx="12" formatCode="0%">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>8.3499999999999998E-3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4.3700000000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.11899999999999999</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.16400000000000001</c:v>
+                  <c:v>-7.4999999999999997E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.108</c:v>
+                  <c:v>0.17300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-2.15E-3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.4999999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.0599999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.1055</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1314,10 +1352,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Scaling!$E$2:$E$28</c:f>
+              <c:f>Scaling!$E$2:$E$24</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0.40404640545139786</c:v>
                 </c:pt>
@@ -1328,86 +1366,74 @@
                   <c:v>0.20595755623739934</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.7080185525392716</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.7080185525392716</c:v>
+                  <c:v>0.73340331201342146</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.73340331201342146</c:v>
+                  <c:v>0.67337701001551531</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.67337701001551531</c:v>
+                  <c:v>0.61044819596631716</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.61044819596631716</c:v>
+                  <c:v>0.48675139825969232</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.48675139825969232</c:v>
+                  <c:v>0.40404640545139786</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.40404640545139786</c:v>
+                  <c:v>0.14320620148801064</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.24310111030084311</c:v>
+                  <c:v>0.66061982302997468</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.14320620148801064</c:v>
+                  <c:v>0.63934303543273963</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>0.51607731125237999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.66061982302997468</c:v>
+                  <c:v>0.39419958208013484</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.63934303543273963</c:v>
+                  <c:v>0.24019347156248674</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.51607731125237999</c:v>
+                  <c:v>0.40396743487514414</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.39419958208013484</c:v>
+                  <c:v>0.33734448723978877</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.24019347156248674</c:v>
+                  <c:v>0.32031968051524407</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>0.75522183279217314</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>0.83328952453018557</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>0.83690216390417715</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>0.85472330738815538</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0</c:v>
+                  <c:v>0.85534354844886418</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Scaling!$G$2:$G$28</c:f>
+              <c:f>Scaling!$G$2:$G$24</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>5.9999999999999995E-4</c:v>
                 </c:pt>
@@ -1417,47 +1443,65 @@
                 <c:pt idx="2">
                   <c:v>-2.1999999999999999E-2</c:v>
                 </c:pt>
-                <c:pt idx="3" formatCode="0%">
+                <c:pt idx="3">
+                  <c:v>7.7999999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.7300000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.19E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.4799999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.9999999999999995E-4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.3499999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.3700000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.11899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.16400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.108</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.7999999999999996E-3</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.7300000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4.19E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.4799999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-2.3E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>5.9999999999999995E-4</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-2.4E-2</c:v>
-                </c:pt>
-                <c:pt idx="12" formatCode="0%">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>8.3499999999999998E-3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4.3700000000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.11899999999999999</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.16400000000000001</c:v>
+                  <c:v>-7.4999999999999997E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.108</c:v>
+                  <c:v>0.17300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-2.15E-3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.4999999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.0599999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.1055</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1774,10 +1818,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.1</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.4</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -4069,13 +4113,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>33337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>109537</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4105,13 +4149,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>33337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>109537</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4141,13 +4185,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4578,7 +4622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B537AA0D-F5C4-4357-8465-DF25FED59988}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -4621,7 +4665,7 @@
       <c r="C2">
         <v>2025</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <f>(F2-H2)/F2</f>
         <v>0.40404640545139786</v>
       </c>
@@ -4645,8 +4689,8 @@
       <c r="C3">
         <v>2030</v>
       </c>
-      <c r="E3" s="3">
-        <f t="shared" ref="E3:E28" si="0">(F3-H3)/F3</f>
+      <c r="E3" s="2">
+        <f t="shared" ref="E3:E24" si="0">(F3-H3)/F3</f>
         <v>0.2857675459404056</v>
       </c>
       <c r="F3">
@@ -4669,7 +4713,7 @@
       <c r="C4">
         <v>2035</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <f t="shared" si="0"/>
         <v>0.20595755623739934</v>
       </c>
@@ -4691,20 +4735,20 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>2025</v>
-      </c>
-      <c r="E5" s="3">
+        <v>2030</v>
+      </c>
+      <c r="E5" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7080185525392716</v>
       </c>
       <c r="F5">
-        <v>13.5</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
+        <v>95.2150848</v>
+      </c>
+      <c r="G5" s="1">
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="H5">
-        <v>13.5</v>
+        <v>27.80103828</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4715,20 +4759,20 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>2030</v>
-      </c>
-      <c r="E6" s="3">
+        <v>2035</v>
+      </c>
+      <c r="E6" s="2">
         <f t="shared" si="0"/>
-        <v>0.7080185525392716</v>
+        <v>0.73340331201342146</v>
       </c>
       <c r="F6">
-        <v>95.2150848</v>
+        <v>214.75016840000001</v>
       </c>
       <c r="G6" s="1">
-        <v>7.7999999999999996E-3</v>
+        <v>2.7300000000000001E-2</v>
       </c>
       <c r="H6">
-        <v>27.80103828</v>
+        <v>57.251683640000003</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4739,20 +4783,20 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>2035</v>
-      </c>
-      <c r="E7" s="3">
+        <v>2040</v>
+      </c>
+      <c r="E7" s="2">
         <f t="shared" si="0"/>
-        <v>0.73340331201342146</v>
+        <v>0.67337701001551531</v>
       </c>
       <c r="F7">
-        <v>214.75016840000001</v>
+        <v>360.96804700000001</v>
       </c>
       <c r="G7" s="1">
-        <v>2.7300000000000001E-2</v>
+        <v>4.19E-2</v>
       </c>
       <c r="H7">
-        <v>57.251683640000003</v>
+        <v>117.9004628</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4763,20 +4807,20 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>2040</v>
-      </c>
-      <c r="E8" s="3">
+        <v>2045</v>
+      </c>
+      <c r="E8" s="2">
         <f t="shared" si="0"/>
-        <v>0.67337701001551531</v>
+        <v>0.61044819596631716</v>
       </c>
       <c r="F8">
-        <v>360.96804700000001</v>
+        <v>623.27188550000005</v>
       </c>
       <c r="G8" s="1">
-        <v>4.19E-2</v>
+        <v>2.4799999999999999E-2</v>
       </c>
       <c r="H8">
-        <v>117.9004628</v>
+        <v>242.7966874</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4787,44 +4831,44 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>2045</v>
-      </c>
-      <c r="E9" s="3">
+        <v>2050</v>
+      </c>
+      <c r="E9" s="2">
         <f t="shared" si="0"/>
-        <v>0.61044819596631716</v>
+        <v>0.48675139825969232</v>
       </c>
       <c r="F9">
-        <v>623.27188550000005</v>
+        <v>974.18677479999997</v>
       </c>
       <c r="G9" s="1">
-        <v>2.4799999999999999E-2</v>
+        <v>-2.3E-2</v>
       </c>
       <c r="H9">
-        <v>242.7966874</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>2050</v>
-      </c>
-      <c r="E10" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E10" s="2">
         <f t="shared" si="0"/>
-        <v>0.48675139825969232</v>
+        <v>0.40404640545139786</v>
       </c>
       <c r="F10">
-        <v>974.18677479999997</v>
+        <v>22.652770490000002</v>
       </c>
       <c r="G10" s="1">
-        <v>-2.3E-2</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="H10">
-        <v>500</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -4835,25 +4879,25 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>2025</v>
-      </c>
-      <c r="E11" s="3">
+        <v>2035</v>
+      </c>
+      <c r="E11" s="2">
         <f t="shared" si="0"/>
-        <v>0.40404640545139786</v>
+        <v>0.14320620148801064</v>
       </c>
       <c r="F11">
-        <v>22.652770490000002</v>
+        <v>103.695629</v>
       </c>
       <c r="G11" s="1">
-        <v>5.9999999999999995E-4</v>
+        <v>-2.4E-2</v>
       </c>
       <c r="H11">
-        <v>13.5</v>
+        <v>88.845771859999999</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -4861,12 +4905,15 @@
       <c r="C12">
         <v>2030</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <f t="shared" si="0"/>
-        <v>0.24310111030084311</v>
+        <v>0.66061982302997468</v>
       </c>
       <c r="F12">
-        <v>45.75593121</v>
+        <v>102.04666</v>
+      </c>
+      <c r="G12" s="1">
+        <v>8.3499999999999998E-3</v>
       </c>
       <c r="H12">
         <v>34.63261353</v>
@@ -4874,7 +4921,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
@@ -4882,15 +4929,15 @@
       <c r="C13">
         <v>2035</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>0.14320620148801064</v>
+        <v>0.63934303543273963</v>
       </c>
       <c r="F13">
-        <v>103.695629</v>
+        <v>246.34425669999999</v>
       </c>
       <c r="G13" s="1">
-        <v>-2.4E-2</v>
+        <v>4.3700000000000003E-2</v>
       </c>
       <c r="H13">
         <v>88.845771859999999</v>
@@ -4904,20 +4951,20 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>2025</v>
-      </c>
-      <c r="E14" s="3">
+        <v>2040</v>
+      </c>
+      <c r="E14" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.51607731125237999</v>
       </c>
       <c r="F14">
-        <v>13.5</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
+        <v>470.9906421</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.11899999999999999</v>
       </c>
       <c r="H14">
-        <v>13.5</v>
+        <v>227.9230579</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4928,20 +4975,20 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>2030</v>
-      </c>
-      <c r="E15" s="3">
+        <v>2045</v>
+      </c>
+      <c r="E15" s="2">
         <f t="shared" si="0"/>
-        <v>0.66061982302997468</v>
+        <v>0.39419958208013484</v>
       </c>
       <c r="F15">
-        <v>102.04666</v>
+        <v>965.18417420000003</v>
       </c>
       <c r="G15" s="1">
-        <v>8.3499999999999998E-3</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="H15">
-        <v>34.63261353</v>
+        <v>584.70897609999997</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -4952,146 +4999,164 @@
         <v>9</v>
       </c>
       <c r="C16">
-        <v>2035</v>
-      </c>
-      <c r="E16" s="3">
+        <v>2050</v>
+      </c>
+      <c r="E16" s="2">
         <f t="shared" si="0"/>
-        <v>0.63934303543273963</v>
+        <v>0.24019347156248674</v>
       </c>
       <c r="F16">
-        <v>246.34425669999999</v>
+        <v>1974.1867749999999</v>
       </c>
       <c r="G16" s="1">
-        <v>4.3700000000000003E-2</v>
+        <v>0.108</v>
       </c>
       <c r="H16">
-        <v>88.845771859999999</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C17">
-        <v>2040</v>
-      </c>
-      <c r="E17" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E17" s="2">
         <f t="shared" si="0"/>
-        <v>0.51607731125237999</v>
+        <v>0.40396743487514414</v>
       </c>
       <c r="F17">
-        <v>470.9906421</v>
+        <v>22.64976914</v>
       </c>
       <c r="G17" s="1">
-        <v>0.11899999999999999</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>227.9230579</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C18">
-        <v>2045</v>
-      </c>
-      <c r="E18" s="3">
+        <v>2030</v>
+      </c>
+      <c r="E18" s="2">
         <f t="shared" si="0"/>
-        <v>0.39419958208013484</v>
+        <v>0.33734448723978877</v>
       </c>
       <c r="F18">
-        <v>965.18417420000003</v>
+        <v>30.407393859999999</v>
       </c>
       <c r="G18" s="1">
-        <v>0.16400000000000001</v>
+        <v>-7.4999999999999997E-3</v>
       </c>
       <c r="H18">
-        <v>584.70897609999997</v>
+        <v>20.149627169999999</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C19">
-        <v>2050</v>
-      </c>
-      <c r="E19" s="3">
+        <v>2035</v>
+      </c>
+      <c r="E19" s="2">
         <f t="shared" si="0"/>
-        <v>0.24019347156248674</v>
+        <v>0.32031968051524407</v>
       </c>
       <c r="F19">
-        <v>1974.1867749999999</v>
+        <v>44.248195699999997</v>
       </c>
       <c r="G19" s="1">
-        <v>0.108</v>
+        <v>0.17300000000000001</v>
       </c>
       <c r="H19">
-        <v>1500</v>
+        <v>30.074627790000001</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
       </c>
       <c r="C20">
-        <v>2025</v>
-      </c>
-      <c r="E20" s="3" t="e">
+        <v>2030</v>
+      </c>
+      <c r="E20" s="2">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0.75522183279217314</v>
+      </c>
+      <c r="F20">
+        <v>82.317910130000001</v>
+      </c>
+      <c r="G20" s="1">
+        <v>-2.15E-3</v>
       </c>
       <c r="H20">
-        <v>13.5</v>
+        <v>20.149627169999999</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
       </c>
       <c r="C21">
-        <v>2030</v>
-      </c>
-      <c r="E21" s="3" t="e">
+        <v>2035</v>
+      </c>
+      <c r="E21" s="2">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0.83328952453018557</v>
+      </c>
+      <c r="F21">
+        <v>180.40034800000001</v>
+      </c>
+      <c r="G21" s="1">
+        <v>7.8E-2</v>
       </c>
       <c r="H21">
-        <v>20.149627169999999</v>
+        <v>30.074627790000001</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
         <v>11</v>
       </c>
       <c r="C22">
-        <v>2035</v>
-      </c>
-      <c r="E22" s="3" t="e">
+        <v>2040</v>
+      </c>
+      <c r="E22" s="2">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0.83690216390417715</v>
+      </c>
+      <c r="F22">
+        <v>275.22336999999999</v>
+      </c>
+      <c r="G22" s="1">
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="H22">
-        <v>30.074627790000001</v>
+        <v>44.888336090000003</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -5102,14 +5167,20 @@
         <v>11</v>
       </c>
       <c r="C23">
-        <v>2025</v>
-      </c>
-      <c r="E23" s="3" t="e">
+        <v>2045</v>
+      </c>
+      <c r="E23" s="2">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0.85472330738815538</v>
+      </c>
+      <c r="F23">
+        <v>461.18036599999999</v>
+      </c>
+      <c r="G23" s="1">
+        <v>5.0599999999999999E-2</v>
       </c>
       <c r="H23">
-        <v>13.5</v>
+        <v>66.998758269999996</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -5120,85 +5191,19 @@
         <v>11</v>
       </c>
       <c r="C24">
-        <v>2030</v>
-      </c>
-      <c r="E24" s="3" t="e">
+        <v>2050</v>
+      </c>
+      <c r="E24" s="2">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0.85534354844886418</v>
+      </c>
+      <c r="F24">
+        <v>691.29305280000005</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.1055</v>
       </c>
       <c r="H24">
-        <v>20.149627169999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25">
-        <v>2035</v>
-      </c>
-      <c r="E25" s="3" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H25">
-        <v>30.074627790000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26">
-        <v>2040</v>
-      </c>
-      <c r="E26" s="3" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H26">
-        <v>44.888336090000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27">
-        <v>2045</v>
-      </c>
-      <c r="E27" s="3" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H27">
-        <v>66.998758269999996</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28">
-        <v>2050</v>
-      </c>
-      <c r="E28" s="3" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H28">
         <v>100</v>
       </c>
     </row>
@@ -5259,22 +5264,28 @@
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>9.1497691446116427</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2">
-        <f>H2-I2</f>
-        <v>0</v>
+        <f t="shared" ref="E2:E13" si="0">H2-I2</f>
+        <v>1519.92382194522</v>
       </c>
       <c r="F2">
         <v>3300</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <f>E2/F2</f>
-        <v>0</v>
+        <v>0.46058297634703638</v>
+      </c>
+      <c r="H2">
+        <v>3736.5136659285899</v>
+      </c>
+      <c r="I2">
+        <v>2216.58984398337</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -5284,22 +5295,28 @@
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>10.257766689126317</v>
       </c>
       <c r="D3">
         <v>2030</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E13" si="0">H3-I3</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1626.1149472671095</v>
       </c>
       <c r="F3">
         <v>3300</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <f t="shared" ref="G3:G13" si="1">E3/F3</f>
-        <v>0</v>
+        <v>0.49276210523245745</v>
+      </c>
+      <c r="H3">
+        <v>4814.1169809663397</v>
+      </c>
+      <c r="I3">
+        <v>3188.0020336992302</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -5309,7 +5326,7 @@
       <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>67.381687905293646</v>
       </c>
       <c r="D4">
@@ -5317,14 +5334,20 @@
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9886.2493241159682</v>
       </c>
       <c r="F4">
         <v>20000</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.49431246620579838</v>
+      </c>
+      <c r="H4">
+        <v>13074.251357815199</v>
+      </c>
+      <c r="I4">
+        <v>3188.0020336992302</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -5334,7 +5357,7 @@
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>5</v>
       </c>
       <c r="D5">
@@ -5342,14 +5365,20 @@
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>793.51772730403991</v>
       </c>
       <c r="F5">
         <v>1608</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.49348117369654221</v>
+      </c>
+      <c r="H5">
+        <v>3981.5197610032701</v>
+      </c>
+      <c r="I5">
+        <v>3188.0020336992302</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5359,7 +5388,7 @@
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>9.1527704871198079</v>
       </c>
       <c r="D6">
@@ -5372,14 +5401,14 @@
       <c r="F6">
         <v>3300</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <f t="shared" si="1"/>
         <v>0.46120303030303023</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>3302.97</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="4">
         <v>1781</v>
       </c>
     </row>
@@ -5390,7 +5419,7 @@
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>11.123317675046577</v>
       </c>
       <c r="D7">
@@ -5403,14 +5432,14 @@
       <c r="F7">
         <v>3300</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <f t="shared" si="1"/>
         <v>0.36212121212121212</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>3330</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="4">
         <v>2135</v>
       </c>
     </row>
@@ -5421,7 +5450,7 @@
       <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>67.381687905293646</v>
       </c>
       <c r="D8">
@@ -5434,14 +5463,14 @@
       <c r="F8">
         <v>20000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <f t="shared" si="1"/>
         <v>0.35675000000000001</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>20155</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="4">
         <v>13020</v>
       </c>
     </row>
@@ -5452,7 +5481,7 @@
       <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>5</v>
       </c>
       <c r="D9">
@@ -5465,14 +5494,14 @@
       <c r="F9">
         <v>1484</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <f t="shared" si="1"/>
         <v>0.37008086253369277</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>1480</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="4">
         <v>930.8</v>
       </c>
     </row>
@@ -5483,7 +5512,7 @@
       <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>11.123317675046577</v>
       </c>
       <c r="D10">
@@ -5496,14 +5525,14 @@
       <c r="F10">
         <v>3300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <f t="shared" si="1"/>
         <v>0.46101818181818172</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>3302.74</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="4">
         <v>1781.38</v>
       </c>
     </row>
@@ -5514,15 +5543,15 @@
       <c r="B11" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>14.849857137390348</v>
       </c>
       <c r="D11">
         <v>2030</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
@@ -5531,7 +5560,7 @@
       <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>67.41404651543381</v>
       </c>
       <c r="D12">
@@ -5544,14 +5573,14 @@
       <c r="F12">
         <v>20000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <f t="shared" si="1"/>
         <v>0.35863100000000003</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>20167</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="4">
         <v>12994.38</v>
       </c>
     </row>
@@ -5562,7 +5591,7 @@
       <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>5</v>
       </c>
       <c r="D13">
@@ -5575,14 +5604,14 @@
       <c r="F13">
         <v>1483</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <f t="shared" si="1"/>
         <v>0.37772083614295338</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>1502.36</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="4">
         <v>942.2</v>
       </c>
     </row>
@@ -5662,18 +5691,18 @@
       <c r="C2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="3">
         <f>E2-$D2</f>
         <v>0</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="3">
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="2">
         <f>I2/SUM(I2:I5)</f>
         <v>0</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
@@ -5685,30 +5714,30 @@
       <c r="C3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>12.302540506666601</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>20.75363917</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>12.38344833</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="3">
         <v>12.337415273333299</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="3">
         <f t="shared" ref="I3:I13" si="0">E3-$D3</f>
         <v>8.4510986633333989</v>
       </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="3">
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="2">
         <f>I3/SUM(I2:I5)</f>
         <v>0.91515732423128149</v>
       </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
@@ -5720,30 +5749,30 @@
       <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>0.75969476000000002</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>1.26107314666666</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>0.74495450333333302</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>0.74290502000000003</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="3">
         <f t="shared" si="0"/>
         <v>0.50137838666666001</v>
       </c>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="3">
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="2">
         <f>I4/SUM(I2:I5)</f>
         <v>5.4293544667750375E-2</v>
       </c>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
@@ -5755,30 +5784,30 @@
       <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>0.17843507</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>0.46054363666666598</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>0.174611396666666</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="3">
         <v>0.173851956666666</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="3">
         <f t="shared" si="0"/>
         <v>0.28210856666666595</v>
       </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="3">
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="2">
         <f>I5/SUM(I2:I5)</f>
         <v>3.0549131100968078E-2</v>
       </c>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
@@ -5790,39 +5819,39 @@
       <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>8.65097456666666</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>11.925114263333301</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>10.037346550000001</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>29.0249384333333</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="3">
         <f t="shared" si="0"/>
         <v>3.2741396966666407</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="3">
         <f t="shared" ref="J6:K17" si="1">F6-$D6</f>
         <v>1.3863719833333406</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="3">
         <f t="shared" si="1"/>
         <v>20.373963866666642</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <f>I6/SUM(I6:I9)</f>
         <v>0.29026154892397193</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="2">
         <f>J6/SUM(J6:J9)</f>
         <v>0.27495341571805787</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="2">
         <f>K6/SUM(K6:K9)</f>
         <v>0.30065410025493072</v>
       </c>
@@ -5837,39 +5866,39 @@
       <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>15.9532513066666</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>22.5884521133333</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>19.007243493333299</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="3">
         <v>55.595604350000002</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="3">
         <f t="shared" si="0"/>
         <v>6.6352008066667008</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="3">
         <f t="shared" si="1"/>
         <v>3.053992186666699</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="3">
         <f t="shared" si="1"/>
         <v>39.642353043333401</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <f>I7/SUM(I6:I9)</f>
         <v>0.58822892179140773</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="2">
         <f>J7/SUM(J6:J9)</f>
         <v>0.60568562650935354</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7" s="2">
         <f>K7/SUM(K6:K9)</f>
         <v>0.58499347815824465</v>
       </c>
@@ -5884,39 +5913,39 @@
       <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>1.8031504333333299</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>2.57378616</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
         <v>2.1532217299999998</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>6.3818963266666602</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="3">
         <f t="shared" si="0"/>
         <v>0.77063572666667013</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="3">
         <f t="shared" si="1"/>
         <v>0.35007129666666992</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="3">
         <f t="shared" si="1"/>
         <v>4.5787458933333305</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <f>I8/SUM(I6:I9)</f>
         <v>6.8318990758442624E-2</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="2">
         <f>J8/SUM(J6:J9)</f>
         <v>6.9428190933231826E-2</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="2">
         <f>K8/SUM(K6:K9)</f>
         <v>6.7567545317401126E-2</v>
       </c>
@@ -5931,39 +5960,39 @@
       <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>0.93724469666666599</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>1.53723203333333</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="3">
         <v>1.1890160333333299</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="3">
         <v>4.1076434300000004</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="3">
         <f t="shared" si="0"/>
         <v>0.59998733666666404</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="3">
         <f t="shared" si="1"/>
         <v>0.25177133666666396</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="3">
         <f t="shared" si="1"/>
         <v>3.1703987333333346</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <f>I9/SUM(I6:I9)</f>
         <v>5.3190538526177646E-2</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="2">
         <f>J9/SUM(J6:J9)</f>
         <v>4.993276683935681E-2</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="2">
         <f>K9/SUM(K6:K9)</f>
         <v>4.6784876269423577E-2</v>
       </c>
@@ -5978,39 +6007,39 @@
       <c r="C10" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>32.8174128333333</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>40.421700000000001</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="3">
         <v>37.7868285666666</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="3">
         <v>114.596670466666</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="3">
         <f t="shared" si="0"/>
         <v>7.6042871666667011</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="3">
         <f t="shared" si="1"/>
         <v>4.9694157333332996</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="3">
         <f t="shared" si="1"/>
         <v>81.779257633332691</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="2">
         <f>I10/SUM(I10:I13)</f>
         <v>0.51139464221983688</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="2">
         <f>J10/SUM(J10:J13)</f>
         <v>0.49509882031009567</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="2">
         <f>K10/SUM(K10:K13)</f>
         <v>0.51852648076029639</v>
       </c>
@@ -6025,39 +6054,39 @@
       <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>6.3966195333333298</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>8.06076223333333</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>7.4923460333333303</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="3">
         <v>26.1684194933333</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="3">
         <f t="shared" si="0"/>
         <v>1.6641427000000002</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="3">
         <f t="shared" si="1"/>
         <v>1.0957265000000005</v>
       </c>
-      <c r="K11" s="4">
+      <c r="K11" s="3">
         <f t="shared" si="1"/>
         <v>19.771799959999971</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="2">
         <f>I11/SUM(I10:I13)</f>
         <v>0.11191498190648941</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="2">
         <f>J11/SUM(J10:J13)</f>
         <v>0.10916633396027549</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="2">
         <f>K11/SUM(K10:K13)</f>
         <v>0.12536433012784678</v>
       </c>
@@ -6072,39 +6101,39 @@
       <c r="C12" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>8.9131753333333297</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>11.88907687</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <v>11.058108819999999</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="3">
         <v>38.070494366666601</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="3">
         <f t="shared" si="0"/>
         <v>2.9759015366666706</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="3">
         <f t="shared" si="1"/>
         <v>2.1449334866666696</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="3">
         <f t="shared" si="1"/>
         <v>29.157319033333273</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="2">
         <f>I12/SUM(I10:I13)</f>
         <v>0.20013185565849878</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="2">
         <f>J12/SUM(J10:J13)</f>
         <v>0.21369796689961559</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="2">
         <f>K12/SUM(K10:K13)</f>
         <v>0.1848737988616464</v>
       </c>
@@ -6119,39 +6148,39 @@
       <c r="C13" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>8.8559258333333304</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>11.481298839999999</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="3">
         <v>10.683070016666599</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="3">
         <v>35.862267099999997</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="3">
         <f t="shared" si="0"/>
         <v>2.6253730066666687</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="3">
         <f t="shared" si="1"/>
         <v>1.8271441833332691</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K13" s="3">
         <f t="shared" si="1"/>
         <v>27.006341266666666</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="2">
         <f>I13/SUM(I10:I13)</f>
         <v>0.17655852021517499</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="2">
         <f>J13/SUM(J10:J13)</f>
         <v>0.18203687883001313</v>
       </c>
-      <c r="N13" s="3">
+      <c r="N13" s="2">
         <f>K13/SUM(K10:K13)</f>
         <v>0.17123539025021053</v>
       </c>
@@ -6166,27 +6195,27 @@
       <c r="C14" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>59.1438998333333</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="3">
         <v>56.976563966666603</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="3">
         <v>56.951071833333302</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="3">
         <v>154.085919166666</v>
       </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4">
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3">
         <f t="shared" si="1"/>
         <v>94.942019333332695</v>
       </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3">
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2">
         <f>K14/SUM(K14:K17)</f>
         <v>0.39032213669832749</v>
       </c>
@@ -6201,27 +6230,27 @@
       <c r="C15" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="3">
         <v>11.3755561333333</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="3">
         <v>11.1483247333333</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="3">
         <v>11.153745166666599</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="3">
         <v>39.758809566666599</v>
       </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4">
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3">
         <f t="shared" si="1"/>
         <v>28.383253433333302</v>
       </c>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3">
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2">
         <f>K15/SUM(K14:K17)</f>
         <v>0.1166881872151129</v>
       </c>
@@ -6236,27 +6265,27 @@
       <c r="C16" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="3">
         <v>19.689983866666601</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="3">
         <v>21.142851033333301</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="3">
         <v>21.151816766666599</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="3">
         <v>74.714340066666594</v>
       </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4">
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3">
         <f t="shared" si="1"/>
         <v>55.024356199999993</v>
       </c>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3">
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2">
         <f>K16/SUM(K14:K17)</f>
         <v>0.22621410870806635</v>
       </c>
@@ -6271,27 +6300,27 @@
       <c r="C17" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
         <v>27.481140133333302</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="3">
         <v>28.4615771</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="3">
         <v>28.472625499999999</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="3">
         <v>92.371672066666605</v>
       </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4">
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3">
         <f t="shared" si="1"/>
         <v>64.890531933333307</v>
       </c>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3">
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2">
         <f>K17/SUM(K14:K17)</f>
         <v>0.26677556737849328</v>
       </c>
@@ -6306,27 +6335,27 @@
       <c r="C18" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
         <v>110.52516749999999</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="3">
         <v>105.954286533333</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="3">
         <v>105.939343766666</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="3">
         <v>242.41138166666599</v>
       </c>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4">
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3">
         <f t="shared" ref="K18:K25" si="2">G18-$D18</f>
         <v>131.88621416666598</v>
       </c>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3">
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2">
         <f>K18/SUM(K18:K21)</f>
         <v>0.34646965147739606</v>
       </c>
@@ -6341,27 +6370,27 @@
       <c r="C19" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
         <v>22.4968641333333</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="3">
         <v>21.9651751</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="3">
         <v>21.967353466666601</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="3">
         <v>63.072072800000001</v>
       </c>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4">
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3">
         <f t="shared" si="2"/>
         <v>40.575208666666697</v>
       </c>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3">
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2">
         <f>K19/SUM(K18:K21)</f>
         <v>0.10659247817665984</v>
       </c>
@@ -6376,27 +6405,27 @@
       <c r="C20" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>33.472099466666599</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="3">
         <v>35.921076766666602</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="3">
         <v>35.926912266666598</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="3">
         <v>111.966809166666</v>
       </c>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4">
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3">
         <f t="shared" si="2"/>
         <v>78.49470969999939</v>
       </c>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3">
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2">
         <f>K20/SUM(K18:K21)</f>
         <v>0.20620832044060539</v>
       </c>
@@ -6411,27 +6440,27 @@
       <c r="C21" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>76.120413600000006</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="3">
         <v>78.775144066666599</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="3">
         <v>78.782043999999999</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="3">
         <v>205.82161600000001</v>
       </c>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4">
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3">
         <f t="shared" si="2"/>
         <v>129.7012024</v>
       </c>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3">
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2">
         <f>K21/SUM(K18:K21)</f>
         <v>0.34072954990533866</v>
       </c>
@@ -6446,27 +6475,27 @@
       <c r="C22" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="3">
         <v>206.888348333333</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="3">
         <v>198.573914</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="3">
         <v>198.586344</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="3">
         <v>297.99930599999999</v>
       </c>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4">
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3">
         <f t="shared" si="2"/>
         <v>91.110957666666991</v>
       </c>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3">
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2">
         <f>K22/SUM(K22:K25)</f>
         <v>0.19206759514842348</v>
       </c>
@@ -6481,27 +6510,27 @@
       <c r="C23" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="3">
         <v>49.988974566666599</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="3">
         <v>48.593891499999998</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="3">
         <v>48.593863266666602</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="3">
         <v>119.52430123333301</v>
       </c>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4">
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3">
         <f t="shared" si="2"/>
         <v>69.535326666666407</v>
       </c>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3">
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2">
         <f>K23/SUM(K22:K25)</f>
         <v>0.14658481606118351</v>
       </c>
@@ -6516,27 +6545,27 @@
       <c r="C24" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="3">
         <v>65.061545266666599</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="3">
         <v>69.434285799999998</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="3">
         <v>69.436308333333301</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G24" s="3">
         <v>182.065700666666</v>
       </c>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4">
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3">
         <f t="shared" si="2"/>
         <v>117.00415539999941</v>
       </c>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3">
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2">
         <f>K24/SUM(K22:K25)</f>
         <v>0.2466520748499603</v>
       </c>
@@ -6551,27 +6580,27 @@
       <c r="C25" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="3">
         <v>177.878598333333</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="3">
         <v>183.20800850000001</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="3">
         <v>183.19356916666601</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="3">
         <v>374.59739093333297</v>
       </c>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4">
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3">
         <f t="shared" si="2"/>
         <v>196.71879259999997</v>
       </c>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3">
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2">
         <f>K25/SUM(K22:K25)</f>
         <v>0.41469551394043275</v>
       </c>
@@ -6586,18 +6615,18 @@
       <c r="C26" t="s">
         <v>21</v>
       </c>
-      <c r="I26" s="4">
+      <c r="I26" s="3">
         <f>E26-$D26</f>
         <v>0</v>
       </c>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="3">
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="2">
         <f>I26/SUM(I26:I29)</f>
         <v>0</v>
       </c>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
@@ -6615,20 +6644,20 @@
       <c r="E27">
         <v>20.753885093333299</v>
       </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="I27" s="4">
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="I27" s="3">
         <f t="shared" ref="I27:I37" si="3">E27-$D27</f>
         <v>8.4519960066666986</v>
       </c>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="3">
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="2">
         <f>I27/SUM(I26:I29)</f>
         <v>0.91523639156372061</v>
       </c>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
@@ -6646,20 +6675,20 @@
       <c r="E28">
         <v>1.2608490400000001</v>
       </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="I28" s="4">
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="I28" s="3">
         <f t="shared" si="3"/>
         <v>0.50075641000000004</v>
       </c>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="3">
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="2">
         <f>I28/SUM(I26:I29)</f>
         <v>5.4225119058184668E-2</v>
       </c>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
@@ -6677,20 +6706,20 @@
       <c r="E29">
         <v>0.46054620333333302</v>
       </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="I29" s="4">
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="I29" s="3">
         <f t="shared" si="3"/>
         <v>0.282015873333333</v>
       </c>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="3">
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="2">
         <f>I29/SUM(I26:I29)</f>
         <v>3.0538489378094842E-2</v>
       </c>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
@@ -6705,28 +6734,28 @@
       <c r="D30">
         <v>10.8468415733333</v>
       </c>
-      <c r="E30" s="4"/>
+      <c r="E30" s="3"/>
       <c r="F30">
         <v>12.15459806</v>
       </c>
       <c r="G30">
         <v>30.969142233333301</v>
       </c>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4">
+      <c r="I30" s="3"/>
+      <c r="J30" s="3">
         <f t="shared" ref="J30:J37" si="4">F30-$D30</f>
         <v>1.3077564866666993</v>
       </c>
-      <c r="K30" s="4">
+      <c r="K30" s="3">
         <f t="shared" ref="K30:K49" si="5">G30-$D30</f>
         <v>20.122300660000001</v>
       </c>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3">
+      <c r="L30" s="2"/>
+      <c r="M30" s="2">
         <f>J30/SUM(J30:J33)</f>
         <v>0.25618436552952295</v>
       </c>
-      <c r="N30" s="3">
+      <c r="N30" s="2">
         <f>K30/SUM(K30:K33)</f>
         <v>0.29717517114896358</v>
       </c>
@@ -6744,28 +6773,28 @@
       <c r="D31">
         <v>19.872583573333301</v>
       </c>
-      <c r="E31" s="4"/>
+      <c r="E31" s="3"/>
       <c r="F31">
         <v>22.984575606666599</v>
       </c>
       <c r="G31">
         <v>59.723357540000002</v>
       </c>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4">
+      <c r="I31" s="3"/>
+      <c r="J31" s="3">
         <f t="shared" si="4"/>
         <v>3.1119920333332978</v>
       </c>
-      <c r="K31" s="4">
+      <c r="K31" s="3">
         <f t="shared" si="5"/>
         <v>39.850773966666701</v>
       </c>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3">
+      <c r="L31" s="2"/>
+      <c r="M31" s="2">
         <f>J31/SUM(J30:J33)</f>
         <v>0.6096270312713119</v>
       </c>
-      <c r="N31" s="3">
+      <c r="N31" s="2">
         <f>K31/SUM(K30:K33)</f>
         <v>0.5885341231136757</v>
       </c>
@@ -6783,28 +6812,28 @@
       <c r="D32">
         <v>2.2453959733333302</v>
       </c>
-      <c r="E32" s="4"/>
+      <c r="E32" s="3"/>
       <c r="F32">
         <v>2.6211905500000001</v>
       </c>
       <c r="G32">
         <v>6.8402470766666603</v>
       </c>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4">
+      <c r="I32" s="3"/>
+      <c r="J32" s="3">
         <f t="shared" si="4"/>
         <v>0.37579457666666993</v>
       </c>
-      <c r="K32" s="4">
+      <c r="K32" s="3">
         <f t="shared" si="5"/>
         <v>4.5948511033333297</v>
       </c>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3">
+      <c r="L32" s="2"/>
+      <c r="M32" s="2">
         <f>J32/SUM(J30:J33)</f>
         <v>7.3616683361420784E-2</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="2">
         <f>K32/SUM(K30:K33)</f>
         <v>6.7858824202514739E-2</v>
       </c>
@@ -6822,28 +6851,28 @@
       <c r="D33">
         <v>1.25755285333333</v>
       </c>
-      <c r="E33" s="4"/>
+      <c r="E33" s="3"/>
       <c r="F33">
         <v>1.56675720666666</v>
       </c>
       <c r="G33">
         <v>4.4015445833333304</v>
       </c>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4">
+      <c r="I33" s="3"/>
+      <c r="J33" s="3">
         <f t="shared" si="4"/>
         <v>0.30920435333332996</v>
       </c>
-      <c r="K33" s="4">
+      <c r="K33" s="3">
         <f t="shared" si="5"/>
         <v>3.1439917300000007</v>
       </c>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3">
+      <c r="L33" s="2"/>
+      <c r="M33" s="2">
         <f>J33/SUM(J30:J33)</f>
         <v>6.0571919837744403E-2</v>
       </c>
-      <c r="N33" s="3">
+      <c r="N33" s="2">
         <f>K33/SUM(K30:K33)</f>
         <v>4.6431881534846134E-2</v>
       </c>
@@ -6870,27 +6899,27 @@
       <c r="G34">
         <v>128.53779913333301</v>
       </c>
-      <c r="I34" s="4">
+      <c r="I34" s="3">
         <f t="shared" si="3"/>
         <v>7.0763139333333953</v>
       </c>
-      <c r="J34" s="4">
+      <c r="J34" s="3">
         <f t="shared" si="4"/>
         <v>4.3877771666667016</v>
       </c>
-      <c r="K34" s="4">
+      <c r="K34" s="3">
         <f t="shared" si="5"/>
         <v>78.015727166666409</v>
       </c>
-      <c r="L34" s="3">
+      <c r="L34" s="2">
         <f>I34/SUM(I34:I37)</f>
         <v>0.47639036558750303</v>
       </c>
-      <c r="M34" s="3">
+      <c r="M34" s="2">
         <f>J34/SUM(J34:J37)</f>
         <v>0.4382677662628251</v>
       </c>
-      <c r="N34" s="3">
+      <c r="N34" s="2">
         <f>K34/SUM(K34:K37)</f>
         <v>0.49492086132824242</v>
       </c>
@@ -6917,27 +6946,27 @@
       <c r="G35">
         <v>30.917709349999999</v>
       </c>
-      <c r="I35" s="4">
+      <c r="I35" s="3">
         <f t="shared" si="3"/>
         <v>1.7145514833333984</v>
       </c>
-      <c r="J35" s="4">
+      <c r="J35" s="3">
         <f t="shared" si="4"/>
         <v>1.1457209499999994</v>
       </c>
-      <c r="K35" s="4">
+      <c r="K35" s="3">
         <f t="shared" si="5"/>
         <v>20.815231433333398</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="2">
         <f>I35/SUM(I34:I37)</f>
         <v>0.11542673426573519</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="2">
         <f>J35/SUM(J34:J37)</f>
         <v>0.11443893854310765</v>
       </c>
-      <c r="N35" s="3">
+      <c r="N35" s="2">
         <f>K35/SUM(K34:K37)</f>
         <v>0.13204891685139269</v>
       </c>
@@ -6964,27 +6993,27 @@
       <c r="G36">
         <v>44.909156233333299</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I36" s="3">
         <f t="shared" si="3"/>
         <v>3.2865443233333007</v>
       </c>
-      <c r="J36" s="4">
+      <c r="J36" s="3">
         <f t="shared" si="4"/>
         <v>2.4800577266665993</v>
       </c>
-      <c r="K36" s="4">
+      <c r="K36" s="3">
         <f t="shared" si="5"/>
         <v>30.7995309233333</v>
       </c>
-      <c r="L36" s="3">
+      <c r="L36" s="2">
         <f>I36/SUM(I34:I37)</f>
         <v>0.22125616054667455</v>
       </c>
-      <c r="M36" s="3">
+      <c r="M36" s="2">
         <f>J36/SUM(J34:J37)</f>
         <v>0.24771753869505342</v>
       </c>
-      <c r="N36" s="3">
+      <c r="N36" s="2">
         <f>K36/SUM(K34:K37)</f>
         <v>0.19538791634303879</v>
       </c>
@@ -7011,27 +7040,27 @@
       <c r="G37">
         <v>41.950605400000001</v>
       </c>
-      <c r="I37" s="4">
+      <c r="I37" s="3">
         <f t="shared" si="3"/>
         <v>2.7766142799999987</v>
       </c>
-      <c r="J37" s="4">
+      <c r="J37" s="3">
         <f t="shared" si="4"/>
         <v>1.9980797466667006</v>
       </c>
-      <c r="K37" s="4">
+      <c r="K37" s="3">
         <f t="shared" si="5"/>
         <v>28.002241813333399</v>
       </c>
-      <c r="L37" s="3">
+      <c r="L37" s="2">
         <f>I37/SUM(I34:I37)</f>
         <v>0.18692673960008727</v>
       </c>
-      <c r="M37" s="3">
+      <c r="M37" s="2">
         <f>J37/SUM(J34:J37)</f>
         <v>0.1995757564990138</v>
       </c>
-      <c r="N37" s="3">
+      <c r="N37" s="2">
         <f>K37/SUM(K34:K37)</f>
         <v>0.17764230547732618</v>
       </c>
@@ -7049,20 +7078,20 @@
       <c r="D38">
         <v>111.1385561</v>
       </c>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
       <c r="G38">
         <v>174.47395166666601</v>
       </c>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4">
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3">
         <f t="shared" si="5"/>
         <v>63.335395566666008</v>
       </c>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3">
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2">
         <f>K38/SUM(K38:K41)</f>
         <v>0.26041637593067141</v>
       </c>
@@ -7080,20 +7109,20 @@
       <c r="D39">
         <v>23.141853900000001</v>
       </c>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
       <c r="G39">
         <v>57.606192233333303</v>
       </c>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4">
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3">
         <f t="shared" si="5"/>
         <v>34.464338333333302</v>
       </c>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3">
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2">
         <f>K39/SUM(K38:K41)</f>
         <v>0.14170714506974419</v>
       </c>
@@ -7111,20 +7140,20 @@
       <c r="D40">
         <v>39.859757299999998</v>
       </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
       <c r="G40">
         <v>110.0637945</v>
       </c>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4">
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3">
         <f t="shared" si="5"/>
         <v>70.204037200000002</v>
       </c>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3">
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2">
         <f>K40/SUM(K38:K41)</f>
         <v>0.28865819467539838</v>
       </c>
@@ -7142,20 +7171,20 @@
       <c r="D41">
         <v>53.642280266666603</v>
       </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
       <c r="G41">
         <v>128.84669966666601</v>
       </c>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4">
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3">
         <f t="shared" si="5"/>
         <v>75.204419399999409</v>
       </c>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3">
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2">
         <f>K41/SUM(K38:K41)</f>
         <v>0.30921828432418608</v>
       </c>
@@ -7173,20 +7202,20 @@
       <c r="D42">
         <v>238.62236933333301</v>
       </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
       <c r="G42">
         <v>296.78645699999998</v>
       </c>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4">
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3">
         <f t="shared" si="5"/>
         <v>58.164087666666973</v>
       </c>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3">
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2">
         <f>K42/SUM(K42:K45)</f>
         <v>0.15285316937789162</v>
       </c>
@@ -7204,20 +7233,20 @@
       <c r="D43">
         <v>60.299173000000003</v>
       </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
       <c r="G43">
         <v>116.07340139999999</v>
       </c>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4">
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3">
         <f t="shared" si="5"/>
         <v>55.774228399999991</v>
       </c>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3">
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2">
         <f>K43/SUM(K42:K45)</f>
         <v>0.14657270357963723</v>
       </c>
@@ -7235,20 +7264,20 @@
       <c r="D44">
         <v>97.315895233333293</v>
       </c>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
       <c r="G44">
         <v>214.53541633333299</v>
       </c>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4">
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3">
         <f t="shared" si="5"/>
         <v>117.2195210999997</v>
       </c>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3">
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2">
         <f>K44/SUM(K42:K45)</f>
         <v>0.30804876396886721</v>
       </c>
@@ -7266,20 +7295,20 @@
       <c r="D45">
         <v>188.42416009999999</v>
       </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
       <c r="G45">
         <v>337.78893756666599</v>
       </c>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4">
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3">
         <f t="shared" si="5"/>
         <v>149.364777466666</v>
       </c>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3">
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2">
         <f>K45/SUM(K42:K45)</f>
         <v>0.39252536307360403</v>
       </c>
@@ -7297,20 +7326,20 @@
       <c r="D46">
         <v>348.79311866666598</v>
       </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
       <c r="G46">
         <v>386.37448666666597</v>
       </c>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4">
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3">
         <f t="shared" si="5"/>
         <v>37.581367999999998</v>
       </c>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3">
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2">
         <f>K46/SUM(K46:K49)</f>
         <v>7.9254516693036001E-2</v>
       </c>
@@ -7328,20 +7357,20 @@
       <c r="D47">
         <v>229.705339966666</v>
       </c>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
       <c r="G47">
         <v>321.027063133333</v>
       </c>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4">
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3">
         <f t="shared" si="5"/>
         <v>91.321723166666999</v>
       </c>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3">
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2">
         <f>K47/SUM(K46:K49)</f>
         <v>0.19258636442264218</v>
       </c>
@@ -7359,20 +7388,20 @@
       <c r="D48">
         <v>345.10346199999998</v>
       </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
       <c r="G48">
         <v>518.30884966666599</v>
       </c>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4">
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3">
         <f t="shared" si="5"/>
         <v>173.20538766666601</v>
       </c>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3">
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2">
         <f>K48/SUM(K46:K49)</f>
         <v>0.36526901543742513</v>
       </c>
@@ -7390,20 +7419,20 @@
       <c r="D49">
         <v>576.39836760000003</v>
       </c>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
       <c r="G49">
         <v>748.47570893333295</v>
       </c>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4">
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3">
         <f t="shared" si="5"/>
         <v>172.07734133333292</v>
       </c>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3">
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2">
         <f>K49/SUM(K46:K49)</f>
         <v>0.36289010344689659</v>
       </c>
@@ -7418,18 +7447,18 @@
       <c r="C50" t="s">
         <v>21</v>
       </c>
-      <c r="I50" s="4">
+      <c r="I50" s="3">
         <f>E50-$D50</f>
         <v>0</v>
       </c>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="3" t="e">
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="2">
         <f>I50/SUM(I50:I53)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
@@ -7441,22 +7470,28 @@
       <c r="C51" t="s">
         <v>22</v>
       </c>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="I51" s="4">
+      <c r="D51">
+        <v>2317.5052434614499</v>
+      </c>
+      <c r="E51">
+        <v>3876.1365728695901</v>
+      </c>
+      <c r="F51">
+        <v>2312.5730481885798</v>
+      </c>
+      <c r="G51" s="3"/>
+      <c r="I51" s="3">
         <f t="shared" ref="I51:I61" si="6">E51-$D51</f>
-        <v>0</v>
-      </c>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="3" t="e">
+        <v>1558.6313294081401</v>
+      </c>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="2">
         <f>I51/SUM(I50:I53)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
+        <v>0.87570969030373169</v>
+      </c>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" t="s">
@@ -7468,22 +7503,28 @@
       <c r="C52" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="I52" s="4">
+      <c r="D52">
+        <v>182.09515124594799</v>
+      </c>
+      <c r="E52">
+        <v>302.35086775823299</v>
+      </c>
+      <c r="F52">
+        <v>178.51766454123899</v>
+      </c>
+      <c r="G52" s="3"/>
+      <c r="I52" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="3" t="e">
+        <v>120.25571651228501</v>
+      </c>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="2">
         <f>I52/SUM(I50:I53)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
+        <v>6.756510938620458E-2</v>
+      </c>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" t="s">
@@ -7495,22 +7536,28 @@
       <c r="C53" t="s">
         <v>24</v>
       </c>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="I53" s="4">
+      <c r="D53">
+        <v>63.301190669687998</v>
+      </c>
+      <c r="E53">
+        <v>164.26350198035999</v>
+      </c>
+      <c r="F53">
+        <v>61.891833647102899</v>
+      </c>
+      <c r="G53" s="3"/>
+      <c r="I53" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="3" t="e">
+        <v>100.96231131067199</v>
+      </c>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="2">
         <f>I53/SUM(I50:I53)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
+        <v>5.6725200310063631E-2</v>
+      </c>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" t="s">
@@ -7522,33 +7569,29 @@
       <c r="C54" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="I54" s="4">
+      <c r="I54" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J54" s="4">
-        <f t="shared" ref="J54:J61" si="7">F54-$D54</f>
+      <c r="J54" s="3">
+        <f t="shared" ref="J54:J65" si="7">F54-$D54</f>
         <v>0</v>
       </c>
-      <c r="K54" s="4">
+      <c r="K54" s="3">
         <f t="shared" ref="K54:K73" si="8">G54-$D54</f>
         <v>0</v>
       </c>
-      <c r="L54" s="3" t="e">
+      <c r="L54" s="2">
         <f>I54/SUM(I54:I57)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M54" s="3" t="e">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2">
         <f>J54/SUM(J54:J57)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N54" s="3" t="e">
+        <v>0</v>
+      </c>
+      <c r="N54" s="2">
         <f>K54/SUM(K54:K57)</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -7561,33 +7604,41 @@
       <c r="C55" t="s">
         <v>22</v>
       </c>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="I55" s="4">
+      <c r="D55">
+        <v>2665.29975566542</v>
+      </c>
+      <c r="E55">
+        <v>3980.8085502945</v>
+      </c>
+      <c r="F55">
+        <v>3292.4960847453999</v>
+      </c>
+      <c r="G55">
+        <v>10820.8510192745</v>
+      </c>
+      <c r="I55" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J55" s="4">
+        <v>1315.5087946290801</v>
+      </c>
+      <c r="J55" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K55" s="4">
+        <v>627.19632907997993</v>
+      </c>
+      <c r="K55" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L55" s="3" t="e">
+        <v>8155.5512636090798</v>
+      </c>
+      <c r="L55" s="2">
         <f>I55/SUM(I54:I57)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M55" s="3" t="e">
+        <v>0.79757159724043636</v>
+      </c>
+      <c r="M55" s="2">
         <f>J55/SUM(J54:J57)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N55" s="3" t="e">
+        <v>0.79070944014070843</v>
+      </c>
+      <c r="N55" s="2">
         <f>K55/SUM(K54:K57)</f>
-        <v>#DIV/0!</v>
+        <v>0.80976703700442687</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -7600,33 +7651,41 @@
       <c r="C56" t="s">
         <v>23</v>
       </c>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="I56" s="4">
+      <c r="D56">
+        <v>299.55375641568997</v>
+      </c>
+      <c r="E56">
+        <v>452.51300344348903</v>
+      </c>
+      <c r="F56">
+        <v>369.57232275599</v>
+      </c>
+      <c r="G56">
+        <v>1248.1796254824601</v>
+      </c>
+      <c r="I56" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J56" s="4">
+        <v>152.95924702779905</v>
+      </c>
+      <c r="J56" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K56" s="4">
+        <v>70.018566340300026</v>
+      </c>
+      <c r="K56" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L56" s="3" t="e">
+        <v>948.62586906677006</v>
+      </c>
+      <c r="L56" s="2">
         <f>I56/SUM(I54:I57)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M56" s="3" t="e">
+        <v>9.273670496368977E-2</v>
+      </c>
+      <c r="M56" s="2">
         <f>J56/SUM(J54:J57)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N56" s="3" t="e">
+        <v>8.8272744631025482E-2</v>
+      </c>
+      <c r="N56" s="2">
         <f>K56/SUM(K54:K57)</f>
-        <v>#DIV/0!</v>
+        <v>9.4189336120978656E-2</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -7639,33 +7698,41 @@
       <c r="C57" t="s">
         <v>24</v>
       </c>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="I57" s="4">
+      <c r="D57">
+        <v>183.72461757723599</v>
+      </c>
+      <c r="E57">
+        <v>364.64930652997799</v>
+      </c>
+      <c r="F57">
+        <v>279.71680587201701</v>
+      </c>
+      <c r="G57">
+        <v>1151.0259360111399</v>
+      </c>
+      <c r="I57" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="4">
+        <v>180.924688952742</v>
+      </c>
+      <c r="J57" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K57" s="4">
+        <v>95.992188294781016</v>
+      </c>
+      <c r="K57" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L57" s="3" t="e">
+        <v>967.30131843390393</v>
+      </c>
+      <c r="L57" s="2">
         <f>I57/SUM(I54:I57)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M57" s="3" t="e">
+        <v>0.10969169779587402</v>
+      </c>
+      <c r="M57" s="2">
         <f>J57/SUM(J54:J57)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N57" s="3" t="e">
+        <v>0.12101781522826606</v>
+      </c>
+      <c r="N57" s="2">
         <f>K57/SUM(K54:K57)</f>
-        <v>#DIV/0!</v>
+        <v>9.6043626874594487E-2</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -7678,33 +7745,32 @@
       <c r="C58" t="s">
         <v>21</v>
       </c>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="I58" s="4">
+      <c r="D58">
+        <v>1437.1253260359499</v>
+      </c>
+      <c r="I58" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="4">
+        <v>-1437.1253260359499</v>
+      </c>
+      <c r="J58" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K58" s="4">
+        <v>-1437.1253260359499</v>
+      </c>
+      <c r="K58" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="e">
+        <v>-1437.1253260359499</v>
+      </c>
+      <c r="L58" s="2">
         <f>I58/SUM(I58:I61)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M58" s="3" t="e">
+        <v>-0.37123459004366133</v>
+      </c>
+      <c r="M58" s="2">
         <f>J58/SUM(J58:J61)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N58" s="3" t="e">
+        <v>-0.50762194036031305</v>
+      </c>
+      <c r="N58" s="2">
         <f>K58/SUM(K58:K61)</f>
-        <v>#DIV/0!</v>
+        <v>-3.8085919845583543E-2</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -7717,33 +7783,41 @@
       <c r="C59" t="s">
         <v>22</v>
       </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="I59" s="4">
+      <c r="D59">
+        <v>1912.0163274440899</v>
+      </c>
+      <c r="E59">
+        <v>3878.1324619694901</v>
+      </c>
+      <c r="F59">
+        <v>3509.1641614923301</v>
+      </c>
+      <c r="G59">
+        <v>16338.8315783952</v>
+      </c>
+      <c r="I59" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="4">
+        <v>1966.1161345254002</v>
+      </c>
+      <c r="J59" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K59" s="4">
+        <v>1597.1478340482402</v>
+      </c>
+      <c r="K59" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L59" s="3" t="e">
+        <v>14426.815250951111</v>
+      </c>
+      <c r="L59" s="2">
         <f>I59/SUM(I58:I61)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M59" s="3" t="e">
+        <v>0.50788216167064248</v>
+      </c>
+      <c r="M59" s="2">
         <f>J59/SUM(J58:J61)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N59" s="3" t="e">
+        <v>0.564145149955807</v>
+      </c>
+      <c r="N59" s="2">
         <f>K59/SUM(K58:K61)</f>
-        <v>#DIV/0!</v>
+        <v>0.38233167234645299</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -7756,33 +7830,41 @@
       <c r="C60" t="s">
         <v>23</v>
       </c>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="I60" s="4">
+      <c r="D60">
+        <v>1733.8995602553</v>
+      </c>
+      <c r="E60">
+        <v>3175.83921502673</v>
+      </c>
+      <c r="F60">
+        <v>2856.5052134766802</v>
+      </c>
+      <c r="G60">
+        <v>13219.904450419201</v>
+      </c>
+      <c r="I60" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J60" s="4">
+        <v>1441.93965477143</v>
+      </c>
+      <c r="J60" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K60" s="4">
+        <v>1122.6056532213802</v>
+      </c>
+      <c r="K60" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L60" s="3" t="e">
+        <v>11486.0048901639</v>
+      </c>
+      <c r="L60" s="2">
         <f>I60/SUM(I58:I61)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M60" s="3" t="e">
+        <v>0.3724782153017181</v>
+      </c>
+      <c r="M60" s="2">
         <f>J60/SUM(J58:J61)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N60" s="3" t="e">
+        <v>0.396527184946039</v>
+      </c>
+      <c r="N60" s="2">
         <f>K60/SUM(K58:K61)</f>
-        <v>#DIV/0!</v>
+        <v>0.30439590317387527</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -7795,33 +7877,41 @@
       <c r="C61" t="s">
         <v>24</v>
       </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="I61" s="4">
+      <c r="D61">
+        <v>1850.7656633716099</v>
+      </c>
+      <c r="E61">
+        <v>3751.0405365178999</v>
+      </c>
+      <c r="F61">
+        <v>3399.2312980756601</v>
+      </c>
+      <c r="G61">
+        <v>15108.8404897418</v>
+      </c>
+      <c r="I61" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="4">
+        <v>1900.27487314629</v>
+      </c>
+      <c r="J61" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K61" s="4">
+        <v>1548.4656347040502</v>
+      </c>
+      <c r="K61" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L61" s="3" t="e">
+        <v>13258.07482637019</v>
+      </c>
+      <c r="L61" s="2">
         <f>I61/SUM(I58:I61)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M61" s="3" t="e">
+        <v>0.4908742130713008</v>
+      </c>
+      <c r="M61" s="2">
         <f>J61/SUM(J58:J61)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N61" s="3" t="e">
+        <v>0.54694960545846705</v>
+      </c>
+      <c r="N61" s="2">
         <f>K61/SUM(K58:K61)</f>
-        <v>#DIV/0!</v>
+        <v>0.35135834432525526</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -7834,21 +7924,19 @@
       <c r="C62" t="s">
         <v>21</v>
       </c>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4">
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3" t="e">
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2">
         <f>K62/SUM(K62:K65)</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -7861,21 +7949,25 @@
       <c r="C63" t="s">
         <v>22</v>
       </c>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4">
+      <c r="D63">
+        <v>2776.2315145113698</v>
+      </c>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63">
+        <v>17390.673329173602</v>
+      </c>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L63" s="3"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3" t="e">
+        <v>14614.441814662232</v>
+      </c>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2">
         <f>K63/SUM(K62:K65)</f>
-        <v>#DIV/0!</v>
+        <v>0.29039686020406907</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -7888,21 +7980,25 @@
       <c r="C64" t="s">
         <v>23</v>
       </c>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4">
+      <c r="D64">
+        <v>2648.0605451709598</v>
+      </c>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64">
+        <v>17478.450226044901</v>
+      </c>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L64" s="3"/>
-      <c r="M64" s="3"/>
-      <c r="N64" s="3" t="e">
+        <v>14830.389680873941</v>
+      </c>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2">
         <f>K64/SUM(K62:K65)</f>
-        <v>#DIV/0!</v>
+        <v>0.29468786105863015</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -7915,21 +8011,25 @@
       <c r="C65" t="s">
         <v>24</v>
       </c>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4">
+      <c r="D65">
+        <v>4265.3844533396496</v>
+      </c>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65">
+        <v>25146.309938758099</v>
+      </c>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3" t="e">
+        <v>20880.925485418447</v>
+      </c>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2">
         <f>K65/SUM(K62:K65)</f>
-        <v>#DIV/0!</v>
+        <v>0.41491527873730083</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -7942,21 +8042,19 @@
       <c r="C66" t="s">
         <v>21</v>
       </c>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4">
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L66" s="3"/>
-      <c r="M66" s="3"/>
-      <c r="N66" s="3" t="e">
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2">
         <f>K66/SUM(K66:K69)</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -7969,21 +8067,25 @@
       <c r="C67" t="s">
         <v>22</v>
       </c>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4">
+      <c r="D67">
+        <v>3046.8072291071499</v>
+      </c>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67">
+        <v>23143.659958120901</v>
+      </c>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3" t="e">
+        <v>20096.85272901375</v>
+      </c>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2">
         <f>K67/SUM(K66:K69)</f>
-        <v>#DIV/0!</v>
+        <v>0.25503271729606303</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -7996,21 +8098,25 @@
       <c r="C68" t="s">
         <v>23</v>
       </c>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4">
+      <c r="D68">
+        <v>2795.2284845232698</v>
+      </c>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68">
+        <v>22816.995727606401</v>
+      </c>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L68" s="3"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3" t="e">
+        <v>20021.76724308313</v>
+      </c>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2">
         <f>K68/SUM(K66:K69)</f>
-        <v>#DIV/0!</v>
+        <v>0.2540798688195085</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -8023,21 +8129,25 @@
       <c r="C69" t="s">
         <v>24</v>
       </c>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4">
+      <c r="D69">
+        <v>6849.0991037536196</v>
+      </c>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69">
+        <v>45531.555880110398</v>
+      </c>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3" t="e">
+        <v>38682.456776356776</v>
+      </c>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2">
         <f>K69/SUM(K66:K69)</f>
-        <v>#DIV/0!</v>
+        <v>0.49088741388442836</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -8050,21 +8160,19 @@
       <c r="C70" t="s">
         <v>21</v>
       </c>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4">
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="3" t="e">
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2">
         <f>K70/SUM(K70:K73)</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -8077,21 +8185,25 @@
       <c r="C71" t="s">
         <v>22</v>
       </c>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="4">
+      <c r="D71">
+        <v>3836.8911031993998</v>
+      </c>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71">
+        <v>31464.8265330295</v>
+      </c>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L71" s="3"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3" t="e">
+        <v>27627.9354298301</v>
+      </c>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2">
         <f>K71/SUM(K70:K73)</f>
-        <v>#DIV/0!</v>
+        <v>0.24989232054808441</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -8104,21 +8216,25 @@
       <c r="C72" t="s">
         <v>23</v>
       </c>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4">
+      <c r="D72">
+        <v>3300.0470468808699</v>
+      </c>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72">
+        <v>30242.557832135099</v>
+      </c>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L72" s="3"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="3" t="e">
+        <v>26942.510785254228</v>
+      </c>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2">
         <f>K72/SUM(K70:K73)</f>
-        <v>#DIV/0!</v>
+        <v>0.24369271307365198</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -8131,21 +8247,25 @@
       <c r="C73" t="s">
         <v>24</v>
       </c>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="4">
+      <c r="D73">
+        <v>9711.1204938189003</v>
+      </c>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73">
+        <v>65700.035883902106</v>
+      </c>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3" t="e">
+        <v>55988.915390083203</v>
+      </c>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2">
         <f>K73/SUM(K70:K73)</f>
-        <v>#DIV/0!</v>
+        <v>0.50641496637826355</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_analysis/procurement.xlsx
+++ b/data/data_analysis/procurement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464EF09C-85D1-4F3F-A239-B0215EDB7C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C150FE-0663-41DB-A5D4-983EE0DEDB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
   </bookViews>
   <sheets>
     <sheet name="Scaling" sheetId="1" r:id="rId1"/>
@@ -19,10 +19,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">'45Q'!$D$2:$D$13</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'45Q'!$D$6:$D$13</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'45Q'!$G$1</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'45Q'!$G$2:$G$13</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'45Q'!$G$6:$G$13</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'45Q'!$G$1</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'45Q'!$G$2:$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="36">
   <si>
     <t>Scenario</t>
   </si>
@@ -145,6 +143,15 @@
   <si>
     <t>% - Rhodium</t>
   </si>
+  <si>
+    <t>Procurement Amount</t>
+  </si>
+  <si>
+    <t>Procurement Budget</t>
+  </si>
+  <si>
+    <t>Actual Budget</t>
+  </si>
 </sst>
 </file>
 
@@ -172,12 +179,18 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -193,12 +206,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -244,7 +259,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Scaling!$G$1</c:f>
+              <c:f>Scaling!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -291,156 +306,162 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Scaling!$F$2:$F$24</c:f>
+              <c:f>Scaling!$D$2:$D$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>22.652770490000002</c:v>
+                  <c:v>22.65</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38.92435596</c:v>
+                  <c:v>38.921038279999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>72.101540779999993</c:v>
+                  <c:v>72.201683639999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>95.2150848</c:v>
+                  <c:v>95.181038279999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>214.75016840000001</c:v>
+                  <c:v>215.76168364</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>360.96804700000001</c:v>
+                  <c:v>364.81046279999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>623.27188550000005</c:v>
+                  <c:v>648.96668739999996</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>974.18677479999997</c:v>
+                  <c:v>1078.26</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>22.652770490000002</c:v>
+                  <c:v>22.65</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>103.695629</c:v>
+                  <c:v>45.752613529999998</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>102.04666</c:v>
+                  <c:v>103.69577185999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>246.34425669999999</c:v>
+                  <c:v>102.04261353</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>470.9906421</c:v>
+                  <c:v>246.34577186000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>965.18417420000003</c:v>
+                  <c:v>470.9930579</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1974.1867749999999</c:v>
+                  <c:v>965.18897609999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>22.64976914</c:v>
+                  <c:v>1974.19</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>30.407393859999999</c:v>
+                  <c:v>22.65</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>44.248195699999997</c:v>
+                  <c:v>30.40962717</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>82.317910130000001</c:v>
+                  <c:v>44.244627790000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>180.40034800000001</c:v>
+                  <c:v>82.319627170000004</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>275.22336999999999</c:v>
+                  <c:v>180.40462779000001</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>461.18036599999999</c:v>
+                  <c:v>275.22833609000003</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>691.29305280000005</c:v>
+                  <c:v>461.17875827</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>691.29</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Scaling!$G$2:$G$24</c:f>
+              <c:f>Scaling!$H$2:$H$25</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>5.9999999999999995E-4</c:v>
+                  <c:v>6.0606060606060606E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.9999999999999993E-3</c:v>
+                  <c:v>9.0909090909090905E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2.1999999999999999E-2</c:v>
+                  <c:v>-2.2121212121212121E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.7999999999999996E-3</c:v>
+                  <c:v>7.7499999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.7300000000000001E-2</c:v>
+                  <c:v>2.7371428571428571E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.19E-2</c:v>
+                  <c:v>4.1939999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2.4799999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-2.3E-2</c:v>
+                  <c:v>-2.3140000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.9999999999999995E-4</c:v>
+                  <c:v>6.0606060606060606E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-2.4E-2</c:v>
+                  <c:v>1.090909090909091E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>-2.0909090909090908E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>8.3499999999999998E-3</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>4.3700000000000003E-2</c:v>
-                </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.11899999999999999</c:v>
+                  <c:v>4.3771428571428572E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.16400000000000001</c:v>
+                  <c:v>0.11934</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.108</c:v>
+                  <c:v>0.16401333333333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>0.10825</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-7.4999999999999997E-3</c:v>
+                  <c:v>-3.0303030303030303E-4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.17300000000000001</c:v>
+                  <c:v>-7.575757575757576E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>0.17303030303030303</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>-2.15E-3</c:v>
                 </c:pt>
-                <c:pt idx="19">
-                  <c:v>7.8E-2</c:v>
-                </c:pt>
                 <c:pt idx="20">
+                  <c:v>7.8085714285714286E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>6.4999999999999997E-3</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>5.0599999999999999E-2</c:v>
-                </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.1055</c:v>
+                  <c:v>5.0680000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.10559</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -772,7 +793,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Scaling!$G$1</c:f>
+              <c:f>Scaling!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -819,10 +840,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Scaling!$H$2:$H$24</c:f>
+              <c:f>Scaling!$E$2:$E$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>13.5</c:v>
                 </c:pt>
@@ -851,45 +872,48 @@
                   <c:v>13.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>34.63261353</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>88.845771859999999</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>34.63261353</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>88.845771859999999</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>227.9230579</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>584.70897609999997</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>1500</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>13.5</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>20.149627169999999</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>30.074627790000001</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>20.149627169999999</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>30.074627790000001</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>44.888336090000003</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>66.998758269999996</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
@@ -897,78 +921,81 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Scaling!$G$2:$G$24</c:f>
+              <c:f>Scaling!$H$2:$H$25</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>5.9999999999999995E-4</c:v>
+                  <c:v>6.0606060606060606E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.9999999999999993E-3</c:v>
+                  <c:v>9.0909090909090905E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2.1999999999999999E-2</c:v>
+                  <c:v>-2.2121212121212121E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.7999999999999996E-3</c:v>
+                  <c:v>7.7499999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.7300000000000001E-2</c:v>
+                  <c:v>2.7371428571428571E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.19E-2</c:v>
+                  <c:v>4.1939999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2.4799999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-2.3E-2</c:v>
+                  <c:v>-2.3140000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.9999999999999995E-4</c:v>
+                  <c:v>6.0606060606060606E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-2.4E-2</c:v>
+                  <c:v>1.090909090909091E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>-2.0909090909090908E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>8.3499999999999998E-3</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>4.3700000000000003E-2</c:v>
-                </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.11899999999999999</c:v>
+                  <c:v>4.3771428571428572E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.16400000000000001</c:v>
+                  <c:v>0.11934</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.108</c:v>
+                  <c:v>0.16401333333333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>0.10825</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-7.4999999999999997E-3</c:v>
+                  <c:v>-3.0303030303030303E-4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.17300000000000001</c:v>
+                  <c:v>-7.575757575757576E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>0.17303030303030303</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>-2.15E-3</c:v>
                 </c:pt>
-                <c:pt idx="19">
-                  <c:v>7.8E-2</c:v>
-                </c:pt>
                 <c:pt idx="20">
+                  <c:v>7.8085714285714286E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>6.4999999999999997E-3</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>5.0599999999999999E-2</c:v>
-                </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.1055</c:v>
+                  <c:v>5.0680000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.10559</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1305,11 +1332,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Scaling!$E$1</c:f>
+              <c:f>Scaling!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Govt Percentage of CDR Market</c:v>
+                  <c:v>Procurement Error</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1352,156 +1379,162 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Scaling!$E$2:$E$24</c:f>
+              <c:f>Scaling!$G$2:$G$25</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>0.40404640545139786</c:v>
+                  <c:v>0.40397350993377479</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2857675459404056</c:v>
+                  <c:v>0.28570666383569043</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.20595755623739934</c:v>
+                  <c:v>0.20705888348173698</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.7080185525392716</c:v>
+                  <c:v>0.70791410996992965</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.73340331201342146</c:v>
+                  <c:v>0.73465314751842192</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.67337701001551531</c:v>
+                  <c:v>0.67681721106601989</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.61044819596631716</c:v>
+                  <c:v>0.62587187892072993</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.48675139825969232</c:v>
+                  <c:v>0.53628994862092627</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.40404640545139786</c:v>
+                  <c:v>0.40397350993377479</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.14320620148801064</c:v>
+                  <c:v>0.24304622494862749</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.66061982302997468</c:v>
+                  <c:v>0.14320738187907053</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.63934303543273963</c:v>
+                  <c:v>0.66060636500829928</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.51607731125237999</c:v>
+                  <c:v>0.63934525366852379</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.39419958208013484</c:v>
+                  <c:v>0.51607979337055954</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.24019347156248674</c:v>
+                  <c:v>0.3942025959904662</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.40396743487514414</c:v>
+                  <c:v>0.24019471276827462</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.33734448723978877</c:v>
+                  <c:v>0.40397350993377479</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.32031968051524407</c:v>
+                  <c:v>0.33739315324858032</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.75522183279217314</c:v>
+                  <c:v>0.32026487073765486</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.83328952453018557</c:v>
+                  <c:v>0.75522693842637822</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.83690216390417715</c:v>
+                  <c:v>0.83329347944993759</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.85472330738815538</c:v>
+                  <c:v>0.83690510676443775</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.85534354844886418</c:v>
+                  <c:v>0.85472280093443687</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.85534290963271564</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Scaling!$G$2:$G$24</c:f>
+              <c:f>Scaling!$H$2:$H$25</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>5.9999999999999995E-4</c:v>
+                  <c:v>6.0606060606060606E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.9999999999999993E-3</c:v>
+                  <c:v>9.0909090909090905E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2.1999999999999999E-2</c:v>
+                  <c:v>-2.2121212121212121E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.7999999999999996E-3</c:v>
+                  <c:v>7.7499999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.7300000000000001E-2</c:v>
+                  <c:v>2.7371428571428571E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.19E-2</c:v>
+                  <c:v>4.1939999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2.4799999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-2.3E-2</c:v>
+                  <c:v>-2.3140000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.9999999999999995E-4</c:v>
+                  <c:v>6.0606060606060606E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-2.4E-2</c:v>
+                  <c:v>1.090909090909091E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>-2.0909090909090908E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>8.3499999999999998E-3</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>4.3700000000000003E-2</c:v>
-                </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.11899999999999999</c:v>
+                  <c:v>4.3771428571428572E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.16400000000000001</c:v>
+                  <c:v>0.11934</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.108</c:v>
+                  <c:v>0.16401333333333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>0.10825</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-7.4999999999999997E-3</c:v>
+                  <c:v>-3.0303030303030303E-4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.17300000000000001</c:v>
+                  <c:v>-7.575757575757576E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>0.17303030303030303</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>-2.15E-3</c:v>
                 </c:pt>
-                <c:pt idx="19">
-                  <c:v>7.8E-2</c:v>
-                </c:pt>
                 <c:pt idx="20">
+                  <c:v>7.8085714285714286E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>6.4999999999999997E-3</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>5.0599999999999999E-2</c:v>
-                </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.1055</c:v>
+                  <c:v>5.0680000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.10559</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1821,7 +1854,7 @@
         <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1859,7 +1892,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{5F8C8374-44F7-452F-BFFD-4FAF44BD728B}" formatIdx="3">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.2</cx:f>
+              <cx:f>_xlchart.v1.1</cx:f>
               <cx:v>Percent of Procurement Budget Spent on 45Q</cx:v>
             </cx:txData>
           </cx:tx>
@@ -4113,13 +4146,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>33337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>109537</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4149,13 +4182,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>33337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>109537</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4185,13 +4218,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4622,7 +4655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B537AA0D-F5C4-4357-8465-DF25FED59988}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -4630,9 +4663,10 @@
     <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4642,20 +4676,29 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
       <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -4665,21 +4708,32 @@
       <c r="C2">
         <v>2025</v>
       </c>
-      <c r="E2" s="2">
-        <f>(F2-H2)/F2</f>
-        <v>0.40404640545139786</v>
+      <c r="D2">
+        <f>E2+F2</f>
+        <v>22.65</v>
+      </c>
+      <c r="E2">
+        <v>13.5</v>
       </c>
       <c r="F2">
-        <v>22.652770490000002</v>
+        <v>9.15</v>
       </c>
       <c r="G2" s="1">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="H2">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <f>(D2-E2)/D2</f>
+        <v>0.40397350993377479</v>
+      </c>
+      <c r="H2" s="5">
+        <f>(J2-I2)/I2</f>
+        <v>6.0606060606060606E-4</v>
+      </c>
+      <c r="I2">
+        <v>3300</v>
+      </c>
+      <c r="J2">
+        <v>3302</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -4689,21 +4743,32 @@
       <c r="C3">
         <v>2030</v>
       </c>
-      <c r="E3" s="2">
-        <f t="shared" ref="E3:E24" si="0">(F3-H3)/F3</f>
-        <v>0.2857675459404056</v>
+      <c r="D3">
+        <f>E3+F3</f>
+        <v>38.921038279999998</v>
+      </c>
+      <c r="E3">
+        <v>27.80103828</v>
       </c>
       <c r="F3">
-        <v>38.92435596</v>
+        <v>11.12</v>
       </c>
       <c r="G3" s="1">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="H3">
-        <v>27.80103828</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <f>(D3-E3)/D3</f>
+        <v>0.28570666383569043</v>
+      </c>
+      <c r="H3" s="5">
+        <f>(J3-I3)/I3</f>
+        <v>9.0909090909090905E-3</v>
+      </c>
+      <c r="I3">
+        <v>3300</v>
+      </c>
+      <c r="J3">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -4713,21 +4778,32 @@
       <c r="C4">
         <v>2035</v>
       </c>
-      <c r="E4" s="2">
-        <f t="shared" si="0"/>
-        <v>0.20595755623739934</v>
+      <c r="D4">
+        <f>E4+F4</f>
+        <v>72.201683639999999</v>
+      </c>
+      <c r="E4">
+        <v>57.251683640000003</v>
       </c>
       <c r="F4">
-        <v>72.101540779999993</v>
+        <v>14.95</v>
       </c>
       <c r="G4" s="1">
-        <v>-2.1999999999999999E-2</v>
-      </c>
-      <c r="H4">
-        <v>57.251683640000003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <f>(D4-E4)/D4</f>
+        <v>0.20705888348173698</v>
+      </c>
+      <c r="H4" s="5">
+        <f>(J4-I4)/I4</f>
+        <v>-2.2121212121212121E-2</v>
+      </c>
+      <c r="I4">
+        <v>3300</v>
+      </c>
+      <c r="J4">
+        <v>3227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -4737,21 +4813,32 @@
       <c r="C5">
         <v>2030</v>
       </c>
-      <c r="E5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.7080185525392716</v>
+      <c r="D5">
+        <f>E5+F5</f>
+        <v>95.181038279999996</v>
+      </c>
+      <c r="E5">
+        <v>27.80103828</v>
       </c>
       <c r="F5">
-        <v>95.2150848</v>
+        <v>67.38</v>
       </c>
       <c r="G5" s="1">
-        <v>7.7999999999999996E-3</v>
-      </c>
-      <c r="H5">
-        <v>27.80103828</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <f>(D5-E5)/D5</f>
+        <v>0.70791410996992965</v>
+      </c>
+      <c r="H5" s="5">
+        <f>(J5-I5)/I5</f>
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="I5">
+        <v>20000</v>
+      </c>
+      <c r="J5">
+        <v>20155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -4761,21 +4848,32 @@
       <c r="C6">
         <v>2035</v>
       </c>
-      <c r="E6" s="2">
-        <f t="shared" si="0"/>
-        <v>0.73340331201342146</v>
+      <c r="D6">
+        <f>E6+F6</f>
+        <v>215.76168364</v>
+      </c>
+      <c r="E6">
+        <v>57.251683640000003</v>
       </c>
       <c r="F6">
-        <v>214.75016840000001</v>
+        <v>158.51</v>
       </c>
       <c r="G6" s="1">
-        <v>2.7300000000000001E-2</v>
-      </c>
-      <c r="H6">
-        <v>57.251683640000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <f>(D6-E6)/D6</f>
+        <v>0.73465314751842192</v>
+      </c>
+      <c r="H6" s="5">
+        <f>(J6-I6)/I6</f>
+        <v>2.7371428571428571E-2</v>
+      </c>
+      <c r="I6">
+        <v>35000</v>
+      </c>
+      <c r="J6">
+        <v>35958</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -4785,21 +4883,32 @@
       <c r="C7">
         <v>2040</v>
       </c>
-      <c r="E7" s="2">
-        <f t="shared" si="0"/>
-        <v>0.67337701001551531</v>
+      <c r="D7">
+        <f>E7+F7</f>
+        <v>364.81046279999998</v>
+      </c>
+      <c r="E7">
+        <v>117.9004628</v>
       </c>
       <c r="F7">
-        <v>360.96804700000001</v>
+        <v>246.91</v>
       </c>
       <c r="G7" s="1">
-        <v>4.19E-2</v>
-      </c>
-      <c r="H7">
-        <v>117.9004628</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <f>(D7-E7)/D7</f>
+        <v>0.67681721106601989</v>
+      </c>
+      <c r="H7" s="5">
+        <f>(J7-I7)/I7</f>
+        <v>4.1939999999999998E-2</v>
+      </c>
+      <c r="I7">
+        <v>50000</v>
+      </c>
+      <c r="J7">
+        <v>52097</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -4809,21 +4918,32 @@
       <c r="C8">
         <v>2045</v>
       </c>
-      <c r="E8" s="2">
-        <f t="shared" si="0"/>
-        <v>0.61044819596631716</v>
+      <c r="D8">
+        <f>E8+F8</f>
+        <v>648.96668739999996</v>
+      </c>
+      <c r="E8">
+        <v>242.7966874</v>
       </c>
       <c r="F8">
-        <v>623.27188550000005</v>
+        <v>406.17</v>
       </c>
       <c r="G8" s="1">
+        <f>(D8-E8)/D8</f>
+        <v>0.62587187892072993</v>
+      </c>
+      <c r="H8" s="5">
+        <f>(J8-I8)/I8</f>
         <v>2.4799999999999999E-2</v>
       </c>
-      <c r="H8">
-        <v>242.7966874</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8">
+        <v>75000</v>
+      </c>
+      <c r="J8">
+        <v>76860</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -4833,21 +4953,32 @@
       <c r="C9">
         <v>2050</v>
       </c>
-      <c r="E9" s="2">
-        <f t="shared" si="0"/>
-        <v>0.48675139825969232</v>
+      <c r="D9">
+        <f>E9+F9</f>
+        <v>1078.26</v>
+      </c>
+      <c r="E9">
+        <v>500</v>
       </c>
       <c r="F9">
-        <v>974.18677479999997</v>
+        <v>578.26</v>
       </c>
       <c r="G9" s="1">
-        <v>-2.3E-2</v>
-      </c>
-      <c r="H9">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <f>(D9-E9)/D9</f>
+        <v>0.53628994862092627</v>
+      </c>
+      <c r="H9" s="5">
+        <f>(J9-I9)/I9</f>
+        <v>-2.3140000000000001E-2</v>
+      </c>
+      <c r="I9">
+        <v>100000</v>
+      </c>
+      <c r="J9">
+        <v>97686</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -4857,21 +4988,32 @@
       <c r="C10">
         <v>2025</v>
       </c>
-      <c r="E10" s="2">
-        <f t="shared" si="0"/>
-        <v>0.40404640545139786</v>
+      <c r="D10">
+        <f>E10+F10</f>
+        <v>22.65</v>
+      </c>
+      <c r="E10">
+        <v>13.5</v>
       </c>
       <c r="F10">
-        <v>22.652770490000002</v>
+        <v>9.15</v>
       </c>
       <c r="G10" s="1">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="H10">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <f>(D10-E10)/D10</f>
+        <v>0.40397350993377479</v>
+      </c>
+      <c r="H10" s="5">
+        <f>(J10-I10)/I10</f>
+        <v>6.0606060606060606E-4</v>
+      </c>
+      <c r="I10">
+        <v>3300</v>
+      </c>
+      <c r="J10">
+        <v>3302</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -4879,47 +5021,69 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>2035</v>
-      </c>
-      <c r="E11" s="2">
-        <f t="shared" si="0"/>
-        <v>0.14320620148801064</v>
+        <v>2030</v>
+      </c>
+      <c r="D11">
+        <f>E11+F11</f>
+        <v>45.752613529999998</v>
+      </c>
+      <c r="E11">
+        <v>34.63261353</v>
       </c>
       <c r="F11">
-        <v>103.695629</v>
+        <v>11.12</v>
       </c>
       <c r="G11" s="1">
-        <v>-2.4E-2</v>
-      </c>
-      <c r="H11">
-        <v>88.845771859999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <f>(D11-E11)/D11</f>
+        <v>0.24304622494862749</v>
+      </c>
+      <c r="H11" s="5">
+        <f>(J11-I11)/I11</f>
+        <v>1.090909090909091E-2</v>
+      </c>
+      <c r="I11">
+        <v>3300</v>
+      </c>
+      <c r="J11">
+        <v>3336</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12">
-        <v>2030</v>
-      </c>
-      <c r="E12" s="2">
-        <f t="shared" si="0"/>
-        <v>0.66061982302997468</v>
+        <v>2035</v>
+      </c>
+      <c r="D12">
+        <f>E12+F12</f>
+        <v>103.69577185999999</v>
+      </c>
+      <c r="E12">
+        <v>88.845771859999999</v>
       </c>
       <c r="F12">
-        <v>102.04666</v>
+        <v>14.85</v>
       </c>
       <c r="G12" s="1">
-        <v>8.3499999999999998E-3</v>
-      </c>
-      <c r="H12">
-        <v>34.63261353</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <f>(D12-E12)/D12</f>
+        <v>0.14320738187907053</v>
+      </c>
+      <c r="H12" s="5">
+        <f>(J12-I12)/I12</f>
+        <v>-2.0909090909090908E-2</v>
+      </c>
+      <c r="I12">
+        <v>3300</v>
+      </c>
+      <c r="J12">
+        <v>3231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -4927,23 +5091,34 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>2035</v>
-      </c>
-      <c r="E13" s="2">
-        <f t="shared" si="0"/>
-        <v>0.63934303543273963</v>
+        <v>2030</v>
+      </c>
+      <c r="D13">
+        <f>E13+F13</f>
+        <v>102.04261353</v>
+      </c>
+      <c r="E13">
+        <v>34.63261353</v>
       </c>
       <c r="F13">
-        <v>246.34425669999999</v>
+        <v>67.41</v>
       </c>
       <c r="G13" s="1">
-        <v>4.3700000000000003E-2</v>
-      </c>
-      <c r="H13">
-        <v>88.845771859999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <f>(D13-E13)/D13</f>
+        <v>0.66060636500829928</v>
+      </c>
+      <c r="H13" s="5">
+        <f>(J13-I13)/I13</f>
+        <v>8.3499999999999998E-3</v>
+      </c>
+      <c r="I13">
+        <v>20000</v>
+      </c>
+      <c r="J13">
+        <v>20167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -4951,23 +5126,34 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>2040</v>
-      </c>
-      <c r="E14" s="2">
-        <f t="shared" si="0"/>
-        <v>0.51607731125237999</v>
+        <v>2035</v>
+      </c>
+      <c r="D14">
+        <f>E14+F14</f>
+        <v>246.34577186000001</v>
+      </c>
+      <c r="E14">
+        <v>88.845771859999999</v>
       </c>
       <c r="F14">
-        <v>470.9906421</v>
+        <v>157.5</v>
       </c>
       <c r="G14" s="1">
-        <v>0.11899999999999999</v>
-      </c>
-      <c r="H14">
-        <v>227.9230579</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <f>(D14-E14)/D14</f>
+        <v>0.63934525366852379</v>
+      </c>
+      <c r="H14" s="5">
+        <f>(J14-I14)/I14</f>
+        <v>4.3771428571428572E-2</v>
+      </c>
+      <c r="I14">
+        <v>35000</v>
+      </c>
+      <c r="J14">
+        <v>36532</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -4975,23 +5161,34 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>2045</v>
-      </c>
-      <c r="E15" s="2">
-        <f t="shared" si="0"/>
-        <v>0.39419958208013484</v>
+        <v>2040</v>
+      </c>
+      <c r="D15">
+        <f>E15+F15</f>
+        <v>470.9930579</v>
+      </c>
+      <c r="E15">
+        <v>227.9230579</v>
       </c>
       <c r="F15">
-        <v>965.18417420000003</v>
+        <v>243.07</v>
       </c>
       <c r="G15" s="1">
-        <v>0.16400000000000001</v>
-      </c>
-      <c r="H15">
-        <v>584.70897609999997</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <f>(D15-E15)/D15</f>
+        <v>0.51607979337055954</v>
+      </c>
+      <c r="H15" s="5">
+        <f>(J15-I15)/I15</f>
+        <v>0.11934</v>
+      </c>
+      <c r="I15">
+        <v>50000</v>
+      </c>
+      <c r="J15">
+        <v>55967</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -4999,47 +5196,69 @@
         <v>9</v>
       </c>
       <c r="C16">
+        <v>2045</v>
+      </c>
+      <c r="D16">
+        <f>E16+F16</f>
+        <v>965.18897609999999</v>
+      </c>
+      <c r="E16">
+        <v>584.70897609999997</v>
+      </c>
+      <c r="F16">
+        <v>380.48</v>
+      </c>
+      <c r="G16" s="1">
+        <f>(D16-E16)/D16</f>
+        <v>0.3942025959904662</v>
+      </c>
+      <c r="H16" s="5">
+        <f>(J16-I16)/I16</f>
+        <v>0.16401333333333334</v>
+      </c>
+      <c r="I16">
+        <v>75000</v>
+      </c>
+      <c r="J16">
+        <v>87301</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17">
         <v>2050</v>
       </c>
-      <c r="E16" s="2">
-        <f t="shared" si="0"/>
-        <v>0.24019347156248674</v>
-      </c>
-      <c r="F16">
-        <v>1974.1867749999999</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0.108</v>
-      </c>
-      <c r="H16">
+      <c r="D17">
+        <f>E17+F17</f>
+        <v>1974.19</v>
+      </c>
+      <c r="E17">
         <v>1500</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17">
-        <v>2025</v>
-      </c>
-      <c r="E17" s="2">
-        <f t="shared" si="0"/>
-        <v>0.40396743487514414</v>
-      </c>
       <c r="F17">
-        <v>22.64976914</v>
+        <v>474.19</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <f>(D17-E17)/D17</f>
+        <v>0.24019471276827462</v>
+      </c>
+      <c r="H17" s="5">
+        <f>(J17-I17)/I17</f>
+        <v>0.10825</v>
+      </c>
+      <c r="I17">
+        <v>100000</v>
+      </c>
+      <c r="J17">
+        <v>110825</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -5047,23 +5266,34 @@
         <v>11</v>
       </c>
       <c r="C18">
-        <v>2030</v>
-      </c>
-      <c r="E18" s="2">
-        <f t="shared" si="0"/>
-        <v>0.33734448723978877</v>
+        <v>2025</v>
+      </c>
+      <c r="D18">
+        <f>E18+F18</f>
+        <v>22.65</v>
+      </c>
+      <c r="E18">
+        <v>13.5</v>
       </c>
       <c r="F18">
-        <v>30.407393859999999</v>
+        <v>9.15</v>
       </c>
       <c r="G18" s="1">
-        <v>-7.4999999999999997E-3</v>
-      </c>
-      <c r="H18">
-        <v>20.149627169999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <f>(D18-E18)/D18</f>
+        <v>0.40397350993377479</v>
+      </c>
+      <c r="H18" s="5">
+        <f>(J18-I18)/I18</f>
+        <v>-3.0303030303030303E-4</v>
+      </c>
+      <c r="I18">
+        <v>3300</v>
+      </c>
+      <c r="J18">
+        <v>3299</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -5071,47 +5301,69 @@
         <v>11</v>
       </c>
       <c r="C19">
-        <v>2035</v>
-      </c>
-      <c r="E19" s="2">
-        <f t="shared" si="0"/>
-        <v>0.32031968051524407</v>
+        <v>2030</v>
+      </c>
+      <c r="D19">
+        <f>E19+F19</f>
+        <v>30.40962717</v>
+      </c>
+      <c r="E19">
+        <v>20.149627169999999</v>
       </c>
       <c r="F19">
-        <v>44.248195699999997</v>
+        <v>10.26</v>
       </c>
       <c r="G19" s="1">
-        <v>0.17300000000000001</v>
-      </c>
-      <c r="H19">
-        <v>30.074627790000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <f>(D19-E19)/D19</f>
+        <v>0.33739315324858032</v>
+      </c>
+      <c r="H19" s="5">
+        <f>(J19-I19)/I19</f>
+        <v>-7.575757575757576E-3</v>
+      </c>
+      <c r="I19">
+        <v>3300</v>
+      </c>
+      <c r="J19">
+        <v>3275</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
       </c>
       <c r="C20">
-        <v>2030</v>
-      </c>
-      <c r="E20" s="2">
-        <f t="shared" si="0"/>
-        <v>0.75522183279217314</v>
+        <v>2035</v>
+      </c>
+      <c r="D20">
+        <f>E20+F20</f>
+        <v>44.244627790000003</v>
+      </c>
+      <c r="E20">
+        <v>30.074627790000001</v>
       </c>
       <c r="F20">
-        <v>82.317910130000001</v>
+        <v>14.17</v>
       </c>
       <c r="G20" s="1">
-        <v>-2.15E-3</v>
-      </c>
-      <c r="H20">
-        <v>20.149627169999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <f>(D20-E20)/D20</f>
+        <v>0.32026487073765486</v>
+      </c>
+      <c r="H20" s="5">
+        <f>(J20-I20)/I20</f>
+        <v>0.17303030303030303</v>
+      </c>
+      <c r="I20">
+        <v>3300</v>
+      </c>
+      <c r="J20">
+        <v>3871</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -5119,23 +5371,34 @@
         <v>11</v>
       </c>
       <c r="C21">
-        <v>2035</v>
-      </c>
-      <c r="E21" s="2">
-        <f t="shared" si="0"/>
-        <v>0.83328952453018557</v>
+        <v>2030</v>
+      </c>
+      <c r="D21">
+        <f>E21+F21</f>
+        <v>82.319627170000004</v>
+      </c>
+      <c r="E21">
+        <v>20.149627169999999</v>
       </c>
       <c r="F21">
-        <v>180.40034800000001</v>
+        <v>62.17</v>
       </c>
       <c r="G21" s="1">
-        <v>7.8E-2</v>
-      </c>
-      <c r="H21">
-        <v>30.074627790000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <f>(D21-E21)/D21</f>
+        <v>0.75522693842637822</v>
+      </c>
+      <c r="H21" s="5">
+        <f>(J21-I21)/I21</f>
+        <v>-2.15E-3</v>
+      </c>
+      <c r="I21">
+        <v>20000</v>
+      </c>
+      <c r="J21">
+        <v>19957</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -5143,23 +5406,34 @@
         <v>11</v>
       </c>
       <c r="C22">
-        <v>2040</v>
-      </c>
-      <c r="E22" s="2">
-        <f t="shared" si="0"/>
-        <v>0.83690216390417715</v>
+        <v>2035</v>
+      </c>
+      <c r="D22">
+        <f>E22+F22</f>
+        <v>180.40462779000001</v>
+      </c>
+      <c r="E22">
+        <v>30.074627790000001</v>
       </c>
       <c r="F22">
-        <v>275.22336999999999</v>
+        <v>150.33000000000001</v>
       </c>
       <c r="G22" s="1">
-        <v>6.4999999999999997E-3</v>
-      </c>
-      <c r="H22">
-        <v>44.888336090000003</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <f>(D22-E22)/D22</f>
+        <v>0.83329347944993759</v>
+      </c>
+      <c r="H22" s="5">
+        <f>(J22-I22)/I22</f>
+        <v>7.8085714285714286E-2</v>
+      </c>
+      <c r="I22">
+        <v>35000</v>
+      </c>
+      <c r="J22">
+        <v>37733</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -5167,23 +5441,34 @@
         <v>11</v>
       </c>
       <c r="C23">
-        <v>2045</v>
-      </c>
-      <c r="E23" s="2">
-        <f t="shared" si="0"/>
-        <v>0.85472330738815538</v>
+        <v>2040</v>
+      </c>
+      <c r="D23">
+        <f>E23+F23</f>
+        <v>275.22833609000003</v>
+      </c>
+      <c r="E23">
+        <v>44.888336090000003</v>
       </c>
       <c r="F23">
-        <v>461.18036599999999</v>
+        <v>230.34</v>
       </c>
       <c r="G23" s="1">
-        <v>5.0599999999999999E-2</v>
-      </c>
-      <c r="H23">
-        <v>66.998758269999996</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <f>(D23-E23)/D23</f>
+        <v>0.83690510676443775</v>
+      </c>
+      <c r="H23" s="5">
+        <f>(J23-I23)/I23</f>
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="I23">
+        <v>50000</v>
+      </c>
+      <c r="J23">
+        <v>50325</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -5191,25 +5476,76 @@
         <v>11</v>
       </c>
       <c r="C24">
+        <v>2045</v>
+      </c>
+      <c r="D24">
+        <f>E24+F24</f>
+        <v>461.17875827</v>
+      </c>
+      <c r="E24">
+        <v>66.998758269999996</v>
+      </c>
+      <c r="F24">
+        <v>394.18</v>
+      </c>
+      <c r="G24" s="1">
+        <f>(D24-E24)/D24</f>
+        <v>0.85472280093443687</v>
+      </c>
+      <c r="H24" s="5">
+        <f>(J24-I24)/I24</f>
+        <v>5.0680000000000003E-2</v>
+      </c>
+      <c r="I24">
+        <v>75000</v>
+      </c>
+      <c r="J24">
+        <v>78801</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25">
         <v>2050</v>
       </c>
-      <c r="E24" s="2">
-        <f t="shared" si="0"/>
-        <v>0.85534354844886418</v>
-      </c>
-      <c r="F24">
-        <v>691.29305280000005</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0.1055</v>
-      </c>
-      <c r="H24">
+      <c r="D25">
+        <f>E25+F25</f>
+        <v>691.29</v>
+      </c>
+      <c r="E25">
         <v>100</v>
       </c>
+      <c r="F25">
+        <v>591.29</v>
+      </c>
+      <c r="G25" s="1">
+        <f>(D25-E25)/D25</f>
+        <v>0.85534290963271564</v>
+      </c>
+      <c r="H25" s="5">
+        <f>(J25-I25)/I25</f>
+        <v>0.10559</v>
+      </c>
+      <c r="I25">
+        <v>100000</v>
+      </c>
+      <c r="J25">
+        <v>110559</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="G26"/>
+      <c r="H26" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5264,7 +5600,7 @@
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>9.1497691446116427</v>
       </c>
       <c r="D2">
@@ -5277,14 +5613,14 @@
       <c r="F2">
         <v>3300</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <f>E2/F2</f>
         <v>0.46058297634703638</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="3">
         <v>3736.5136659285899</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="3">
         <v>2216.58984398337</v>
       </c>
     </row>
@@ -5295,7 +5631,7 @@
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>10.257766689126317</v>
       </c>
       <c r="D3">
@@ -5308,14 +5644,14 @@
       <c r="F3">
         <v>3300</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <f t="shared" ref="G3:G13" si="1">E3/F3</f>
         <v>0.49276210523245745</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="3">
         <v>4814.1169809663397</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="3">
         <v>3188.0020336992302</v>
       </c>
     </row>
@@ -5326,7 +5662,7 @@
       <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>67.381687905293646</v>
       </c>
       <c r="D4">
@@ -5339,14 +5675,14 @@
       <c r="F4">
         <v>20000</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <f t="shared" si="1"/>
         <v>0.49431246620579838</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="3">
         <v>13074.251357815199</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="3">
         <v>3188.0020336992302</v>
       </c>
     </row>
@@ -5357,7 +5693,7 @@
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>5</v>
       </c>
       <c r="D5">
@@ -5370,14 +5706,14 @@
       <c r="F5">
         <v>1608</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <f t="shared" si="1"/>
         <v>0.49348117369654221</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="3">
         <v>3981.5197610032701</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="3">
         <v>3188.0020336992302</v>
       </c>
     </row>
@@ -5388,7 +5724,7 @@
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>9.1527704871198079</v>
       </c>
       <c r="D6">
@@ -5401,14 +5737,14 @@
       <c r="F6">
         <v>3300</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <f t="shared" si="1"/>
         <v>0.46120303030303023</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="6">
         <v>3302.97</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="6">
         <v>1781</v>
       </c>
     </row>
@@ -5419,7 +5755,7 @@
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>11.123317675046577</v>
       </c>
       <c r="D7">
@@ -5432,14 +5768,14 @@
       <c r="F7">
         <v>3300</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="1">
         <f t="shared" si="1"/>
         <v>0.36212121212121212</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="6">
         <v>3330</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="6">
         <v>2135</v>
       </c>
     </row>
@@ -5450,7 +5786,7 @@
       <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>67.381687905293646</v>
       </c>
       <c r="D8">
@@ -5463,14 +5799,14 @@
       <c r="F8">
         <v>20000</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
         <f t="shared" si="1"/>
         <v>0.35675000000000001</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="6">
         <v>20155</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="6">
         <v>13020</v>
       </c>
     </row>
@@ -5481,7 +5817,7 @@
       <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>5</v>
       </c>
       <c r="D9">
@@ -5494,14 +5830,14 @@
       <c r="F9">
         <v>1484</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="1">
         <f t="shared" si="1"/>
         <v>0.37008086253369277</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="6">
         <v>1480</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="6">
         <v>930.8</v>
       </c>
     </row>
@@ -5512,7 +5848,7 @@
       <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>11.123317675046577</v>
       </c>
       <c r="D10">
@@ -5525,14 +5861,14 @@
       <c r="F10">
         <v>3300</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <f t="shared" si="1"/>
         <v>0.46101818181818172</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="6">
         <v>3302.74</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="6">
         <v>1781.38</v>
       </c>
     </row>
@@ -5543,15 +5879,15 @@
       <c r="B11" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>14.849857137390348</v>
       </c>
       <c r="D11">
         <v>2030</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
@@ -5560,7 +5896,7 @@
       <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>67.41404651543381</v>
       </c>
       <c r="D12">
@@ -5573,14 +5909,14 @@
       <c r="F12">
         <v>20000</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <f t="shared" si="1"/>
         <v>0.35863100000000003</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="6">
         <v>20167</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="6">
         <v>12994.38</v>
       </c>
     </row>
@@ -5591,7 +5927,7 @@
       <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <v>5</v>
       </c>
       <c r="D13">
@@ -5604,14 +5940,14 @@
       <c r="F13">
         <v>1483</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <f t="shared" si="1"/>
         <v>0.37772083614295338</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="6">
         <v>1502.36</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="6">
         <v>942.2</v>
       </c>
     </row>
@@ -5682,957 +6018,957 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>2025</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
         <f>E2-$D2</f>
         <v>0</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="2">
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="1">
         <f>I2/SUM(I2:I5)</f>
         <v>0</v>
       </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>2025</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>12.302540506666601</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>20.75363917</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>12.38344833</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>12.337415273333299</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <f t="shared" ref="I3:I13" si="0">E3-$D3</f>
         <v>8.4510986633333989</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="2">
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="1">
         <f>I3/SUM(I2:I5)</f>
         <v>0.91515732423128149</v>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>2025</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>0.75969476000000002</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>1.26107314666666</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>0.74495450333333302</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>0.74290502000000003</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <f t="shared" si="0"/>
         <v>0.50137838666666001</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="2">
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="1">
         <f>I4/SUM(I2:I5)</f>
         <v>5.4293544667750375E-2</v>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>2025</v>
       </c>
       <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>0.17843507</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>0.46054363666666598</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>0.174611396666666</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>0.173851956666666</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <f t="shared" si="0"/>
         <v>0.28210856666666595</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="2">
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="1">
         <f>I5/SUM(I2:I5)</f>
         <v>3.0549131100968078E-2</v>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>2030</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>8.65097456666666</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>11.925114263333301</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>10.037346550000001</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>29.0249384333333</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <f t="shared" si="0"/>
         <v>3.2741396966666407</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <f t="shared" ref="J6:K17" si="1">F6-$D6</f>
         <v>1.3863719833333406</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="2">
         <f t="shared" si="1"/>
         <v>20.373963866666642</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="1">
         <f>I6/SUM(I6:I9)</f>
         <v>0.29026154892397193</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="1">
         <f>J6/SUM(J6:J9)</f>
         <v>0.27495341571805787</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="1">
         <f>K6/SUM(K6:K9)</f>
         <v>0.30065410025493072</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="3">
         <v>2030</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>15.9532513066666</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>22.5884521133333</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>19.007243493333299</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>55.595604350000002</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <f t="shared" si="0"/>
         <v>6.6352008066667008</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <f t="shared" si="1"/>
         <v>3.053992186666699</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="2">
         <f t="shared" si="1"/>
         <v>39.642353043333401</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="1">
         <f>I7/SUM(I6:I9)</f>
         <v>0.58822892179140773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="1">
         <f>J7/SUM(J6:J9)</f>
         <v>0.60568562650935354</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="1">
         <f>K7/SUM(K6:K9)</f>
         <v>0.58499347815824465</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="3">
         <v>2030</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>1.8031504333333299</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>2.57378616</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>2.1532217299999998</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <v>6.3818963266666602</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="2">
         <f t="shared" si="0"/>
         <v>0.77063572666667013</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <f t="shared" si="1"/>
         <v>0.35007129666666992</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="2">
         <f t="shared" si="1"/>
         <v>4.5787458933333305</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="1">
         <f>I8/SUM(I6:I9)</f>
         <v>6.8318990758442624E-2</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="1">
         <f>J8/SUM(J6:J9)</f>
         <v>6.9428190933231826E-2</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="1">
         <f>K8/SUM(K6:K9)</f>
         <v>6.7567545317401126E-2</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="3">
         <v>2030</v>
       </c>
       <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>0.93724469666666599</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>1.53723203333333</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>1.1890160333333299</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <v>4.1076434300000004</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
         <f t="shared" si="0"/>
         <v>0.59998733666666404</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <f t="shared" si="1"/>
         <v>0.25177133666666396</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="2">
         <f t="shared" si="1"/>
         <v>3.1703987333333346</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="1">
         <f>I9/SUM(I6:I9)</f>
         <v>5.3190538526177646E-2</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="1">
         <f>J9/SUM(J6:J9)</f>
         <v>4.993276683935681E-2</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="1">
         <f>K9/SUM(K6:K9)</f>
         <v>4.6784876269423577E-2</v>
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="3">
         <v>2035</v>
       </c>
       <c r="C10" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>32.8174128333333</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>40.421700000000001</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>37.7868285666666</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <v>114.596670466666</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="2">
         <f t="shared" si="0"/>
         <v>7.6042871666667011</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="2">
         <f t="shared" si="1"/>
         <v>4.9694157333332996</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="2">
         <f t="shared" si="1"/>
         <v>81.779257633332691</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="1">
         <f>I10/SUM(I10:I13)</f>
         <v>0.51139464221983688</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="1">
         <f>J10/SUM(J10:J13)</f>
         <v>0.49509882031009567</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="1">
         <f>K10/SUM(K10:K13)</f>
         <v>0.51852648076029639</v>
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="3">
         <v>2035</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>6.3966195333333298</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>8.06076223333333</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>7.4923460333333303</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>26.1684194933333</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <f t="shared" si="0"/>
         <v>1.6641427000000002</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <f t="shared" si="1"/>
         <v>1.0957265000000005</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="2">
         <f t="shared" si="1"/>
         <v>19.771799959999971</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="1">
         <f>I11/SUM(I10:I13)</f>
         <v>0.11191498190648941</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="1">
         <f>J11/SUM(J10:J13)</f>
         <v>0.10916633396027549</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="1">
         <f>K11/SUM(K10:K13)</f>
         <v>0.12536433012784678</v>
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="3">
         <v>2035</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>8.9131753333333297</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>11.88907687</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>11.058108819999999</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <v>38.070494366666601</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="2">
         <f t="shared" si="0"/>
         <v>2.9759015366666706</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="2">
         <f t="shared" si="1"/>
         <v>2.1449334866666696</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="2">
         <f t="shared" si="1"/>
         <v>29.157319033333273</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="1">
         <f>I12/SUM(I10:I13)</f>
         <v>0.20013185565849878</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12" s="1">
         <f>J12/SUM(J10:J13)</f>
         <v>0.21369796689961559</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="1">
         <f>K12/SUM(K10:K13)</f>
         <v>0.1848737988616464</v>
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="3">
         <v>2035</v>
       </c>
       <c r="C13" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>8.8559258333333304</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <v>11.481298839999999</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>10.683070016666599</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <v>35.862267099999997</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="2">
         <f t="shared" si="0"/>
         <v>2.6253730066666687</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="2">
         <f t="shared" si="1"/>
         <v>1.8271441833332691</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="2">
         <f t="shared" si="1"/>
         <v>27.006341266666666</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="1">
         <f>I13/SUM(I10:I13)</f>
         <v>0.17655852021517499</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13" s="1">
         <f>J13/SUM(J10:J13)</f>
         <v>0.18203687883001313</v>
       </c>
-      <c r="N13" s="2">
+      <c r="N13" s="1">
         <f>K13/SUM(K10:K13)</f>
         <v>0.17123539025021053</v>
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" t="s">
+      <c r="A14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="3">
         <v>2040</v>
       </c>
       <c r="C14" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <v>59.1438998333333</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <v>56.976563966666603</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>56.951071833333302</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <v>154.085919166666</v>
       </c>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3">
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2">
         <f t="shared" si="1"/>
         <v>94.942019333332695</v>
       </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2">
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1">
         <f>K14/SUM(K14:K17)</f>
         <v>0.39032213669832749</v>
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="3">
         <v>2040</v>
       </c>
       <c r="C15" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <v>11.3755561333333</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <v>11.1483247333333</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>11.153745166666599</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <v>39.758809566666599</v>
       </c>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3">
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2">
         <f t="shared" si="1"/>
         <v>28.383253433333302</v>
       </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2">
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1">
         <f>K15/SUM(K14:K17)</f>
         <v>0.1166881872151129</v>
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="3">
         <v>2040</v>
       </c>
       <c r="C16" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <v>19.689983866666601</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <v>21.142851033333301</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>21.151816766666599</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <v>74.714340066666594</v>
       </c>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3">
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2">
         <f t="shared" si="1"/>
         <v>55.024356199999993</v>
       </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2">
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1">
         <f>K16/SUM(K14:K17)</f>
         <v>0.22621410870806635</v>
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="3">
         <v>2040</v>
       </c>
       <c r="C17" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <v>27.481140133333302</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <v>28.4615771</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <v>28.472625499999999</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="2">
         <v>92.371672066666605</v>
       </c>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3">
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2">
         <f t="shared" si="1"/>
         <v>64.890531933333307</v>
       </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2">
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1">
         <f>K17/SUM(K14:K17)</f>
         <v>0.26677556737849328</v>
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="3">
         <v>2045</v>
       </c>
       <c r="C18" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <v>110.52516749999999</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <v>105.954286533333</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <v>105.939343766666</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
         <v>242.41138166666599</v>
       </c>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3">
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2">
         <f t="shared" ref="K18:K25" si="2">G18-$D18</f>
         <v>131.88621416666598</v>
       </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2">
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1">
         <f>K18/SUM(K18:K21)</f>
         <v>0.34646965147739606</v>
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="3">
         <v>2045</v>
       </c>
       <c r="C19" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <v>22.4968641333333</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <v>21.9651751</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <v>21.967353466666601</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="2">
         <v>63.072072800000001</v>
       </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3">
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2">
         <f t="shared" si="2"/>
         <v>40.575208666666697</v>
       </c>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2">
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1">
         <f>K19/SUM(K18:K21)</f>
         <v>0.10659247817665984</v>
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" t="s">
+      <c r="A20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="3">
         <v>2045</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="2">
         <v>33.472099466666599</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="2">
         <v>35.921076766666602</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="2">
         <v>35.926912266666598</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="2">
         <v>111.966809166666</v>
       </c>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3">
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2">
         <f t="shared" si="2"/>
         <v>78.49470969999939</v>
       </c>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2">
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1">
         <f>K20/SUM(K18:K21)</f>
         <v>0.20620832044060539</v>
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" t="s">
+      <c r="A21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="3">
         <v>2045</v>
       </c>
       <c r="C21" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="2">
         <v>76.120413600000006</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="2">
         <v>78.775144066666599</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
         <v>78.782043999999999</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="2">
         <v>205.82161600000001</v>
       </c>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3">
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2">
         <f t="shared" si="2"/>
         <v>129.7012024</v>
       </c>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2">
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1">
         <f>K21/SUM(K18:K21)</f>
         <v>0.34072954990533866</v>
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" t="s">
+      <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="3">
         <v>2050</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="2">
         <v>206.888348333333</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="2">
         <v>198.573914</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="2">
         <v>198.586344</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="2">
         <v>297.99930599999999</v>
       </c>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3">
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2">
         <f t="shared" si="2"/>
         <v>91.110957666666991</v>
       </c>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2">
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1">
         <f>K22/SUM(K22:K25)</f>
         <v>0.19206759514842348</v>
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" t="s">
+      <c r="A23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="3">
         <v>2050</v>
       </c>
       <c r="C23" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="2">
         <v>49.988974566666599</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="2">
         <v>48.593891499999998</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="2">
         <v>48.593863266666602</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="2">
         <v>119.52430123333301</v>
       </c>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3">
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2">
         <f t="shared" si="2"/>
         <v>69.535326666666407</v>
       </c>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2">
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1">
         <f>K23/SUM(K22:K25)</f>
         <v>0.14658481606118351</v>
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" t="s">
+      <c r="A24" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="3">
         <v>2050</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="2">
         <v>65.061545266666599</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="2">
         <v>69.434285799999998</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="2">
         <v>69.436308333333301</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="2">
         <v>182.065700666666</v>
       </c>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3">
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2">
         <f t="shared" si="2"/>
         <v>117.00415539999941</v>
       </c>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2">
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1">
         <f>K24/SUM(K22:K25)</f>
         <v>0.2466520748499603</v>
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" t="s">
+      <c r="A25" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="3">
         <v>2050</v>
       </c>
       <c r="C25" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="2">
         <v>177.878598333333</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="2">
         <v>183.20800850000001</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="2">
         <v>183.19356916666601</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="2">
         <v>374.59739093333297</v>
       </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3">
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2">
         <f t="shared" si="2"/>
         <v>196.71879259999997</v>
       </c>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2">
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1">
         <f>K25/SUM(K22:K25)</f>
         <v>0.41469551394043275</v>
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" t="s">
+      <c r="A26" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="3">
         <v>2025</v>
       </c>
       <c r="C26" t="s">
         <v>21</v>
       </c>
-      <c r="I26" s="3">
+      <c r="I26" s="2">
         <f>E26-$D26</f>
         <v>0</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="2">
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="1">
         <f>I26/SUM(I26:I29)</f>
         <v>0</v>
       </c>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" t="s">
+      <c r="A27" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="3">
         <v>2025</v>
       </c>
       <c r="C27" t="s">
@@ -6644,26 +6980,26 @@
       <c r="E27">
         <v>20.753885093333299</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="I27" s="3">
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="I27" s="2">
         <f t="shared" ref="I27:I37" si="3">E27-$D27</f>
         <v>8.4519960066666986</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="2">
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="1">
         <f>I27/SUM(I26:I29)</f>
         <v>0.91523639156372061</v>
       </c>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" t="s">
+      <c r="A28" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="3">
         <v>2025</v>
       </c>
       <c r="C28" t="s">
@@ -6675,26 +7011,26 @@
       <c r="E28">
         <v>1.2608490400000001</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="I28" s="3">
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="I28" s="2">
         <f t="shared" si="3"/>
         <v>0.50075641000000004</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="2">
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="1">
         <f>I28/SUM(I26:I29)</f>
         <v>5.4225119058184668E-2</v>
       </c>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" t="s">
+      <c r="A29" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="3">
         <v>2025</v>
       </c>
       <c r="C29" t="s">
@@ -6706,26 +7042,26 @@
       <c r="E29">
         <v>0.46054620333333302</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="I29" s="3">
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="I29" s="2">
         <f t="shared" si="3"/>
         <v>0.282015873333333</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="2">
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="1">
         <f>I29/SUM(I26:I29)</f>
         <v>3.0538489378094842E-2</v>
       </c>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" t="s">
+      <c r="A30" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="3">
         <v>2030</v>
       </c>
       <c r="C30" t="s">
@@ -6734,37 +7070,37 @@
       <c r="D30">
         <v>10.8468415733333</v>
       </c>
-      <c r="E30" s="3"/>
+      <c r="E30" s="2"/>
       <c r="F30">
         <v>12.15459806</v>
       </c>
       <c r="G30">
         <v>30.969142233333301</v>
       </c>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3">
+      <c r="I30" s="2"/>
+      <c r="J30" s="2">
         <f t="shared" ref="J30:J37" si="4">F30-$D30</f>
         <v>1.3077564866666993</v>
       </c>
-      <c r="K30" s="3">
+      <c r="K30" s="2">
         <f t="shared" ref="K30:K49" si="5">G30-$D30</f>
         <v>20.122300660000001</v>
       </c>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2">
+      <c r="L30" s="1"/>
+      <c r="M30" s="1">
         <f>J30/SUM(J30:J33)</f>
         <v>0.25618436552952295</v>
       </c>
-      <c r="N30" s="2">
+      <c r="N30" s="1">
         <f>K30/SUM(K30:K33)</f>
         <v>0.29717517114896358</v>
       </c>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" t="s">
+      <c r="A31" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="3">
         <v>2030</v>
       </c>
       <c r="C31" t="s">
@@ -6773,37 +7109,37 @@
       <c r="D31">
         <v>19.872583573333301</v>
       </c>
-      <c r="E31" s="3"/>
+      <c r="E31" s="2"/>
       <c r="F31">
         <v>22.984575606666599</v>
       </c>
       <c r="G31">
         <v>59.723357540000002</v>
       </c>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3">
+      <c r="I31" s="2"/>
+      <c r="J31" s="2">
         <f t="shared" si="4"/>
         <v>3.1119920333332978</v>
       </c>
-      <c r="K31" s="3">
+      <c r="K31" s="2">
         <f t="shared" si="5"/>
         <v>39.850773966666701</v>
       </c>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2">
+      <c r="L31" s="1"/>
+      <c r="M31" s="1">
         <f>J31/SUM(J30:J33)</f>
         <v>0.6096270312713119</v>
       </c>
-      <c r="N31" s="2">
+      <c r="N31" s="1">
         <f>K31/SUM(K30:K33)</f>
         <v>0.5885341231136757</v>
       </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" t="s">
+      <c r="A32" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="3">
         <v>2030</v>
       </c>
       <c r="C32" t="s">
@@ -6812,37 +7148,37 @@
       <c r="D32">
         <v>2.2453959733333302</v>
       </c>
-      <c r="E32" s="3"/>
+      <c r="E32" s="2"/>
       <c r="F32">
         <v>2.6211905500000001</v>
       </c>
       <c r="G32">
         <v>6.8402470766666603</v>
       </c>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3">
+      <c r="I32" s="2"/>
+      <c r="J32" s="2">
         <f t="shared" si="4"/>
         <v>0.37579457666666993</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="2">
         <f t="shared" si="5"/>
         <v>4.5948511033333297</v>
       </c>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2">
+      <c r="L32" s="1"/>
+      <c r="M32" s="1">
         <f>J32/SUM(J30:J33)</f>
         <v>7.3616683361420784E-2</v>
       </c>
-      <c r="N32" s="2">
+      <c r="N32" s="1">
         <f>K32/SUM(K30:K33)</f>
         <v>6.7858824202514739E-2</v>
       </c>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" t="s">
+      <c r="A33" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="3">
         <v>2030</v>
       </c>
       <c r="C33" t="s">
@@ -6851,37 +7187,37 @@
       <c r="D33">
         <v>1.25755285333333</v>
       </c>
-      <c r="E33" s="3"/>
+      <c r="E33" s="2"/>
       <c r="F33">
         <v>1.56675720666666</v>
       </c>
       <c r="G33">
         <v>4.4015445833333304</v>
       </c>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3">
+      <c r="I33" s="2"/>
+      <c r="J33" s="2">
         <f t="shared" si="4"/>
         <v>0.30920435333332996</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="2">
         <f t="shared" si="5"/>
         <v>3.1439917300000007</v>
       </c>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2">
+      <c r="L33" s="1"/>
+      <c r="M33" s="1">
         <f>J33/SUM(J30:J33)</f>
         <v>6.0571919837744403E-2</v>
       </c>
-      <c r="N33" s="2">
+      <c r="N33" s="1">
         <f>K33/SUM(K30:K33)</f>
         <v>4.6431881534846134E-2</v>
       </c>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" t="s">
+      <c r="A34" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="3">
         <v>2035</v>
       </c>
       <c r="C34" t="s">
@@ -6899,36 +7235,36 @@
       <c r="G34">
         <v>128.53779913333301</v>
       </c>
-      <c r="I34" s="3">
+      <c r="I34" s="2">
         <f t="shared" si="3"/>
         <v>7.0763139333333953</v>
       </c>
-      <c r="J34" s="3">
+      <c r="J34" s="2">
         <f t="shared" si="4"/>
         <v>4.3877771666667016</v>
       </c>
-      <c r="K34" s="3">
+      <c r="K34" s="2">
         <f t="shared" si="5"/>
         <v>78.015727166666409</v>
       </c>
-      <c r="L34" s="2">
+      <c r="L34" s="1">
         <f>I34/SUM(I34:I37)</f>
         <v>0.47639036558750303</v>
       </c>
-      <c r="M34" s="2">
+      <c r="M34" s="1">
         <f>J34/SUM(J34:J37)</f>
         <v>0.4382677662628251</v>
       </c>
-      <c r="N34" s="2">
+      <c r="N34" s="1">
         <f>K34/SUM(K34:K37)</f>
         <v>0.49492086132824242</v>
       </c>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" t="s">
+      <c r="A35" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="3">
         <v>2035</v>
       </c>
       <c r="C35" t="s">
@@ -6946,36 +7282,36 @@
       <c r="G35">
         <v>30.917709349999999</v>
       </c>
-      <c r="I35" s="3">
+      <c r="I35" s="2">
         <f t="shared" si="3"/>
         <v>1.7145514833333984</v>
       </c>
-      <c r="J35" s="3">
+      <c r="J35" s="2">
         <f t="shared" si="4"/>
         <v>1.1457209499999994</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="2">
         <f t="shared" si="5"/>
         <v>20.815231433333398</v>
       </c>
-      <c r="L35" s="2">
+      <c r="L35" s="1">
         <f>I35/SUM(I34:I37)</f>
         <v>0.11542673426573519</v>
       </c>
-      <c r="M35" s="2">
+      <c r="M35" s="1">
         <f>J35/SUM(J34:J37)</f>
         <v>0.11443893854310765</v>
       </c>
-      <c r="N35" s="2">
+      <c r="N35" s="1">
         <f>K35/SUM(K34:K37)</f>
         <v>0.13204891685139269</v>
       </c>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" t="s">
+      <c r="A36" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="3">
         <v>2035</v>
       </c>
       <c r="C36" t="s">
@@ -6993,36 +7329,36 @@
       <c r="G36">
         <v>44.909156233333299</v>
       </c>
-      <c r="I36" s="3">
+      <c r="I36" s="2">
         <f t="shared" si="3"/>
         <v>3.2865443233333007</v>
       </c>
-      <c r="J36" s="3">
+      <c r="J36" s="2">
         <f t="shared" si="4"/>
         <v>2.4800577266665993</v>
       </c>
-      <c r="K36" s="3">
+      <c r="K36" s="2">
         <f t="shared" si="5"/>
         <v>30.7995309233333</v>
       </c>
-      <c r="L36" s="2">
+      <c r="L36" s="1">
         <f>I36/SUM(I34:I37)</f>
         <v>0.22125616054667455</v>
       </c>
-      <c r="M36" s="2">
+      <c r="M36" s="1">
         <f>J36/SUM(J34:J37)</f>
         <v>0.24771753869505342</v>
       </c>
-      <c r="N36" s="2">
+      <c r="N36" s="1">
         <f>K36/SUM(K34:K37)</f>
         <v>0.19538791634303879</v>
       </c>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" t="s">
+      <c r="A37" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="3">
         <v>2035</v>
       </c>
       <c r="C37" t="s">
@@ -7040,36 +7376,36 @@
       <c r="G37">
         <v>41.950605400000001</v>
       </c>
-      <c r="I37" s="3">
+      <c r="I37" s="2">
         <f t="shared" si="3"/>
         <v>2.7766142799999987</v>
       </c>
-      <c r="J37" s="3">
+      <c r="J37" s="2">
         <f t="shared" si="4"/>
         <v>1.9980797466667006</v>
       </c>
-      <c r="K37" s="3">
+      <c r="K37" s="2">
         <f t="shared" si="5"/>
         <v>28.002241813333399</v>
       </c>
-      <c r="L37" s="2">
+      <c r="L37" s="1">
         <f>I37/SUM(I34:I37)</f>
         <v>0.18692673960008727</v>
       </c>
-      <c r="M37" s="2">
+      <c r="M37" s="1">
         <f>J37/SUM(J34:J37)</f>
         <v>0.1995757564990138</v>
       </c>
-      <c r="N37" s="2">
+      <c r="N37" s="1">
         <f>K37/SUM(K34:K37)</f>
         <v>0.17764230547732618</v>
       </c>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" t="s">
+      <c r="A38" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="3">
         <v>2040</v>
       </c>
       <c r="C38" t="s">
@@ -7078,29 +7414,29 @@
       <c r="D38">
         <v>111.1385561</v>
       </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
       <c r="G38">
         <v>174.47395166666601</v>
       </c>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3">
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2">
         <f t="shared" si="5"/>
         <v>63.335395566666008</v>
       </c>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2">
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1">
         <f>K38/SUM(K38:K41)</f>
         <v>0.26041637593067141</v>
       </c>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" t="s">
+      <c r="A39" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="3">
         <v>2040</v>
       </c>
       <c r="C39" t="s">
@@ -7109,29 +7445,29 @@
       <c r="D39">
         <v>23.141853900000001</v>
       </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
       <c r="G39">
         <v>57.606192233333303</v>
       </c>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3">
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2">
         <f t="shared" si="5"/>
         <v>34.464338333333302</v>
       </c>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="2">
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1">
         <f>K39/SUM(K38:K41)</f>
         <v>0.14170714506974419</v>
       </c>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" t="s">
+      <c r="A40" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="3">
         <v>2040</v>
       </c>
       <c r="C40" t="s">
@@ -7140,29 +7476,29 @@
       <c r="D40">
         <v>39.859757299999998</v>
       </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
       <c r="G40">
         <v>110.0637945</v>
       </c>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3">
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2">
         <f t="shared" si="5"/>
         <v>70.204037200000002</v>
       </c>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-      <c r="N40" s="2">
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1">
         <f>K40/SUM(K38:K41)</f>
         <v>0.28865819467539838</v>
       </c>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" t="s">
+      <c r="A41" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="3">
         <v>2040</v>
       </c>
       <c r="C41" t="s">
@@ -7171,29 +7507,29 @@
       <c r="D41">
         <v>53.642280266666603</v>
       </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
       <c r="G41">
         <v>128.84669966666601</v>
       </c>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3">
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2">
         <f t="shared" si="5"/>
         <v>75.204419399999409</v>
       </c>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2">
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1">
         <f>K41/SUM(K38:K41)</f>
         <v>0.30921828432418608</v>
       </c>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" t="s">
+      <c r="A42" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="3">
         <v>2045</v>
       </c>
       <c r="C42" t="s">
@@ -7202,29 +7538,29 @@
       <c r="D42">
         <v>238.62236933333301</v>
       </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
       <c r="G42">
         <v>296.78645699999998</v>
       </c>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3">
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2">
         <f t="shared" si="5"/>
         <v>58.164087666666973</v>
       </c>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2">
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1">
         <f>K42/SUM(K42:K45)</f>
         <v>0.15285316937789162</v>
       </c>
     </row>
     <row r="43" spans="1:14">
-      <c r="A43" t="s">
+      <c r="A43" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="3">
         <v>2045</v>
       </c>
       <c r="C43" t="s">
@@ -7233,29 +7569,29 @@
       <c r="D43">
         <v>60.299173000000003</v>
       </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
       <c r="G43">
         <v>116.07340139999999</v>
       </c>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3">
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2">
         <f t="shared" si="5"/>
         <v>55.774228399999991</v>
       </c>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
-      <c r="N43" s="2">
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1">
         <f>K43/SUM(K42:K45)</f>
         <v>0.14657270357963723</v>
       </c>
     </row>
     <row r="44" spans="1:14">
-      <c r="A44" t="s">
+      <c r="A44" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="3">
         <v>2045</v>
       </c>
       <c r="C44" t="s">
@@ -7264,29 +7600,29 @@
       <c r="D44">
         <v>97.315895233333293</v>
       </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
       <c r="G44">
         <v>214.53541633333299</v>
       </c>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3">
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2">
         <f t="shared" si="5"/>
         <v>117.2195210999997</v>
       </c>
-      <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
-      <c r="N44" s="2">
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1">
         <f>K44/SUM(K42:K45)</f>
         <v>0.30804876396886721</v>
       </c>
     </row>
     <row r="45" spans="1:14">
-      <c r="A45" t="s">
+      <c r="A45" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="3">
         <v>2045</v>
       </c>
       <c r="C45" t="s">
@@ -7295,29 +7631,29 @@
       <c r="D45">
         <v>188.42416009999999</v>
       </c>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
       <c r="G45">
         <v>337.78893756666599</v>
       </c>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3">
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2">
         <f t="shared" si="5"/>
         <v>149.364777466666</v>
       </c>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2">
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1">
         <f>K45/SUM(K42:K45)</f>
         <v>0.39252536307360403</v>
       </c>
     </row>
     <row r="46" spans="1:14">
-      <c r="A46" t="s">
+      <c r="A46" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="3">
         <v>2050</v>
       </c>
       <c r="C46" t="s">
@@ -7326,29 +7662,29 @@
       <c r="D46">
         <v>348.79311866666598</v>
       </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
       <c r="G46">
         <v>386.37448666666597</v>
       </c>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3">
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2">
         <f t="shared" si="5"/>
         <v>37.581367999999998</v>
       </c>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2">
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1">
         <f>K46/SUM(K46:K49)</f>
         <v>7.9254516693036001E-2</v>
       </c>
     </row>
     <row r="47" spans="1:14">
-      <c r="A47" t="s">
+      <c r="A47" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="3">
         <v>2050</v>
       </c>
       <c r="C47" t="s">
@@ -7357,29 +7693,29 @@
       <c r="D47">
         <v>229.705339966666</v>
       </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
       <c r="G47">
         <v>321.027063133333</v>
       </c>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3">
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2">
         <f t="shared" si="5"/>
         <v>91.321723166666999</v>
       </c>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
-      <c r="N47" s="2">
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1">
         <f>K47/SUM(K46:K49)</f>
         <v>0.19258636442264218</v>
       </c>
     </row>
     <row r="48" spans="1:14">
-      <c r="A48" t="s">
+      <c r="A48" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="3">
         <v>2050</v>
       </c>
       <c r="C48" t="s">
@@ -7388,29 +7724,29 @@
       <c r="D48">
         <v>345.10346199999998</v>
       </c>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
       <c r="G48">
         <v>518.30884966666599</v>
       </c>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3">
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2">
         <f t="shared" si="5"/>
         <v>173.20538766666601</v>
       </c>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
-      <c r="N48" s="2">
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1">
         <f>K48/SUM(K46:K49)</f>
         <v>0.36526901543742513</v>
       </c>
     </row>
     <row r="49" spans="1:14">
-      <c r="A49" t="s">
+      <c r="A49" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="3">
         <v>2050</v>
       </c>
       <c r="C49" t="s">
@@ -7419,52 +7755,52 @@
       <c r="D49">
         <v>576.39836760000003</v>
       </c>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
       <c r="G49">
         <v>748.47570893333295</v>
       </c>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3">
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2">
         <f t="shared" si="5"/>
         <v>172.07734133333292</v>
       </c>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2">
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1">
         <f>K49/SUM(K46:K49)</f>
         <v>0.36289010344689659</v>
       </c>
     </row>
     <row r="50" spans="1:14">
-      <c r="A50" t="s">
+      <c r="A50" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="3">
         <v>2025</v>
       </c>
       <c r="C50" t="s">
         <v>21</v>
       </c>
-      <c r="I50" s="3">
+      <c r="I50" s="2">
         <f>E50-$D50</f>
         <v>0</v>
       </c>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="2">
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="1">
         <f>I50/SUM(I50:I53)</f>
         <v>0</v>
       </c>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
     </row>
     <row r="51" spans="1:14">
-      <c r="A51" t="s">
+      <c r="A51" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="3">
         <v>2025</v>
       </c>
       <c r="C51" t="s">
@@ -7479,25 +7815,25 @@
       <c r="F51">
         <v>2312.5730481885798</v>
       </c>
-      <c r="G51" s="3"/>
-      <c r="I51" s="3">
+      <c r="G51" s="2"/>
+      <c r="I51" s="2">
         <f t="shared" ref="I51:I61" si="6">E51-$D51</f>
         <v>1558.6313294081401</v>
       </c>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="2">
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="1">
         <f>I51/SUM(I50:I53)</f>
         <v>0.87570969030373169</v>
       </c>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" t="s">
+      <c r="A52" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="3">
         <v>2025</v>
       </c>
       <c r="C52" t="s">
@@ -7512,25 +7848,25 @@
       <c r="F52">
         <v>178.51766454123899</v>
       </c>
-      <c r="G52" s="3"/>
-      <c r="I52" s="3">
+      <c r="G52" s="2"/>
+      <c r="I52" s="2">
         <f t="shared" si="6"/>
         <v>120.25571651228501</v>
       </c>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="2">
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="1">
         <f>I52/SUM(I50:I53)</f>
         <v>6.756510938620458E-2</v>
       </c>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
     </row>
     <row r="53" spans="1:14">
-      <c r="A53" t="s">
+      <c r="A53" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" t="s">
@@ -7545,60 +7881,60 @@
       <c r="F53">
         <v>61.891833647102899</v>
       </c>
-      <c r="G53" s="3"/>
-      <c r="I53" s="3">
+      <c r="G53" s="2"/>
+      <c r="I53" s="2">
         <f t="shared" si="6"/>
         <v>100.96231131067199</v>
       </c>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="2">
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="1">
         <f>I53/SUM(I50:I53)</f>
         <v>5.6725200310063631E-2</v>
       </c>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
     </row>
     <row r="54" spans="1:14">
-      <c r="A54" t="s">
+      <c r="A54" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="3">
         <v>2030</v>
       </c>
       <c r="C54" t="s">
         <v>21</v>
       </c>
-      <c r="I54" s="3">
+      <c r="I54" s="2">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J54" s="3">
-        <f t="shared" ref="J54:J65" si="7">F54-$D54</f>
+      <c r="J54" s="2">
+        <f t="shared" ref="J54:J61" si="7">F54-$D54</f>
         <v>0</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="2">
         <f t="shared" ref="K54:K73" si="8">G54-$D54</f>
         <v>0</v>
       </c>
-      <c r="L54" s="2">
+      <c r="L54" s="1">
         <f>I54/SUM(I54:I57)</f>
         <v>0</v>
       </c>
-      <c r="M54" s="2">
+      <c r="M54" s="1">
         <f>J54/SUM(J54:J57)</f>
         <v>0</v>
       </c>
-      <c r="N54" s="2">
+      <c r="N54" s="1">
         <f>K54/SUM(K54:K57)</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:14">
-      <c r="A55" t="s">
+      <c r="A55" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="3">
         <v>2030</v>
       </c>
       <c r="C55" t="s">
@@ -7616,36 +7952,36 @@
       <c r="G55">
         <v>10820.8510192745</v>
       </c>
-      <c r="I55" s="3">
+      <c r="I55" s="2">
         <f t="shared" si="6"/>
         <v>1315.5087946290801</v>
       </c>
-      <c r="J55" s="3">
+      <c r="J55" s="2">
         <f t="shared" si="7"/>
         <v>627.19632907997993</v>
       </c>
-      <c r="K55" s="3">
+      <c r="K55" s="2">
         <f t="shared" si="8"/>
         <v>8155.5512636090798</v>
       </c>
-      <c r="L55" s="2">
+      <c r="L55" s="1">
         <f>I55/SUM(I54:I57)</f>
         <v>0.79757159724043636</v>
       </c>
-      <c r="M55" s="2">
+      <c r="M55" s="1">
         <f>J55/SUM(J54:J57)</f>
         <v>0.79070944014070843</v>
       </c>
-      <c r="N55" s="2">
+      <c r="N55" s="1">
         <f>K55/SUM(K54:K57)</f>
         <v>0.80976703700442687</v>
       </c>
     </row>
     <row r="56" spans="1:14">
-      <c r="A56" t="s">
+      <c r="A56" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="3">
         <v>2030</v>
       </c>
       <c r="C56" t="s">
@@ -7663,36 +7999,36 @@
       <c r="G56">
         <v>1248.1796254824601</v>
       </c>
-      <c r="I56" s="3">
+      <c r="I56" s="2">
         <f t="shared" si="6"/>
         <v>152.95924702779905</v>
       </c>
-      <c r="J56" s="3">
+      <c r="J56" s="2">
         <f t="shared" si="7"/>
         <v>70.018566340300026</v>
       </c>
-      <c r="K56" s="3">
+      <c r="K56" s="2">
         <f t="shared" si="8"/>
         <v>948.62586906677006</v>
       </c>
-      <c r="L56" s="2">
+      <c r="L56" s="1">
         <f>I56/SUM(I54:I57)</f>
         <v>9.273670496368977E-2</v>
       </c>
-      <c r="M56" s="2">
+      <c r="M56" s="1">
         <f>J56/SUM(J54:J57)</f>
         <v>8.8272744631025482E-2</v>
       </c>
-      <c r="N56" s="2">
+      <c r="N56" s="1">
         <f>K56/SUM(K54:K57)</f>
         <v>9.4189336120978656E-2</v>
       </c>
     </row>
     <row r="57" spans="1:14">
-      <c r="A57" t="s">
+      <c r="A57" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="3">
         <v>2030</v>
       </c>
       <c r="C57" t="s">
@@ -7710,36 +8046,36 @@
       <c r="G57">
         <v>1151.0259360111399</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="2">
         <f t="shared" si="6"/>
         <v>180.924688952742</v>
       </c>
-      <c r="J57" s="3">
+      <c r="J57" s="2">
         <f t="shared" si="7"/>
         <v>95.992188294781016</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="2">
         <f t="shared" si="8"/>
         <v>967.30131843390393</v>
       </c>
-      <c r="L57" s="2">
+      <c r="L57" s="1">
         <f>I57/SUM(I54:I57)</f>
         <v>0.10969169779587402</v>
       </c>
-      <c r="M57" s="2">
+      <c r="M57" s="1">
         <f>J57/SUM(J54:J57)</f>
         <v>0.12101781522826606</v>
       </c>
-      <c r="N57" s="2">
+      <c r="N57" s="1">
         <f>K57/SUM(K54:K57)</f>
         <v>9.6043626874594487E-2</v>
       </c>
     </row>
     <row r="58" spans="1:14">
-      <c r="A58" t="s">
+      <c r="A58" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="3">
         <v>2035</v>
       </c>
       <c r="C58" t="s">
@@ -7748,36 +8084,36 @@
       <c r="D58">
         <v>1437.1253260359499</v>
       </c>
-      <c r="I58" s="3">
+      <c r="I58" s="2">
         <f t="shared" si="6"/>
         <v>-1437.1253260359499</v>
       </c>
-      <c r="J58" s="3">
+      <c r="J58" s="2">
         <f t="shared" si="7"/>
         <v>-1437.1253260359499</v>
       </c>
-      <c r="K58" s="3">
+      <c r="K58" s="2">
         <f t="shared" si="8"/>
         <v>-1437.1253260359499</v>
       </c>
-      <c r="L58" s="2">
+      <c r="L58" s="1">
         <f>I58/SUM(I58:I61)</f>
         <v>-0.37123459004366133</v>
       </c>
-      <c r="M58" s="2">
+      <c r="M58" s="1">
         <f>J58/SUM(J58:J61)</f>
         <v>-0.50762194036031305</v>
       </c>
-      <c r="N58" s="2">
+      <c r="N58" s="1">
         <f>K58/SUM(K58:K61)</f>
         <v>-3.8085919845583543E-2</v>
       </c>
     </row>
     <row r="59" spans="1:14">
-      <c r="A59" t="s">
+      <c r="A59" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="3">
         <v>2035</v>
       </c>
       <c r="C59" t="s">
@@ -7795,36 +8131,36 @@
       <c r="G59">
         <v>16338.8315783952</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="2">
         <f t="shared" si="6"/>
         <v>1966.1161345254002</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="2">
         <f t="shared" si="7"/>
         <v>1597.1478340482402</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="2">
         <f t="shared" si="8"/>
         <v>14426.815250951111</v>
       </c>
-      <c r="L59" s="2">
+      <c r="L59" s="1">
         <f>I59/SUM(I58:I61)</f>
         <v>0.50788216167064248</v>
       </c>
-      <c r="M59" s="2">
+      <c r="M59" s="1">
         <f>J59/SUM(J58:J61)</f>
         <v>0.564145149955807</v>
       </c>
-      <c r="N59" s="2">
+      <c r="N59" s="1">
         <f>K59/SUM(K58:K61)</f>
         <v>0.38233167234645299</v>
       </c>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" t="s">
+      <c r="A60" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="3">
         <v>2035</v>
       </c>
       <c r="C60" t="s">
@@ -7842,36 +8178,36 @@
       <c r="G60">
         <v>13219.904450419201</v>
       </c>
-      <c r="I60" s="3">
+      <c r="I60" s="2">
         <f t="shared" si="6"/>
         <v>1441.93965477143</v>
       </c>
-      <c r="J60" s="3">
+      <c r="J60" s="2">
         <f t="shared" si="7"/>
         <v>1122.6056532213802</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="2">
         <f t="shared" si="8"/>
         <v>11486.0048901639</v>
       </c>
-      <c r="L60" s="2">
+      <c r="L60" s="1">
         <f>I60/SUM(I58:I61)</f>
         <v>0.3724782153017181</v>
       </c>
-      <c r="M60" s="2">
+      <c r="M60" s="1">
         <f>J60/SUM(J58:J61)</f>
         <v>0.396527184946039</v>
       </c>
-      <c r="N60" s="2">
+      <c r="N60" s="1">
         <f>K60/SUM(K58:K61)</f>
         <v>0.30439590317387527</v>
       </c>
     </row>
     <row r="61" spans="1:14">
-      <c r="A61" t="s">
+      <c r="A61" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="3">
         <v>2035</v>
       </c>
       <c r="C61" t="s">
@@ -7889,61 +8225,61 @@
       <c r="G61">
         <v>15108.8404897418</v>
       </c>
-      <c r="I61" s="3">
+      <c r="I61" s="2">
         <f t="shared" si="6"/>
         <v>1900.27487314629</v>
       </c>
-      <c r="J61" s="3">
+      <c r="J61" s="2">
         <f t="shared" si="7"/>
         <v>1548.4656347040502</v>
       </c>
-      <c r="K61" s="3">
+      <c r="K61" s="2">
         <f t="shared" si="8"/>
         <v>13258.07482637019</v>
       </c>
-      <c r="L61" s="2">
+      <c r="L61" s="1">
         <f>I61/SUM(I58:I61)</f>
         <v>0.4908742130713008</v>
       </c>
-      <c r="M61" s="2">
+      <c r="M61" s="1">
         <f>J61/SUM(J58:J61)</f>
         <v>0.54694960545846705</v>
       </c>
-      <c r="N61" s="2">
+      <c r="N61" s="1">
         <f>K61/SUM(K58:K61)</f>
         <v>0.35135834432525526</v>
       </c>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" t="s">
+      <c r="A62" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="3">
         <v>2040</v>
       </c>
       <c r="C62" t="s">
         <v>21</v>
       </c>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3">
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L62" s="2"/>
-      <c r="M62" s="2"/>
-      <c r="N62" s="2">
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1">
         <f>K62/SUM(K62:K65)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:14">
-      <c r="A63" t="s">
+      <c r="A63" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="3">
         <v>2040</v>
       </c>
       <c r="C63" t="s">
@@ -7952,29 +8288,29 @@
       <c r="D63">
         <v>2776.2315145113698</v>
       </c>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
       <c r="G63">
         <v>17390.673329173602</v>
       </c>
-      <c r="I63" s="3"/>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3">
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2">
         <f t="shared" si="8"/>
         <v>14614.441814662232</v>
       </c>
-      <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2">
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1">
         <f>K63/SUM(K62:K65)</f>
         <v>0.29039686020406907</v>
       </c>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" t="s">
+      <c r="A64" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="3">
         <v>2040</v>
       </c>
       <c r="C64" t="s">
@@ -7983,29 +8319,29 @@
       <c r="D64">
         <v>2648.0605451709598</v>
       </c>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
       <c r="G64">
         <v>17478.450226044901</v>
       </c>
-      <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3">
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2">
         <f t="shared" si="8"/>
         <v>14830.389680873941</v>
       </c>
-      <c r="L64" s="2"/>
-      <c r="M64" s="2"/>
-      <c r="N64" s="2">
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1">
         <f>K64/SUM(K62:K65)</f>
         <v>0.29468786105863015</v>
       </c>
     </row>
     <row r="65" spans="1:14">
-      <c r="A65" t="s">
+      <c r="A65" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="3">
         <v>2040</v>
       </c>
       <c r="C65" t="s">
@@ -8014,54 +8350,54 @@
       <c r="D65">
         <v>4265.3844533396496</v>
       </c>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
       <c r="G65">
         <v>25146.309938758099</v>
       </c>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3">
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2">
         <f t="shared" si="8"/>
         <v>20880.925485418447</v>
       </c>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2">
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1">
         <f>K65/SUM(K62:K65)</f>
         <v>0.41491527873730083</v>
       </c>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" t="s">
+      <c r="A66" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="3">
         <v>2045</v>
       </c>
       <c r="C66" t="s">
         <v>21</v>
       </c>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="I66" s="3"/>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3">
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
-      <c r="N66" s="2">
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1">
         <f>K66/SUM(K66:K69)</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:14">
-      <c r="A67" t="s">
+      <c r="A67" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="3">
         <v>2045</v>
       </c>
       <c r="C67" t="s">
@@ -8070,29 +8406,29 @@
       <c r="D67">
         <v>3046.8072291071499</v>
       </c>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
       <c r="G67">
         <v>23143.659958120901</v>
       </c>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3">
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2">
         <f t="shared" si="8"/>
         <v>20096.85272901375</v>
       </c>
-      <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
-      <c r="N67" s="2">
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1">
         <f>K67/SUM(K66:K69)</f>
         <v>0.25503271729606303</v>
       </c>
     </row>
     <row r="68" spans="1:14">
-      <c r="A68" t="s">
+      <c r="A68" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="3">
         <v>2045</v>
       </c>
       <c r="C68" t="s">
@@ -8101,29 +8437,29 @@
       <c r="D68">
         <v>2795.2284845232698</v>
       </c>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
       <c r="G68">
         <v>22816.995727606401</v>
       </c>
-      <c r="I68" s="3"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3">
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2">
         <f t="shared" si="8"/>
         <v>20021.76724308313</v>
       </c>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2">
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1">
         <f>K68/SUM(K66:K69)</f>
         <v>0.2540798688195085</v>
       </c>
     </row>
     <row r="69" spans="1:14">
-      <c r="A69" t="s">
+      <c r="A69" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="3">
         <v>2045</v>
       </c>
       <c r="C69" t="s">
@@ -8132,54 +8468,54 @@
       <c r="D69">
         <v>6849.0991037536196</v>
       </c>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
       <c r="G69">
         <v>45531.555880110398</v>
       </c>
-      <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3">
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2">
         <f t="shared" si="8"/>
         <v>38682.456776356776</v>
       </c>
-      <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
-      <c r="N69" s="2">
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1">
         <f>K69/SUM(K66:K69)</f>
         <v>0.49088741388442836</v>
       </c>
     </row>
     <row r="70" spans="1:14">
-      <c r="A70" t="s">
+      <c r="A70" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="3">
         <v>2050</v>
       </c>
       <c r="C70" t="s">
         <v>21</v>
       </c>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3">
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
-      <c r="N70" s="2">
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1">
         <f>K70/SUM(K70:K73)</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:14">
-      <c r="A71" t="s">
+      <c r="A71" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="3">
         <v>2050</v>
       </c>
       <c r="C71" t="s">
@@ -8188,29 +8524,29 @@
       <c r="D71">
         <v>3836.8911031993998</v>
       </c>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
       <c r="G71">
         <v>31464.8265330295</v>
       </c>
-      <c r="I71" s="3"/>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3">
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2">
         <f t="shared" si="8"/>
         <v>27627.9354298301</v>
       </c>
-      <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
-      <c r="N71" s="2">
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1">
         <f>K71/SUM(K70:K73)</f>
         <v>0.24989232054808441</v>
       </c>
     </row>
     <row r="72" spans="1:14">
-      <c r="A72" t="s">
+      <c r="A72" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="3">
         <v>2050</v>
       </c>
       <c r="C72" t="s">
@@ -8219,29 +8555,29 @@
       <c r="D72">
         <v>3300.0470468808699</v>
       </c>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
       <c r="G72">
         <v>30242.557832135099</v>
       </c>
-      <c r="I72" s="3"/>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3">
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2">
         <f t="shared" si="8"/>
         <v>26942.510785254228</v>
       </c>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2">
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1">
         <f>K72/SUM(K70:K73)</f>
         <v>0.24369271307365198</v>
       </c>
     </row>
     <row r="73" spans="1:14">
-      <c r="A73" t="s">
+      <c r="A73" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="3">
         <v>2050</v>
       </c>
       <c r="C73" t="s">
@@ -8250,20 +8586,20 @@
       <c r="D73">
         <v>9711.1204938189003</v>
       </c>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
       <c r="G73">
         <v>65700.035883902106</v>
       </c>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3">
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2">
         <f t="shared" si="8"/>
         <v>55988.915390083203</v>
       </c>
-      <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2">
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+      <c r="N73" s="1">
         <f>K73/SUM(K70:K73)</f>
         <v>0.50641496637826355</v>
       </c>

--- a/data/data_analysis/procurement.xlsx
+++ b/data/data_analysis/procurement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C150FE-0663-41DB-A5D4-983EE0DEDB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C8A5C7-21C9-4D25-87B8-D230D85F779B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="40">
   <si>
     <t>Scenario</t>
   </si>
@@ -152,12 +152,24 @@
   <si>
     <t>Actual Budget</t>
   </si>
+  <si>
+    <t>Average Mix</t>
+  </si>
+  <si>
+    <t>Low Baseline</t>
+  </si>
+  <si>
+    <t>High Baseline</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,6 +189,14 @@
       <color rgb="FFA9B7C6"/>
       <name val="JetBrains Mono"/>
       <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -206,16 +226,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4655,7 +4676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B537AA0D-F5C4-4357-8465-DF25FED59988}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -4663,7 +4684,6 @@
     <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -4688,7 +4708,7 @@
       <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
       <c r="I1" t="s">
@@ -4709,7 +4729,7 @@
         <v>2025</v>
       </c>
       <c r="D2">
-        <f>E2+F2</f>
+        <f t="shared" ref="D2:D25" si="0">E2+F2</f>
         <v>22.65</v>
       </c>
       <c r="E2">
@@ -4719,11 +4739,11 @@
         <v>9.15</v>
       </c>
       <c r="G2" s="1">
-        <f>(D2-E2)/D2</f>
+        <f t="shared" ref="G2:G25" si="1">(D2-E2)/D2</f>
         <v>0.40397350993377479</v>
       </c>
-      <c r="H2" s="5">
-        <f>(J2-I2)/I2</f>
+      <c r="H2" s="4">
+        <f t="shared" ref="H2:H25" si="2">(J2-I2)/I2</f>
         <v>6.0606060606060606E-4</v>
       </c>
       <c r="I2">
@@ -4744,7 +4764,7 @@
         <v>2030</v>
       </c>
       <c r="D3">
-        <f>E3+F3</f>
+        <f t="shared" si="0"/>
         <v>38.921038279999998</v>
       </c>
       <c r="E3">
@@ -4754,11 +4774,11 @@
         <v>11.12</v>
       </c>
       <c r="G3" s="1">
-        <f>(D3-E3)/D3</f>
+        <f t="shared" si="1"/>
         <v>0.28570666383569043</v>
       </c>
-      <c r="H3" s="5">
-        <f>(J3-I3)/I3</f>
+      <c r="H3" s="4">
+        <f t="shared" si="2"/>
         <v>9.0909090909090905E-3</v>
       </c>
       <c r="I3">
@@ -4779,7 +4799,7 @@
         <v>2035</v>
       </c>
       <c r="D4">
-        <f>E4+F4</f>
+        <f t="shared" si="0"/>
         <v>72.201683639999999</v>
       </c>
       <c r="E4">
@@ -4789,11 +4809,11 @@
         <v>14.95</v>
       </c>
       <c r="G4" s="1">
-        <f>(D4-E4)/D4</f>
+        <f t="shared" si="1"/>
         <v>0.20705888348173698</v>
       </c>
-      <c r="H4" s="5">
-        <f>(J4-I4)/I4</f>
+      <c r="H4" s="4">
+        <f t="shared" si="2"/>
         <v>-2.2121212121212121E-2</v>
       </c>
       <c r="I4">
@@ -4814,7 +4834,7 @@
         <v>2030</v>
       </c>
       <c r="D5">
-        <f>E5+F5</f>
+        <f t="shared" si="0"/>
         <v>95.181038279999996</v>
       </c>
       <c r="E5">
@@ -4824,11 +4844,11 @@
         <v>67.38</v>
       </c>
       <c r="G5" s="1">
-        <f>(D5-E5)/D5</f>
+        <f t="shared" si="1"/>
         <v>0.70791410996992965</v>
       </c>
-      <c r="H5" s="5">
-        <f>(J5-I5)/I5</f>
+      <c r="H5" s="4">
+        <f t="shared" si="2"/>
         <v>7.7499999999999999E-3</v>
       </c>
       <c r="I5">
@@ -4849,7 +4869,7 @@
         <v>2035</v>
       </c>
       <c r="D6">
-        <f>E6+F6</f>
+        <f t="shared" si="0"/>
         <v>215.76168364</v>
       </c>
       <c r="E6">
@@ -4859,11 +4879,11 @@
         <v>158.51</v>
       </c>
       <c r="G6" s="1">
-        <f>(D6-E6)/D6</f>
+        <f t="shared" si="1"/>
         <v>0.73465314751842192</v>
       </c>
-      <c r="H6" s="5">
-        <f>(J6-I6)/I6</f>
+      <c r="H6" s="4">
+        <f t="shared" si="2"/>
         <v>2.7371428571428571E-2</v>
       </c>
       <c r="I6">
@@ -4884,7 +4904,7 @@
         <v>2040</v>
       </c>
       <c r="D7">
-        <f>E7+F7</f>
+        <f t="shared" si="0"/>
         <v>364.81046279999998</v>
       </c>
       <c r="E7">
@@ -4894,11 +4914,11 @@
         <v>246.91</v>
       </c>
       <c r="G7" s="1">
-        <f>(D7-E7)/D7</f>
+        <f t="shared" si="1"/>
         <v>0.67681721106601989</v>
       </c>
-      <c r="H7" s="5">
-        <f>(J7-I7)/I7</f>
+      <c r="H7" s="4">
+        <f t="shared" si="2"/>
         <v>4.1939999999999998E-2</v>
       </c>
       <c r="I7">
@@ -4919,7 +4939,7 @@
         <v>2045</v>
       </c>
       <c r="D8">
-        <f>E8+F8</f>
+        <f t="shared" si="0"/>
         <v>648.96668739999996</v>
       </c>
       <c r="E8">
@@ -4929,11 +4949,11 @@
         <v>406.17</v>
       </c>
       <c r="G8" s="1">
-        <f>(D8-E8)/D8</f>
+        <f t="shared" si="1"/>
         <v>0.62587187892072993</v>
       </c>
-      <c r="H8" s="5">
-        <f>(J8-I8)/I8</f>
+      <c r="H8" s="4">
+        <f t="shared" si="2"/>
         <v>2.4799999999999999E-2</v>
       </c>
       <c r="I8">
@@ -4954,7 +4974,7 @@
         <v>2050</v>
       </c>
       <c r="D9">
-        <f>E9+F9</f>
+        <f t="shared" si="0"/>
         <v>1078.26</v>
       </c>
       <c r="E9">
@@ -4964,11 +4984,11 @@
         <v>578.26</v>
       </c>
       <c r="G9" s="1">
-        <f>(D9-E9)/D9</f>
+        <f t="shared" si="1"/>
         <v>0.53628994862092627</v>
       </c>
-      <c r="H9" s="5">
-        <f>(J9-I9)/I9</f>
+      <c r="H9" s="4">
+        <f t="shared" si="2"/>
         <v>-2.3140000000000001E-2</v>
       </c>
       <c r="I9">
@@ -4989,7 +5009,7 @@
         <v>2025</v>
       </c>
       <c r="D10">
-        <f>E10+F10</f>
+        <f t="shared" si="0"/>
         <v>22.65</v>
       </c>
       <c r="E10">
@@ -4999,11 +5019,11 @@
         <v>9.15</v>
       </c>
       <c r="G10" s="1">
-        <f>(D10-E10)/D10</f>
+        <f t="shared" si="1"/>
         <v>0.40397350993377479</v>
       </c>
-      <c r="H10" s="5">
-        <f>(J10-I10)/I10</f>
+      <c r="H10" s="4">
+        <f t="shared" si="2"/>
         <v>6.0606060606060606E-4</v>
       </c>
       <c r="I10">
@@ -5024,7 +5044,7 @@
         <v>2030</v>
       </c>
       <c r="D11">
-        <f>E11+F11</f>
+        <f t="shared" si="0"/>
         <v>45.752613529999998</v>
       </c>
       <c r="E11">
@@ -5034,11 +5054,11 @@
         <v>11.12</v>
       </c>
       <c r="G11" s="1">
-        <f>(D11-E11)/D11</f>
+        <f t="shared" si="1"/>
         <v>0.24304622494862749</v>
       </c>
-      <c r="H11" s="5">
-        <f>(J11-I11)/I11</f>
+      <c r="H11" s="4">
+        <f t="shared" si="2"/>
         <v>1.090909090909091E-2</v>
       </c>
       <c r="I11">
@@ -5059,7 +5079,7 @@
         <v>2035</v>
       </c>
       <c r="D12">
-        <f>E12+F12</f>
+        <f t="shared" si="0"/>
         <v>103.69577185999999</v>
       </c>
       <c r="E12">
@@ -5069,11 +5089,11 @@
         <v>14.85</v>
       </c>
       <c r="G12" s="1">
-        <f>(D12-E12)/D12</f>
+        <f t="shared" si="1"/>
         <v>0.14320738187907053</v>
       </c>
-      <c r="H12" s="5">
-        <f>(J12-I12)/I12</f>
+      <c r="H12" s="4">
+        <f t="shared" si="2"/>
         <v>-2.0909090909090908E-2</v>
       </c>
       <c r="I12">
@@ -5094,7 +5114,7 @@
         <v>2030</v>
       </c>
       <c r="D13">
-        <f>E13+F13</f>
+        <f t="shared" si="0"/>
         <v>102.04261353</v>
       </c>
       <c r="E13">
@@ -5104,11 +5124,11 @@
         <v>67.41</v>
       </c>
       <c r="G13" s="1">
-        <f>(D13-E13)/D13</f>
+        <f t="shared" si="1"/>
         <v>0.66060636500829928</v>
       </c>
-      <c r="H13" s="5">
-        <f>(J13-I13)/I13</f>
+      <c r="H13" s="4">
+        <f t="shared" si="2"/>
         <v>8.3499999999999998E-3</v>
       </c>
       <c r="I13">
@@ -5129,7 +5149,7 @@
         <v>2035</v>
       </c>
       <c r="D14">
-        <f>E14+F14</f>
+        <f t="shared" si="0"/>
         <v>246.34577186000001</v>
       </c>
       <c r="E14">
@@ -5139,11 +5159,11 @@
         <v>157.5</v>
       </c>
       <c r="G14" s="1">
-        <f>(D14-E14)/D14</f>
+        <f t="shared" si="1"/>
         <v>0.63934525366852379</v>
       </c>
-      <c r="H14" s="5">
-        <f>(J14-I14)/I14</f>
+      <c r="H14" s="4">
+        <f t="shared" si="2"/>
         <v>4.3771428571428572E-2</v>
       </c>
       <c r="I14">
@@ -5164,7 +5184,7 @@
         <v>2040</v>
       </c>
       <c r="D15">
-        <f>E15+F15</f>
+        <f t="shared" si="0"/>
         <v>470.9930579</v>
       </c>
       <c r="E15">
@@ -5174,11 +5194,11 @@
         <v>243.07</v>
       </c>
       <c r="G15" s="1">
-        <f>(D15-E15)/D15</f>
+        <f t="shared" si="1"/>
         <v>0.51607979337055954</v>
       </c>
-      <c r="H15" s="5">
-        <f>(J15-I15)/I15</f>
+      <c r="H15" s="4">
+        <f t="shared" si="2"/>
         <v>0.11934</v>
       </c>
       <c r="I15">
@@ -5199,7 +5219,7 @@
         <v>2045</v>
       </c>
       <c r="D16">
-        <f>E16+F16</f>
+        <f t="shared" si="0"/>
         <v>965.18897609999999</v>
       </c>
       <c r="E16">
@@ -5209,11 +5229,11 @@
         <v>380.48</v>
       </c>
       <c r="G16" s="1">
-        <f>(D16-E16)/D16</f>
+        <f t="shared" si="1"/>
         <v>0.3942025959904662</v>
       </c>
-      <c r="H16" s="5">
-        <f>(J16-I16)/I16</f>
+      <c r="H16" s="4">
+        <f t="shared" si="2"/>
         <v>0.16401333333333334</v>
       </c>
       <c r="I16">
@@ -5234,7 +5254,7 @@
         <v>2050</v>
       </c>
       <c r="D17">
-        <f>E17+F17</f>
+        <f t="shared" si="0"/>
         <v>1974.19</v>
       </c>
       <c r="E17">
@@ -5244,11 +5264,11 @@
         <v>474.19</v>
       </c>
       <c r="G17" s="1">
-        <f>(D17-E17)/D17</f>
+        <f t="shared" si="1"/>
         <v>0.24019471276827462</v>
       </c>
-      <c r="H17" s="5">
-        <f>(J17-I17)/I17</f>
+      <c r="H17" s="4">
+        <f t="shared" si="2"/>
         <v>0.10825</v>
       </c>
       <c r="I17">
@@ -5269,7 +5289,7 @@
         <v>2025</v>
       </c>
       <c r="D18">
-        <f>E18+F18</f>
+        <f t="shared" si="0"/>
         <v>22.65</v>
       </c>
       <c r="E18">
@@ -5279,11 +5299,11 @@
         <v>9.15</v>
       </c>
       <c r="G18" s="1">
-        <f>(D18-E18)/D18</f>
+        <f t="shared" si="1"/>
         <v>0.40397350993377479</v>
       </c>
-      <c r="H18" s="5">
-        <f>(J18-I18)/I18</f>
+      <c r="H18" s="4">
+        <f t="shared" si="2"/>
         <v>-3.0303030303030303E-4</v>
       </c>
       <c r="I18">
@@ -5304,7 +5324,7 @@
         <v>2030</v>
       </c>
       <c r="D19">
-        <f>E19+F19</f>
+        <f t="shared" si="0"/>
         <v>30.40962717</v>
       </c>
       <c r="E19">
@@ -5314,11 +5334,11 @@
         <v>10.26</v>
       </c>
       <c r="G19" s="1">
-        <f>(D19-E19)/D19</f>
+        <f t="shared" si="1"/>
         <v>0.33739315324858032</v>
       </c>
-      <c r="H19" s="5">
-        <f>(J19-I19)/I19</f>
+      <c r="H19" s="4">
+        <f t="shared" si="2"/>
         <v>-7.575757575757576E-3</v>
       </c>
       <c r="I19">
@@ -5339,7 +5359,7 @@
         <v>2035</v>
       </c>
       <c r="D20">
-        <f>E20+F20</f>
+        <f t="shared" si="0"/>
         <v>44.244627790000003</v>
       </c>
       <c r="E20">
@@ -5349,11 +5369,11 @@
         <v>14.17</v>
       </c>
       <c r="G20" s="1">
-        <f>(D20-E20)/D20</f>
+        <f t="shared" si="1"/>
         <v>0.32026487073765486</v>
       </c>
-      <c r="H20" s="5">
-        <f>(J20-I20)/I20</f>
+      <c r="H20" s="4">
+        <f t="shared" si="2"/>
         <v>0.17303030303030303</v>
       </c>
       <c r="I20">
@@ -5374,7 +5394,7 @@
         <v>2030</v>
       </c>
       <c r="D21">
-        <f>E21+F21</f>
+        <f t="shared" si="0"/>
         <v>82.319627170000004</v>
       </c>
       <c r="E21">
@@ -5384,11 +5404,11 @@
         <v>62.17</v>
       </c>
       <c r="G21" s="1">
-        <f>(D21-E21)/D21</f>
+        <f t="shared" si="1"/>
         <v>0.75522693842637822</v>
       </c>
-      <c r="H21" s="5">
-        <f>(J21-I21)/I21</f>
+      <c r="H21" s="4">
+        <f t="shared" si="2"/>
         <v>-2.15E-3</v>
       </c>
       <c r="I21">
@@ -5409,7 +5429,7 @@
         <v>2035</v>
       </c>
       <c r="D22">
-        <f>E22+F22</f>
+        <f t="shared" si="0"/>
         <v>180.40462779000001</v>
       </c>
       <c r="E22">
@@ -5419,11 +5439,11 @@
         <v>150.33000000000001</v>
       </c>
       <c r="G22" s="1">
-        <f>(D22-E22)/D22</f>
+        <f t="shared" si="1"/>
         <v>0.83329347944993759</v>
       </c>
-      <c r="H22" s="5">
-        <f>(J22-I22)/I22</f>
+      <c r="H22" s="4">
+        <f t="shared" si="2"/>
         <v>7.8085714285714286E-2</v>
       </c>
       <c r="I22">
@@ -5444,7 +5464,7 @@
         <v>2040</v>
       </c>
       <c r="D23">
-        <f>E23+F23</f>
+        <f t="shared" si="0"/>
         <v>275.22833609000003</v>
       </c>
       <c r="E23">
@@ -5454,11 +5474,11 @@
         <v>230.34</v>
       </c>
       <c r="G23" s="1">
-        <f>(D23-E23)/D23</f>
+        <f t="shared" si="1"/>
         <v>0.83690510676443775</v>
       </c>
-      <c r="H23" s="5">
-        <f>(J23-I23)/I23</f>
+      <c r="H23" s="4">
+        <f t="shared" si="2"/>
         <v>6.4999999999999997E-3</v>
       </c>
       <c r="I23">
@@ -5479,7 +5499,7 @@
         <v>2045</v>
       </c>
       <c r="D24">
-        <f>E24+F24</f>
+        <f t="shared" si="0"/>
         <v>461.17875827</v>
       </c>
       <c r="E24">
@@ -5489,11 +5509,11 @@
         <v>394.18</v>
       </c>
       <c r="G24" s="1">
-        <f>(D24-E24)/D24</f>
+        <f t="shared" si="1"/>
         <v>0.85472280093443687</v>
       </c>
-      <c r="H24" s="5">
-        <f>(J24-I24)/I24</f>
+      <c r="H24" s="4">
+        <f t="shared" si="2"/>
         <v>5.0680000000000003E-2</v>
       </c>
       <c r="I24">
@@ -5514,7 +5534,7 @@
         <v>2050</v>
       </c>
       <c r="D25">
-        <f>E25+F25</f>
+        <f t="shared" si="0"/>
         <v>691.29</v>
       </c>
       <c r="E25">
@@ -5524,11 +5544,11 @@
         <v>591.29</v>
       </c>
       <c r="G25" s="1">
-        <f>(D25-E25)/D25</f>
+        <f t="shared" si="1"/>
         <v>0.85534290963271564</v>
       </c>
-      <c r="H25" s="5">
-        <f>(J25-I25)/I25</f>
+      <c r="H25" s="4">
+        <f t="shared" si="2"/>
         <v>0.10559</v>
       </c>
       <c r="I25">
@@ -5537,10 +5557,6 @@
       <c r="J25">
         <v>110559</v>
       </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="G26"/>
-      <c r="H26" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5741,10 +5757,10 @@
         <f t="shared" si="1"/>
         <v>0.46120303030303023</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>3302.97</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>1781</v>
       </c>
     </row>
@@ -5772,10 +5788,10 @@
         <f t="shared" si="1"/>
         <v>0.36212121212121212</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>3330</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>2135</v>
       </c>
     </row>
@@ -5803,10 +5819,10 @@
         <f t="shared" si="1"/>
         <v>0.35675000000000001</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>20155</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>13020</v>
       </c>
     </row>
@@ -5834,10 +5850,10 @@
         <f t="shared" si="1"/>
         <v>0.37008086253369277</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>1480</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>930.8</v>
       </c>
     </row>
@@ -5865,10 +5881,10 @@
         <f t="shared" si="1"/>
         <v>0.46101818181818172</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>3302.74</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <v>1781.38</v>
       </c>
     </row>
@@ -5886,8 +5902,8 @@
         <v>2030</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
@@ -5913,10 +5929,10 @@
         <f t="shared" si="1"/>
         <v>0.35863100000000003</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>20167</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <v>12994.38</v>
       </c>
     </row>
@@ -5944,10 +5960,10 @@
         <f t="shared" si="1"/>
         <v>0.37772083614295338</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>1502.36</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="5">
         <v>942.2</v>
       </c>
     </row>
@@ -5959,7 +5975,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB97F9D7-BF24-4FBB-A24F-14025D988DE1}">
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:X73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -5976,7 +5992,7 @@
     <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:24">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -6016,8 +6032,11 @@
       <c r="N1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -6031,16 +6050,26 @@
         <f>E2-$D2</f>
         <v>0</v>
       </c>
-      <c r="J2" s="2"/>
+      <c r="J2" s="2">
+        <f>F2-$D2</f>
+        <v>0</v>
+      </c>
       <c r="K2" s="2"/>
       <c r="L2" s="1">
         <f>I2/SUM(I2:I5)</f>
         <v>0</v>
       </c>
-      <c r="M2" s="1"/>
+      <c r="M2" s="1">
+        <f>J2/SUM(J2:J5)</f>
+        <v>0</v>
+      </c>
       <c r="N2" s="1"/>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" s="1">
+        <f>SUM(L2:N2)/2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -6050,32 +6079,61 @@
       <c r="C3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3">
         <v>12.302540506666601</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3">
         <v>20.75363917</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3">
         <v>12.38344833</v>
       </c>
-      <c r="G3" s="2">
-        <v>12.337415273333299</v>
-      </c>
+      <c r="G3" s="2"/>
       <c r="I3" s="2">
-        <f t="shared" ref="I3:I13" si="0">E3-$D3</f>
+        <f t="shared" ref="I3:J13" si="0">E3-$D3</f>
         <v>8.4510986633333989</v>
       </c>
-      <c r="J3" s="2"/>
+      <c r="J3" s="2">
+        <f t="shared" si="0"/>
+        <v>8.090782333339952E-2</v>
+      </c>
       <c r="K3" s="2"/>
       <c r="L3" s="1">
         <f>I3/SUM(I2:I5)</f>
         <v>0.91515732423128149</v>
       </c>
-      <c r="M3" s="1"/>
+      <c r="M3" s="1">
+        <f>J3/SUM(J2:J5)</f>
+        <v>1.2977666136557442</v>
+      </c>
       <c r="N3" s="1"/>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" s="1">
+        <f t="shared" ref="O3:O5" si="1">SUM(L3:N3)/2</f>
+        <v>1.1064619689435129</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="S3">
+        <v>2025</v>
+      </c>
+      <c r="T3">
+        <v>2030</v>
+      </c>
+      <c r="U3">
+        <v>2035</v>
+      </c>
+      <c r="V3">
+        <v>2040</v>
+      </c>
+      <c r="W3">
+        <v>2045</v>
+      </c>
+      <c r="X3">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -6085,32 +6143,68 @@
       <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4">
         <v>0.75969476000000002</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4">
         <v>1.26107314666666</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4">
         <v>0.74495450333333302</v>
       </c>
-      <c r="G4" s="2">
-        <v>0.74290502000000003</v>
-      </c>
+      <c r="G4" s="2"/>
       <c r="I4" s="2">
         <f t="shared" si="0"/>
         <v>0.50137838666666001</v>
       </c>
-      <c r="J4" s="2"/>
+      <c r="J4" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.4740256666667007E-2</v>
+      </c>
       <c r="K4" s="2"/>
       <c r="L4" s="1">
         <f>I4/SUM(I2:I5)</f>
         <v>5.4293544667750375E-2</v>
       </c>
-      <c r="M4" s="1"/>
+      <c r="M4" s="1">
+        <f>J4/SUM(J2:J5)</f>
+        <v>-0.23643465107063566</v>
+      </c>
       <c r="N4" s="1"/>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" s="1">
+        <f t="shared" si="1"/>
+        <v>-9.1070553201442639E-2</v>
+      </c>
+      <c r="R4" t="str">
+        <f>C2</f>
+        <v>BECCS</v>
+      </c>
+      <c r="S4" s="6">
+        <f>O2</f>
+        <v>0</v>
+      </c>
+      <c r="T4" s="6">
+        <f>O6</f>
+        <v>0.28862302163232018</v>
+      </c>
+      <c r="U4" s="6">
+        <f>O10</f>
+        <v>0.50833998109674294</v>
+      </c>
+      <c r="V4" s="6">
+        <f>O14</f>
+        <v>0.39032213669832749</v>
+      </c>
+      <c r="W4" s="6">
+        <f>O18</f>
+        <v>0.34646965147739606</v>
+      </c>
+      <c r="X4" s="6">
+        <f>O22</f>
+        <v>0.19206759514842348</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -6120,32 +6214,68 @@
       <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5">
         <v>0.17843507</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5">
         <v>0.46054363666666598</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5">
         <v>0.174611396666666</v>
       </c>
-      <c r="G5" s="2">
-        <v>0.173851956666666</v>
-      </c>
+      <c r="G5" s="2"/>
       <c r="I5" s="2">
         <f t="shared" si="0"/>
         <v>0.28210856666666595</v>
       </c>
-      <c r="J5" s="2"/>
+      <c r="J5" s="2">
+        <f t="shared" si="0"/>
+        <v>-3.8236733333339989E-3</v>
+      </c>
       <c r="K5" s="2"/>
       <c r="L5" s="1">
         <f>I5/SUM(I2:I5)</f>
         <v>3.0549131100968078E-2</v>
       </c>
-      <c r="M5" s="1"/>
+      <c r="M5" s="1">
+        <f>J5/SUM(J2:J5)</f>
+        <v>-6.1331962585108597E-2</v>
+      </c>
       <c r="N5" s="1"/>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" s="1">
+        <f t="shared" si="1"/>
+        <v>-1.539141574207026E-2</v>
+      </c>
+      <c r="R5" t="str">
+        <f t="shared" ref="R5:R7" si="2">C3</f>
+        <v>DAC</v>
+      </c>
+      <c r="S5" s="6">
+        <f t="shared" ref="S5:S7" si="3">O3</f>
+        <v>1.1064619689435129</v>
+      </c>
+      <c r="T5" s="6">
+        <f t="shared" ref="T5:T7" si="4">O7</f>
+        <v>0.5929693421530019</v>
+      </c>
+      <c r="U5" s="6">
+        <f t="shared" ref="U5:U7" si="5">O11</f>
+        <v>0.1154818819982039</v>
+      </c>
+      <c r="V5" s="6">
+        <f t="shared" ref="V5:V7" si="6">O15</f>
+        <v>0.1166881872151129</v>
+      </c>
+      <c r="W5" s="6">
+        <f t="shared" ref="W5:W7" si="7">O19</f>
+        <v>0.10659247817665984</v>
+      </c>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X7" si="8">O23</f>
+        <v>0.14658481606118351</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
@@ -6155,16 +6285,16 @@
       <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6">
         <v>8.65097456666666</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6">
         <v>11.925114263333301</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6">
         <v>10.037346550000001</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6">
         <v>29.0249384333333</v>
       </c>
       <c r="I6" s="2">
@@ -6172,11 +6302,11 @@
         <v>3.2741396966666407</v>
       </c>
       <c r="J6" s="2">
-        <f t="shared" ref="J6:K17" si="1">F6-$D6</f>
+        <f t="shared" ref="J6:K17" si="9">F6-$D6</f>
         <v>1.3863719833333406</v>
       </c>
       <c r="K6" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>20.373963866666642</v>
       </c>
       <c r="L6" s="1">
@@ -6191,8 +6321,40 @@
         <f>K6/SUM(K6:K9)</f>
         <v>0.30065410025493072</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" s="1">
+        <f>SUM(L6:N6)/3</f>
+        <v>0.28862302163232018</v>
+      </c>
+      <c r="R6" t="str">
+        <f t="shared" si="2"/>
+        <v>OEW</v>
+      </c>
+      <c r="S6" s="6">
+        <f t="shared" si="3"/>
+        <v>-9.1070553201442639E-2</v>
+      </c>
+      <c r="T6" s="6">
+        <f t="shared" si="4"/>
+        <v>6.8438242336358521E-2</v>
+      </c>
+      <c r="U6" s="6">
+        <f t="shared" si="5"/>
+        <v>0.19956787380658692</v>
+      </c>
+      <c r="V6" s="6">
+        <f t="shared" si="6"/>
+        <v>0.22621410870806635</v>
+      </c>
+      <c r="W6" s="6">
+        <f t="shared" si="7"/>
+        <v>0.20620832044060539</v>
+      </c>
+      <c r="X6" s="6">
+        <f t="shared" si="8"/>
+        <v>0.2466520748499603</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -6202,16 +6364,16 @@
       <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7">
         <v>15.9532513066666</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7">
         <v>22.5884521133333</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7">
         <v>19.007243493333299</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7">
         <v>55.595604350000002</v>
       </c>
       <c r="I7" s="2">
@@ -6219,11 +6381,11 @@
         <v>6.6352008066667008</v>
       </c>
       <c r="J7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>3.053992186666699</v>
       </c>
       <c r="K7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>39.642353043333401</v>
       </c>
       <c r="L7" s="1">
@@ -6238,8 +6400,40 @@
         <f>K7/SUM(K6:K9)</f>
         <v>0.58499347815824465</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" s="1">
+        <f t="shared" ref="O7:O13" si="10">SUM(L7:N7)/3</f>
+        <v>0.5929693421530019</v>
+      </c>
+      <c r="R7" t="str">
+        <f t="shared" si="2"/>
+        <v>TEW</v>
+      </c>
+      <c r="S7" s="6">
+        <f t="shared" si="3"/>
+        <v>-1.539141574207026E-2</v>
+      </c>
+      <c r="T7" s="6">
+        <f t="shared" si="4"/>
+        <v>4.9969393878319342E-2</v>
+      </c>
+      <c r="U7" s="6">
+        <f t="shared" si="5"/>
+        <v>0.1766102630984662</v>
+      </c>
+      <c r="V7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.26677556737849328</v>
+      </c>
+      <c r="W7" s="6">
+        <f t="shared" si="7"/>
+        <v>0.34072954990533866</v>
+      </c>
+      <c r="X7" s="6">
+        <f t="shared" si="8"/>
+        <v>0.41469551394043275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -6249,16 +6443,16 @@
       <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8">
         <v>1.8031504333333299</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8">
         <v>2.57378616</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8">
         <v>2.1532217299999998</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8">
         <v>6.3818963266666602</v>
       </c>
       <c r="I8" s="2">
@@ -6266,11 +6460,11 @@
         <v>0.77063572666667013</v>
       </c>
       <c r="J8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>0.35007129666666992</v>
       </c>
       <c r="K8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>4.5787458933333305</v>
       </c>
       <c r="L8" s="1">
@@ -6285,8 +6479,39 @@
         <f>K8/SUM(K6:K9)</f>
         <v>6.7567545317401126E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" s="1">
+        <f t="shared" si="10"/>
+        <v>6.8438242336358521E-2</v>
+      </c>
+      <c r="R8" t="s">
+        <v>39</v>
+      </c>
+      <c r="S8" s="6">
+        <f>SUM(S4:S7)</f>
+        <v>1</v>
+      </c>
+      <c r="T8" s="6">
+        <f t="shared" ref="T8:X8" si="11">SUM(T4:T7)</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="U8" s="6">
+        <f t="shared" si="11"/>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="V8" s="6">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="W8" s="6">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="X8" s="6">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
       <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
@@ -6296,16 +6521,16 @@
       <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9">
         <v>0.93724469666666599</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9">
         <v>1.53723203333333</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9">
         <v>1.1890160333333299</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9">
         <v>4.1076434300000004</v>
       </c>
       <c r="I9" s="2">
@@ -6313,11 +6538,11 @@
         <v>0.59998733666666404</v>
       </c>
       <c r="J9" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>0.25177133666666396</v>
       </c>
       <c r="K9" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>3.1703987333333346</v>
       </c>
       <c r="L9" s="1">
@@ -6332,8 +6557,12 @@
         <f>K9/SUM(K6:K9)</f>
         <v>4.6784876269423577E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" s="1">
+        <f t="shared" si="10"/>
+        <v>4.9969393878319342E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
       <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
@@ -6343,16 +6572,16 @@
       <c r="C10" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10">
         <v>32.8174128333333</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10">
         <v>40.421700000000001</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10">
         <v>37.7868285666666</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10">
         <v>114.596670466666</v>
       </c>
       <c r="I10" s="2">
@@ -6360,11 +6589,11 @@
         <v>7.6042871666667011</v>
       </c>
       <c r="J10" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>4.9694157333332996</v>
       </c>
       <c r="K10" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>81.779257633332691</v>
       </c>
       <c r="L10" s="1">
@@ -6379,8 +6608,39 @@
         <f>K10/SUM(K10:K13)</f>
         <v>0.51852648076029639</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" s="1">
+        <f t="shared" si="10"/>
+        <v>0.50833998109674294</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="S10">
+        <f>S3</f>
+        <v>2025</v>
+      </c>
+      <c r="T10">
+        <f>T3</f>
+        <v>2030</v>
+      </c>
+      <c r="U10">
+        <f>U3</f>
+        <v>2035</v>
+      </c>
+      <c r="V10">
+        <f>V3</f>
+        <v>2040</v>
+      </c>
+      <c r="W10">
+        <f>W3</f>
+        <v>2045</v>
+      </c>
+      <c r="X10">
+        <f>X3</f>
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
       <c r="A11" s="3" t="s">
         <v>6</v>
       </c>
@@ -6390,16 +6650,16 @@
       <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11">
         <v>6.3966195333333298</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11">
         <v>8.06076223333333</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11">
         <v>7.4923460333333303</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11">
         <v>26.1684194933333</v>
       </c>
       <c r="I11" s="2">
@@ -6407,11 +6667,11 @@
         <v>1.6641427000000002</v>
       </c>
       <c r="J11" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>1.0957265000000005</v>
       </c>
       <c r="K11" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>19.771799959999971</v>
       </c>
       <c r="L11" s="1">
@@ -6426,8 +6686,40 @@
         <f>K11/SUM(K10:K13)</f>
         <v>0.12536433012784678</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" s="1">
+        <f t="shared" si="10"/>
+        <v>0.1154818819982039</v>
+      </c>
+      <c r="R11" t="str">
+        <f>R4</f>
+        <v>BECCS</v>
+      </c>
+      <c r="S11" s="6">
+        <f>O26</f>
+        <v>0</v>
+      </c>
+      <c r="T11" s="6">
+        <f>O30</f>
+        <v>0.2788249200253905</v>
+      </c>
+      <c r="U11" s="6">
+        <f>O34</f>
+        <v>0.46823589811557143</v>
+      </c>
+      <c r="V11" s="6">
+        <f>O38</f>
+        <v>0.26041637593067141</v>
+      </c>
+      <c r="W11" s="6">
+        <f>O42</f>
+        <v>0.15285316937789162</v>
+      </c>
+      <c r="X11" s="6">
+        <f>O46</f>
+        <v>7.9254516693036001E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
       <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
@@ -6437,16 +6729,16 @@
       <c r="C12" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12">
         <v>8.9131753333333297</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12">
         <v>11.88907687</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12">
         <v>11.058108819999999</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12">
         <v>38.070494366666601</v>
       </c>
       <c r="I12" s="2">
@@ -6454,11 +6746,11 @@
         <v>2.9759015366666706</v>
       </c>
       <c r="J12" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>2.1449334866666696</v>
       </c>
       <c r="K12" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>29.157319033333273</v>
       </c>
       <c r="L12" s="1">
@@ -6473,8 +6765,40 @@
         <f>K12/SUM(K10:K13)</f>
         <v>0.1848737988616464</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" s="1">
+        <f t="shared" si="10"/>
+        <v>0.19956787380658692</v>
+      </c>
+      <c r="R12" t="str">
+        <f>R5</f>
+        <v>DAC</v>
+      </c>
+      <c r="S12" s="6">
+        <f>O27</f>
+        <v>1.1046840333110053</v>
+      </c>
+      <c r="T12" s="6">
+        <f>O31</f>
+        <v>0.59718983726713759</v>
+      </c>
+      <c r="U12" s="6">
+        <f>O35</f>
+        <v>0.12113894109271006</v>
+      </c>
+      <c r="V12" s="6">
+        <f>O39</f>
+        <v>0.14170714506974419</v>
+      </c>
+      <c r="W12" s="6">
+        <f>O43</f>
+        <v>0.14657270357963723</v>
+      </c>
+      <c r="X12" s="6">
+        <f>O47</f>
+        <v>0.19258636442264218</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
       <c r="A13" s="3" t="s">
         <v>6</v>
       </c>
@@ -6484,16 +6808,16 @@
       <c r="C13" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13">
         <v>8.8559258333333304</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13">
         <v>11.481298839999999</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13">
         <v>10.683070016666599</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13">
         <v>35.862267099999997</v>
       </c>
       <c r="I13" s="2">
@@ -6501,11 +6825,11 @@
         <v>2.6253730066666687</v>
       </c>
       <c r="J13" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>1.8271441833332691</v>
       </c>
       <c r="K13" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>27.006341266666666</v>
       </c>
       <c r="L13" s="1">
@@ -6520,8 +6844,40 @@
         <f>K13/SUM(K10:K13)</f>
         <v>0.17123539025021053</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" s="1">
+        <f t="shared" si="10"/>
+        <v>0.1766102630984662</v>
+      </c>
+      <c r="R13" t="str">
+        <f>R6</f>
+        <v>OEW</v>
+      </c>
+      <c r="S13" s="6">
+        <f>O28</f>
+        <v>-8.7905321380154999E-2</v>
+      </c>
+      <c r="T13" s="6">
+        <f>O32</f>
+        <v>7.0774412070130452E-2</v>
+      </c>
+      <c r="U13" s="6">
+        <f>O36</f>
+        <v>0.22200081594740231</v>
+      </c>
+      <c r="V13" s="6">
+        <f>O40</f>
+        <v>0.28865819467539838</v>
+      </c>
+      <c r="W13" s="6">
+        <f>O44</f>
+        <v>0.30804876396886721</v>
+      </c>
+      <c r="X13" s="6">
+        <f>O48</f>
+        <v>0.36526901543742513</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
       <c r="A14" s="3" t="s">
         <v>6</v>
       </c>
@@ -6531,22 +6887,18 @@
       <c r="C14" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14">
         <v>59.1438998333333</v>
       </c>
-      <c r="E14" s="2">
-        <v>56.976563966666603</v>
-      </c>
-      <c r="F14" s="2">
-        <v>56.951071833333302</v>
-      </c>
-      <c r="G14" s="2">
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14">
         <v>154.085919166666</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>94.942019333332695</v>
       </c>
       <c r="L14" s="1"/>
@@ -6555,8 +6907,40 @@
         <f>K14/SUM(K14:K17)</f>
         <v>0.39032213669832749</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" s="6">
+        <f>N14</f>
+        <v>0.39032213669832749</v>
+      </c>
+      <c r="R14" t="str">
+        <f>R7</f>
+        <v>TEW</v>
+      </c>
+      <c r="S14" s="6">
+        <f>O29</f>
+        <v>-1.6778711930850287E-2</v>
+      </c>
+      <c r="T14" s="6">
+        <f>O33</f>
+        <v>5.3210830637341631E-2</v>
+      </c>
+      <c r="U14" s="6">
+        <f>O37</f>
+        <v>0.1886243448443162</v>
+      </c>
+      <c r="V14" s="6">
+        <f>O41</f>
+        <v>0.30921828432418608</v>
+      </c>
+      <c r="W14" s="6">
+        <f>O45</f>
+        <v>0.39252536307360403</v>
+      </c>
+      <c r="X14" s="6">
+        <f>O49</f>
+        <v>0.36289010344689659</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
       <c r="A15" s="3" t="s">
         <v>6</v>
       </c>
@@ -6566,22 +6950,18 @@
       <c r="C15" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15">
         <v>11.3755561333333</v>
       </c>
-      <c r="E15" s="2">
-        <v>11.1483247333333</v>
-      </c>
-      <c r="F15" s="2">
-        <v>11.153745166666599</v>
-      </c>
-      <c r="G15" s="2">
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15">
         <v>39.758809566666599</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>28.383253433333302</v>
       </c>
       <c r="L15" s="1"/>
@@ -6590,8 +6970,36 @@
         <f>K15/SUM(K14:K17)</f>
         <v>0.1166881872151129</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" s="6">
+        <f t="shared" ref="O15:O25" si="12">N15</f>
+        <v>0.1166881872151129</v>
+      </c>
+      <c r="S15" s="6">
+        <f>SUM(S11:S14)</f>
+        <v>1</v>
+      </c>
+      <c r="T15" s="6">
+        <f t="shared" ref="T15" si="13">SUM(T11:T14)</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="U15" s="6">
+        <f t="shared" ref="U15" si="14">SUM(U11:U14)</f>
+        <v>1</v>
+      </c>
+      <c r="V15" s="6">
+        <f t="shared" ref="V15" si="15">SUM(V11:V14)</f>
+        <v>1</v>
+      </c>
+      <c r="W15" s="6">
+        <f t="shared" ref="W15" si="16">SUM(W11:W14)</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="X15" s="6">
+        <f t="shared" ref="X15" si="17">SUM(X11:X14)</f>
+        <v>0.99999999999999978</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24">
       <c r="A16" s="3" t="s">
         <v>6</v>
       </c>
@@ -6601,22 +7009,18 @@
       <c r="C16" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16">
         <v>19.689983866666601</v>
       </c>
-      <c r="E16" s="2">
-        <v>21.142851033333301</v>
-      </c>
-      <c r="F16" s="2">
-        <v>21.151816766666599</v>
-      </c>
-      <c r="G16" s="2">
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16">
         <v>74.714340066666594</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>55.024356199999993</v>
       </c>
       <c r="L16" s="1"/>
@@ -6625,8 +7029,12 @@
         <f>K16/SUM(K14:K17)</f>
         <v>0.22621410870806635</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" s="6">
+        <f t="shared" si="12"/>
+        <v>0.22621410870806635</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="3" t="s">
         <v>6</v>
       </c>
@@ -6636,22 +7044,18 @@
       <c r="C17" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17">
         <v>27.481140133333302</v>
       </c>
-      <c r="E17" s="2">
-        <v>28.4615771</v>
-      </c>
-      <c r="F17" s="2">
-        <v>28.472625499999999</v>
-      </c>
-      <c r="G17" s="2">
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17">
         <v>92.371672066666605</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>64.890531933333307</v>
       </c>
       <c r="L17" s="1"/>
@@ -6660,8 +7064,12 @@
         <f>K17/SUM(K14:K17)</f>
         <v>0.26677556737849328</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" s="6">
+        <f t="shared" si="12"/>
+        <v>0.26677556737849328</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="3" t="s">
         <v>6</v>
       </c>
@@ -6671,22 +7079,18 @@
       <c r="C18" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18">
         <v>110.52516749999999</v>
       </c>
-      <c r="E18" s="2">
-        <v>105.954286533333</v>
-      </c>
-      <c r="F18" s="2">
-        <v>105.939343766666</v>
-      </c>
-      <c r="G18" s="2">
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18">
         <v>242.41138166666599</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2">
-        <f t="shared" ref="K18:K25" si="2">G18-$D18</f>
+        <f t="shared" ref="K18:K25" si="18">G18-$D18</f>
         <v>131.88621416666598</v>
       </c>
       <c r="L18" s="1"/>
@@ -6695,8 +7099,12 @@
         <f>K18/SUM(K18:K21)</f>
         <v>0.34646965147739606</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" s="6">
+        <f t="shared" si="12"/>
+        <v>0.34646965147739606</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="3" t="s">
         <v>6</v>
       </c>
@@ -6706,22 +7114,18 @@
       <c r="C19" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19">
         <v>22.4968641333333</v>
       </c>
-      <c r="E19" s="2">
-        <v>21.9651751</v>
-      </c>
-      <c r="F19" s="2">
-        <v>21.967353466666601</v>
-      </c>
-      <c r="G19" s="2">
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19">
         <v>63.072072800000001</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="18"/>
         <v>40.575208666666697</v>
       </c>
       <c r="L19" s="1"/>
@@ -6730,8 +7134,12 @@
         <f>K19/SUM(K18:K21)</f>
         <v>0.10659247817665984</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19" s="6">
+        <f t="shared" si="12"/>
+        <v>0.10659247817665984</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="3" t="s">
         <v>6</v>
       </c>
@@ -6741,22 +7149,18 @@
       <c r="C20" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20">
         <v>33.472099466666599</v>
       </c>
-      <c r="E20" s="2">
-        <v>35.921076766666602</v>
-      </c>
-      <c r="F20" s="2">
-        <v>35.926912266666598</v>
-      </c>
-      <c r="G20" s="2">
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20">
         <v>111.966809166666</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="18"/>
         <v>78.49470969999939</v>
       </c>
       <c r="L20" s="1"/>
@@ -6765,8 +7169,12 @@
         <f>K20/SUM(K18:K21)</f>
         <v>0.20620832044060539</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" s="6">
+        <f t="shared" si="12"/>
+        <v>0.20620832044060539</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="3" t="s">
         <v>6</v>
       </c>
@@ -6776,22 +7184,18 @@
       <c r="C21" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21">
         <v>76.120413600000006</v>
       </c>
-      <c r="E21" s="2">
-        <v>78.775144066666599</v>
-      </c>
-      <c r="F21" s="2">
-        <v>78.782043999999999</v>
-      </c>
-      <c r="G21" s="2">
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21">
         <v>205.82161600000001</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="18"/>
         <v>129.7012024</v>
       </c>
       <c r="L21" s="1"/>
@@ -6800,8 +7204,12 @@
         <f>K21/SUM(K18:K21)</f>
         <v>0.34072954990533866</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21" s="6">
+        <f t="shared" si="12"/>
+        <v>0.34072954990533866</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
@@ -6811,22 +7219,18 @@
       <c r="C22" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22">
         <v>206.888348333333</v>
       </c>
-      <c r="E22" s="2">
-        <v>198.573914</v>
-      </c>
-      <c r="F22" s="2">
-        <v>198.586344</v>
-      </c>
-      <c r="G22" s="2">
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22">
         <v>297.99930599999999</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="18"/>
         <v>91.110957666666991</v>
       </c>
       <c r="L22" s="1"/>
@@ -6835,8 +7239,12 @@
         <f>K22/SUM(K22:K25)</f>
         <v>0.19206759514842348</v>
       </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22" s="6">
+        <f t="shared" si="12"/>
+        <v>0.19206759514842348</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="3" t="s">
         <v>6</v>
       </c>
@@ -6846,22 +7254,18 @@
       <c r="C23" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23">
         <v>49.988974566666599</v>
       </c>
-      <c r="E23" s="2">
-        <v>48.593891499999998</v>
-      </c>
-      <c r="F23" s="2">
-        <v>48.593863266666602</v>
-      </c>
-      <c r="G23" s="2">
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23">
         <v>119.52430123333301</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="18"/>
         <v>69.535326666666407</v>
       </c>
       <c r="L23" s="1"/>
@@ -6870,8 +7274,12 @@
         <f>K23/SUM(K22:K25)</f>
         <v>0.14658481606118351</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23" s="6">
+        <f t="shared" si="12"/>
+        <v>0.14658481606118351</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="3" t="s">
         <v>6</v>
       </c>
@@ -6881,22 +7289,18 @@
       <c r="C24" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24">
         <v>65.061545266666599</v>
       </c>
-      <c r="E24" s="2">
-        <v>69.434285799999998</v>
-      </c>
-      <c r="F24" s="2">
-        <v>69.436308333333301</v>
-      </c>
-      <c r="G24" s="2">
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24">
         <v>182.065700666666</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="18"/>
         <v>117.00415539999941</v>
       </c>
       <c r="L24" s="1"/>
@@ -6905,8 +7309,12 @@
         <f>K24/SUM(K22:K25)</f>
         <v>0.2466520748499603</v>
       </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24" s="6">
+        <f t="shared" si="12"/>
+        <v>0.2466520748499603</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="3" t="s">
         <v>6</v>
       </c>
@@ -6916,22 +7324,18 @@
       <c r="C25" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25">
         <v>177.878598333333</v>
       </c>
-      <c r="E25" s="2">
-        <v>183.20800850000001</v>
-      </c>
-      <c r="F25" s="2">
-        <v>183.19356916666601</v>
-      </c>
-      <c r="G25" s="2">
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25">
         <v>374.59739093333297</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="18"/>
         <v>196.71879259999997</v>
       </c>
       <c r="L25" s="1"/>
@@ -6940,8 +7344,12 @@
         <f>K25/SUM(K22:K25)</f>
         <v>0.41469551394043275</v>
       </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25" s="6">
+        <f t="shared" si="12"/>
+        <v>0.41469551394043275</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="3" t="s">
         <v>9</v>
       </c>
@@ -6955,16 +7363,26 @@
         <f>E26-$D26</f>
         <v>0</v>
       </c>
-      <c r="J26" s="2"/>
+      <c r="J26" s="2">
+        <f>F26-$D26</f>
+        <v>0</v>
+      </c>
       <c r="K26" s="2"/>
       <c r="L26" s="1">
         <f>I26/SUM(I26:I29)</f>
         <v>0</v>
       </c>
-      <c r="M26" s="1"/>
+      <c r="M26" s="1">
+        <f>J26/SUM(J26:J29)</f>
+        <v>0</v>
+      </c>
       <c r="N26" s="1"/>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26" s="1">
+        <f>SUM(L26:N26)/2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="3" t="s">
         <v>9</v>
       </c>
@@ -6978,24 +7396,36 @@
         <v>12.3018890866666</v>
       </c>
       <c r="E27">
-        <v>20.753885093333299</v>
-      </c>
-      <c r="F27" s="2"/>
+        <v>20.753807836666599</v>
+      </c>
+      <c r="F27">
+        <v>12.383095450000001</v>
+      </c>
       <c r="G27" s="2"/>
       <c r="I27" s="2">
-        <f t="shared" ref="I27:I37" si="3">E27-$D27</f>
-        <v>8.4519960066666986</v>
-      </c>
-      <c r="J27" s="2"/>
+        <f t="shared" ref="I27:J37" si="19">E27-$D27</f>
+        <v>8.451918749999999</v>
+      </c>
+      <c r="J27" s="2">
+        <f t="shared" si="19"/>
+        <v>8.1206363333400589E-2</v>
+      </c>
       <c r="K27" s="2"/>
       <c r="L27" s="1">
         <f>I27/SUM(I26:I29)</f>
-        <v>0.91523639156372061</v>
-      </c>
-      <c r="M27" s="1"/>
+        <v>0.91522866165137384</v>
+      </c>
+      <c r="M27" s="1">
+        <f>J27/SUM(J26:J29)</f>
+        <v>1.2941394049706367</v>
+      </c>
       <c r="N27" s="1"/>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27" s="1">
+        <f t="shared" ref="O27:O29" si="20">SUM(L27:N27)/2</f>
+        <v>1.1046840333110053</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="3" t="s">
         <v>9</v>
       </c>
@@ -7009,24 +7439,36 @@
         <v>0.76009263000000005</v>
       </c>
       <c r="E28">
-        <v>1.2608490400000001</v>
-      </c>
-      <c r="F28" s="2"/>
+        <v>1.2609590399999999</v>
+      </c>
+      <c r="F28">
+        <v>0.74565729333333297</v>
+      </c>
       <c r="G28" s="2"/>
       <c r="I28" s="2">
-        <f t="shared" si="3"/>
-        <v>0.50075641000000004</v>
-      </c>
-      <c r="J28" s="2"/>
+        <f t="shared" si="19"/>
+        <v>0.50086640999999987</v>
+      </c>
+      <c r="J28" s="2">
+        <f t="shared" si="19"/>
+        <v>-1.4435336666667076E-2</v>
+      </c>
       <c r="K28" s="2"/>
       <c r="L28" s="1">
         <f>I28/SUM(I26:I29)</f>
-        <v>5.4225119058184668E-2</v>
-      </c>
-      <c r="M28" s="1"/>
+        <v>5.4237068250381396E-2</v>
+      </c>
+      <c r="M28" s="1">
+        <f>J28/SUM(J26:J29)</f>
+        <v>-0.23004771101069138</v>
+      </c>
       <c r="N28" s="1"/>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28" s="1">
+        <f t="shared" si="20"/>
+        <v>-8.7905321380154999E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" s="3" t="s">
         <v>9</v>
       </c>
@@ -7040,24 +7482,36 @@
         <v>0.17853032999999999</v>
       </c>
       <c r="E29">
-        <v>0.46054620333333302</v>
-      </c>
-      <c r="F29" s="2"/>
+        <v>0.46050704333333298</v>
+      </c>
+      <c r="F29">
+        <v>0.17450862</v>
+      </c>
       <c r="G29" s="2"/>
       <c r="I29" s="2">
-        <f t="shared" si="3"/>
-        <v>0.282015873333333</v>
-      </c>
-      <c r="J29" s="2"/>
+        <f t="shared" si="19"/>
+        <v>0.28197671333333296</v>
+      </c>
+      <c r="J29" s="2">
+        <f t="shared" si="19"/>
+        <v>-4.0217099999999839E-3</v>
+      </c>
       <c r="K29" s="2"/>
       <c r="L29" s="1">
         <f>I29/SUM(I26:I29)</f>
-        <v>3.0538489378094842E-2</v>
-      </c>
-      <c r="M29" s="1"/>
+        <v>3.0534270098244786E-2</v>
+      </c>
+      <c r="M29" s="1">
+        <f>J29/SUM(J26:J29)</f>
+        <v>-6.4091693959945364E-2</v>
+      </c>
       <c r="N29" s="1"/>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29" s="1">
+        <f t="shared" si="20"/>
+        <v>-1.6778711930850287E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" s="3" t="s">
         <v>9</v>
       </c>
@@ -7070,23 +7524,31 @@
       <c r="D30">
         <v>10.8468415733333</v>
       </c>
-      <c r="E30" s="2"/>
+      <c r="E30">
+        <v>14.043595646666599</v>
+      </c>
       <c r="F30">
         <v>12.15459806</v>
       </c>
       <c r="G30">
         <v>30.969142233333301</v>
       </c>
-      <c r="I30" s="2"/>
+      <c r="I30" s="2">
+        <f t="shared" ref="I30:J37" si="21">E30-$D30</f>
+        <v>3.1967540733332989</v>
+      </c>
       <c r="J30" s="2">
-        <f t="shared" ref="J30:J37" si="4">F30-$D30</f>
+        <f t="shared" si="21"/>
         <v>1.3077564866666993</v>
       </c>
       <c r="K30" s="2">
-        <f t="shared" ref="K30:K49" si="5">G30-$D30</f>
+        <f t="shared" ref="K30:K49" si="22">G30-$D30</f>
         <v>20.122300660000001</v>
       </c>
-      <c r="L30" s="1"/>
+      <c r="L30" s="1">
+        <f>I30/SUM(I30:I33)</f>
+        <v>0.28311522339768491</v>
+      </c>
       <c r="M30" s="1">
         <f>J30/SUM(J30:J33)</f>
         <v>0.25618436552952295</v>
@@ -7095,8 +7557,12 @@
         <f>K30/SUM(K30:K33)</f>
         <v>0.29717517114896358</v>
       </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="O30" s="1">
+        <f>SUM(L30:N30)/3</f>
+        <v>0.2788249200253905</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" s="3" t="s">
         <v>9</v>
       </c>
@@ -7109,23 +7575,31 @@
       <c r="D31">
         <v>19.872583573333301</v>
       </c>
-      <c r="E31" s="2"/>
+      <c r="E31">
+        <v>26.5729671166666</v>
+      </c>
       <c r="F31">
         <v>22.984575606666599</v>
       </c>
       <c r="G31">
         <v>59.723357540000002</v>
       </c>
-      <c r="I31" s="2"/>
+      <c r="I31" s="2">
+        <f t="shared" si="21"/>
+        <v>6.7003835433332988</v>
+      </c>
       <c r="J31" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>3.1119920333332978</v>
       </c>
       <c r="K31" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>39.850773966666701</v>
       </c>
-      <c r="L31" s="1"/>
+      <c r="L31" s="1">
+        <f>I31/SUM(I30:I33)</f>
+        <v>0.59340835741642495</v>
+      </c>
       <c r="M31" s="1">
         <f>J31/SUM(J30:J33)</f>
         <v>0.6096270312713119</v>
@@ -7134,8 +7608,12 @@
         <f>K31/SUM(K30:K33)</f>
         <v>0.5885341231136757</v>
       </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="O31" s="1">
+        <f t="shared" ref="O31:O37" si="23">SUM(L31:N31)/3</f>
+        <v>0.59718983726713759</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" s="3" t="s">
         <v>9</v>
       </c>
@@ -7148,23 +7626,31 @@
       <c r="D32">
         <v>2.2453959733333302</v>
       </c>
-      <c r="E32" s="2"/>
+      <c r="E32">
+        <v>3.04536272333333</v>
+      </c>
       <c r="F32">
         <v>2.6211905500000001</v>
       </c>
       <c r="G32">
         <v>6.8402470766666603</v>
       </c>
-      <c r="I32" s="2"/>
+      <c r="I32" s="2">
+        <f t="shared" si="21"/>
+        <v>0.79996674999999984</v>
+      </c>
       <c r="J32" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>0.37579457666666993</v>
       </c>
       <c r="K32" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>4.5948511033333297</v>
       </c>
-      <c r="L32" s="1"/>
+      <c r="L32" s="1">
+        <f>I32/SUM(I30:I33)</f>
+        <v>7.0847728646455832E-2</v>
+      </c>
       <c r="M32" s="1">
         <f>J32/SUM(J30:J33)</f>
         <v>7.3616683361420784E-2</v>
@@ -7173,8 +7659,12 @@
         <f>K32/SUM(K30:K33)</f>
         <v>6.7858824202514739E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32" s="1">
+        <f t="shared" si="23"/>
+        <v>7.0774412070130452E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" s="3" t="s">
         <v>9</v>
       </c>
@@ -7187,23 +7677,31 @@
       <c r="D33">
         <v>1.25755285333333</v>
       </c>
-      <c r="E33" s="2"/>
+      <c r="E33">
+        <v>1.85180200333333</v>
+      </c>
       <c r="F33">
         <v>1.56675720666666</v>
       </c>
       <c r="G33">
         <v>4.4015445833333304</v>
       </c>
-      <c r="I33" s="2"/>
+      <c r="I33" s="2">
+        <f t="shared" si="21"/>
+        <v>0.59424915</v>
+      </c>
       <c r="J33" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>0.30920435333332996</v>
       </c>
       <c r="K33" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>3.1439917300000007</v>
       </c>
-      <c r="L33" s="1"/>
+      <c r="L33" s="1">
+        <f>I33/SUM(I30:I33)</f>
+        <v>5.2628690539434343E-2</v>
+      </c>
       <c r="M33" s="1">
         <f>J33/SUM(J30:J33)</f>
         <v>6.0571919837744403E-2</v>
@@ -7212,8 +7710,12 @@
         <f>K33/SUM(K30:K33)</f>
         <v>4.6431881534846134E-2</v>
       </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33" s="1">
+        <f t="shared" si="23"/>
+        <v>5.3210830637341631E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" s="3" t="s">
         <v>9</v>
       </c>
@@ -7227,7 +7729,7 @@
         <v>50.522071966666601</v>
       </c>
       <c r="E34">
-        <v>57.598385899999997</v>
+        <v>57.525930000000002</v>
       </c>
       <c r="F34">
         <v>54.909849133333303</v>
@@ -7236,20 +7738,20 @@
         <v>128.53779913333301</v>
       </c>
       <c r="I34" s="2">
-        <f t="shared" si="3"/>
-        <v>7.0763139333333953</v>
+        <f t="shared" si="19"/>
+        <v>7.0038580333334011</v>
       </c>
       <c r="J34" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>4.3877771666667016</v>
       </c>
       <c r="K34" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>78.015727166666409</v>
       </c>
       <c r="L34" s="1">
         <f>I34/SUM(I34:I37)</f>
-        <v>0.47639036558750303</v>
+        <v>0.47151906675564675</v>
       </c>
       <c r="M34" s="1">
         <f>J34/SUM(J34:J37)</f>
@@ -7259,8 +7761,12 @@
         <f>K34/SUM(K34:K37)</f>
         <v>0.49492086132824242</v>
       </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="O34" s="1">
+        <f t="shared" si="23"/>
+        <v>0.46823589811557143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" s="3" t="s">
         <v>9</v>
       </c>
@@ -7274,7 +7780,7 @@
         <v>10.102477916666601</v>
       </c>
       <c r="E35">
-        <v>11.817029399999999</v>
+        <v>11.8393194333333</v>
       </c>
       <c r="F35">
         <v>11.2481988666666</v>
@@ -7283,20 +7789,20 @@
         <v>30.917709349999999</v>
       </c>
       <c r="I35" s="2">
-        <f t="shared" si="3"/>
-        <v>1.7145514833333984</v>
+        <f t="shared" si="19"/>
+        <v>1.7368415166666988</v>
       </c>
       <c r="J35" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>1.1457209499999994</v>
       </c>
       <c r="K35" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>20.815231433333398</v>
       </c>
       <c r="L35" s="1">
         <f>I35/SUM(I34:I37)</f>
-        <v>0.11542673426573519</v>
+        <v>0.11692896788362982</v>
       </c>
       <c r="M35" s="1">
         <f>J35/SUM(J34:J37)</f>
@@ -7306,8 +7812,12 @@
         <f>K35/SUM(K34:K37)</f>
         <v>0.13204891685139269</v>
       </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="O35" s="1">
+        <f t="shared" si="23"/>
+        <v>0.12113894109271006</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" s="3" t="s">
         <v>9</v>
       </c>
@@ -7321,7 +7831,7 @@
         <v>14.10962531</v>
       </c>
       <c r="E36">
-        <v>17.396169633333301</v>
+        <v>17.420496499999999</v>
       </c>
       <c r="F36">
         <v>16.589683036666599</v>
@@ -7330,20 +7840,20 @@
         <v>44.909156233333299</v>
       </c>
       <c r="I36" s="2">
-        <f t="shared" si="3"/>
-        <v>3.2865443233333007</v>
+        <f t="shared" si="19"/>
+        <v>3.3108711899999985</v>
       </c>
       <c r="J36" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>2.4800577266665993</v>
       </c>
       <c r="K36" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>30.7995309233333</v>
       </c>
       <c r="L36" s="1">
         <f>I36/SUM(I34:I37)</f>
-        <v>0.22125616054667455</v>
+        <v>0.22289699280411482</v>
       </c>
       <c r="M36" s="1">
         <f>J36/SUM(J34:J37)</f>
@@ -7353,8 +7863,12 @@
         <f>K36/SUM(K34:K37)</f>
         <v>0.19538791634303879</v>
       </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="O36" s="1">
+        <f t="shared" si="23"/>
+        <v>0.22200081594740231</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" s="3" t="s">
         <v>9</v>
       </c>
@@ -7368,7 +7882,7 @@
         <v>13.9483635866666</v>
       </c>
       <c r="E37">
-        <v>16.724977866666599</v>
+        <v>16.750610066666599</v>
       </c>
       <c r="F37">
         <v>15.946443333333301</v>
@@ -7377,20 +7891,20 @@
         <v>41.950605400000001</v>
       </c>
       <c r="I37" s="2">
-        <f t="shared" si="3"/>
-        <v>2.7766142799999987</v>
+        <f t="shared" si="19"/>
+        <v>2.8022464799999991</v>
       </c>
       <c r="J37" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>1.9980797466667006</v>
       </c>
       <c r="K37" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>28.002241813333399</v>
       </c>
       <c r="L37" s="1">
         <f>I37/SUM(I34:I37)</f>
-        <v>0.18692673960008727</v>
+        <v>0.18865497255660862</v>
       </c>
       <c r="M37" s="1">
         <f>J37/SUM(J34:J37)</f>
@@ -7400,8 +7914,12 @@
         <f>K37/SUM(K34:K37)</f>
         <v>0.17764230547732618</v>
       </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="O37" s="1">
+        <f t="shared" si="23"/>
+        <v>0.1886243448443162</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" s="3" t="s">
         <v>9</v>
       </c>
@@ -7422,7 +7940,7 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>63.335395566666008</v>
       </c>
       <c r="L38" s="1"/>
@@ -7431,8 +7949,12 @@
         <f>K38/SUM(K38:K41)</f>
         <v>0.26041637593067141</v>
       </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="O38" s="6">
+        <f>N38</f>
+        <v>0.26041637593067141</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" s="3" t="s">
         <v>9</v>
       </c>
@@ -7453,7 +7975,7 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>34.464338333333302</v>
       </c>
       <c r="L39" s="1"/>
@@ -7462,8 +7984,12 @@
         <f>K39/SUM(K38:K41)</f>
         <v>0.14170714506974419</v>
       </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="O39" s="6">
+        <f t="shared" ref="O39:O49" si="24">N39</f>
+        <v>0.14170714506974419</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
       <c r="A40" s="3" t="s">
         <v>9</v>
       </c>
@@ -7484,7 +8010,7 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>70.204037200000002</v>
       </c>
       <c r="L40" s="1"/>
@@ -7493,8 +8019,12 @@
         <f>K40/SUM(K38:K41)</f>
         <v>0.28865819467539838</v>
       </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40" s="6">
+        <f t="shared" si="24"/>
+        <v>0.28865819467539838</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" s="3" t="s">
         <v>9</v>
       </c>
@@ -7515,7 +8045,7 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>75.204419399999409</v>
       </c>
       <c r="L41" s="1"/>
@@ -7524,8 +8054,12 @@
         <f>K41/SUM(K38:K41)</f>
         <v>0.30921828432418608</v>
       </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41" s="6">
+        <f t="shared" si="24"/>
+        <v>0.30921828432418608</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" s="3" t="s">
         <v>9</v>
       </c>
@@ -7546,7 +8080,7 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>58.164087666666973</v>
       </c>
       <c r="L42" s="1"/>
@@ -7555,8 +8089,12 @@
         <f>K42/SUM(K42:K45)</f>
         <v>0.15285316937789162</v>
       </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="O42" s="6">
+        <f t="shared" si="24"/>
+        <v>0.15285316937789162</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" s="3" t="s">
         <v>9</v>
       </c>
@@ -7577,7 +8115,7 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>55.774228399999991</v>
       </c>
       <c r="L43" s="1"/>
@@ -7586,8 +8124,12 @@
         <f>K43/SUM(K42:K45)</f>
         <v>0.14657270357963723</v>
       </c>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="O43" s="6">
+        <f t="shared" si="24"/>
+        <v>0.14657270357963723</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" s="3" t="s">
         <v>9</v>
       </c>
@@ -7608,7 +8150,7 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>117.2195210999997</v>
       </c>
       <c r="L44" s="1"/>
@@ -7617,8 +8159,12 @@
         <f>K44/SUM(K42:K45)</f>
         <v>0.30804876396886721</v>
       </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="O44" s="6">
+        <f t="shared" si="24"/>
+        <v>0.30804876396886721</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" s="3" t="s">
         <v>9</v>
       </c>
@@ -7639,7 +8185,7 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>149.364777466666</v>
       </c>
       <c r="L45" s="1"/>
@@ -7648,8 +8194,12 @@
         <f>K45/SUM(K42:K45)</f>
         <v>0.39252536307360403</v>
       </c>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="O45" s="6">
+        <f t="shared" si="24"/>
+        <v>0.39252536307360403</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46" s="3" t="s">
         <v>9</v>
       </c>
@@ -7670,7 +8220,7 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>37.581367999999998</v>
       </c>
       <c r="L46" s="1"/>
@@ -7679,8 +8229,12 @@
         <f>K46/SUM(K46:K49)</f>
         <v>7.9254516693036001E-2</v>
       </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46" s="6">
+        <f t="shared" si="24"/>
+        <v>7.9254516693036001E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" s="3" t="s">
         <v>9</v>
       </c>
@@ -7701,7 +8255,7 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>91.321723166666999</v>
       </c>
       <c r="L47" s="1"/>
@@ -7710,8 +8264,12 @@
         <f>K47/SUM(K46:K49)</f>
         <v>0.19258636442264218</v>
       </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47" s="6">
+        <f t="shared" si="24"/>
+        <v>0.19258636442264218</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" s="3" t="s">
         <v>9</v>
       </c>
@@ -7732,7 +8290,7 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>173.20538766666601</v>
       </c>
       <c r="L48" s="1"/>
@@ -7741,8 +8299,12 @@
         <f>K48/SUM(K46:K49)</f>
         <v>0.36526901543742513</v>
       </c>
-    </row>
-    <row r="49" spans="1:14">
+      <c r="O48" s="6">
+        <f t="shared" si="24"/>
+        <v>0.36526901543742513</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49" s="3" t="s">
         <v>9</v>
       </c>
@@ -7763,7 +8325,7 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>172.07734133333292</v>
       </c>
       <c r="L49" s="1"/>
@@ -7772,8 +8334,12 @@
         <f>K49/SUM(K46:K49)</f>
         <v>0.36289010344689659</v>
       </c>
-    </row>
-    <row r="50" spans="1:14">
+      <c r="O49" s="6">
+        <f t="shared" si="24"/>
+        <v>0.36289010344689659</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" s="3" t="s">
         <v>11</v>
       </c>
@@ -7787,16 +8353,26 @@
         <f>E50-$D50</f>
         <v>0</v>
       </c>
-      <c r="J50" s="2"/>
+      <c r="J50" s="2">
+        <f>F50-$D50</f>
+        <v>0</v>
+      </c>
       <c r="K50" s="2"/>
       <c r="L50" s="1">
         <f>I50/SUM(I50:I53)</f>
         <v>0</v>
       </c>
-      <c r="M50" s="1"/>
+      <c r="M50" s="1">
+        <f>J50/SUM(J50:J53)</f>
+        <v>0</v>
+      </c>
       <c r="N50" s="1"/>
-    </row>
-    <row r="51" spans="1:14">
+      <c r="O50" s="1">
+        <f>SUM(L50:N50)/2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51" s="3" t="s">
         <v>11</v>
       </c>
@@ -7807,29 +8383,33 @@
         <v>22</v>
       </c>
       <c r="D51">
-        <v>2317.5052434614499</v>
-      </c>
-      <c r="E51">
-        <v>3876.1365728695901</v>
-      </c>
-      <c r="F51">
-        <v>2312.5730481885798</v>
+        <v>12.3143563033333</v>
       </c>
       <c r="G51" s="2"/>
       <c r="I51" s="2">
-        <f t="shared" ref="I51:I61" si="6">E51-$D51</f>
-        <v>1558.6313294081401</v>
-      </c>
-      <c r="J51" s="2"/>
+        <f t="shared" ref="I51:J61" si="25">E51-$D51</f>
+        <v>-12.3143563033333</v>
+      </c>
+      <c r="J51" s="2">
+        <f t="shared" si="25"/>
+        <v>-12.3143563033333</v>
+      </c>
       <c r="K51" s="2"/>
       <c r="L51" s="1">
         <f>I51/SUM(I50:I53)</f>
-        <v>0.87570969030373169</v>
-      </c>
-      <c r="M51" s="1"/>
+        <v>0.92925269976099745</v>
+      </c>
+      <c r="M51" s="1">
+        <f>J51/SUM(J50:J53)</f>
+        <v>0.92925269976099745</v>
+      </c>
       <c r="N51" s="1"/>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="O51" s="1">
+        <f t="shared" ref="O51:O53" si="26">SUM(L51:N51)/2</f>
+        <v>0.92925269976099745</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" s="3" t="s">
         <v>11</v>
       </c>
@@ -7840,29 +8420,33 @@
         <v>23</v>
       </c>
       <c r="D52">
-        <v>182.09515124594799</v>
-      </c>
-      <c r="E52">
-        <v>302.35086775823299</v>
-      </c>
-      <c r="F52">
-        <v>178.51766454123899</v>
+        <v>0.75909940333333303</v>
       </c>
       <c r="G52" s="2"/>
       <c r="I52" s="2">
-        <f t="shared" si="6"/>
-        <v>120.25571651228501</v>
-      </c>
-      <c r="J52" s="2"/>
+        <f t="shared" si="25"/>
+        <v>-0.75909940333333303</v>
+      </c>
+      <c r="J52" s="2">
+        <f t="shared" si="25"/>
+        <v>-0.75909940333333303</v>
+      </c>
       <c r="K52" s="2"/>
       <c r="L52" s="1">
         <f>I52/SUM(I50:I53)</f>
-        <v>6.756510938620458E-2</v>
-      </c>
-      <c r="M52" s="1"/>
+        <v>5.7282342053357901E-2</v>
+      </c>
+      <c r="M52" s="1">
+        <f>J52/SUM(J50:J53)</f>
+        <v>5.7282342053357901E-2</v>
+      </c>
       <c r="N52" s="1"/>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="O52" s="1">
+        <f t="shared" si="26"/>
+        <v>5.7282342053357901E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" s="3" t="s">
         <v>11</v>
       </c>
@@ -7873,29 +8457,33 @@
         <v>24</v>
       </c>
       <c r="D53">
-        <v>63.301190669687998</v>
-      </c>
-      <c r="E53">
-        <v>164.26350198035999</v>
-      </c>
-      <c r="F53">
-        <v>61.891833647102899</v>
+        <v>0.17843617000000001</v>
       </c>
       <c r="G53" s="2"/>
       <c r="I53" s="2">
-        <f t="shared" si="6"/>
-        <v>100.96231131067199</v>
-      </c>
-      <c r="J53" s="2"/>
+        <f t="shared" si="25"/>
+        <v>-0.17843617000000001</v>
+      </c>
+      <c r="J53" s="2">
+        <f t="shared" si="25"/>
+        <v>-0.17843617000000001</v>
+      </c>
       <c r="K53" s="2"/>
       <c r="L53" s="1">
         <f>I53/SUM(I50:I53)</f>
-        <v>5.6725200310063631E-2</v>
-      </c>
-      <c r="M53" s="1"/>
+        <v>1.3464958185644634E-2</v>
+      </c>
+      <c r="M53" s="1">
+        <f>J53/SUM(J50:J53)</f>
+        <v>1.3464958185644634E-2</v>
+      </c>
       <c r="N53" s="1"/>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="O53" s="1">
+        <f t="shared" si="26"/>
+        <v>1.3464958185644634E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" s="3" t="s">
         <v>11</v>
       </c>
@@ -7906,15 +8494,15 @@
         <v>21</v>
       </c>
       <c r="I54" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="J54" s="2">
-        <f t="shared" ref="J54:J61" si="7">F54-$D54</f>
+        <f t="shared" ref="J54:J61" si="27">F54-$D54</f>
         <v>0</v>
       </c>
       <c r="K54" s="2">
-        <f t="shared" ref="K54:K73" si="8">G54-$D54</f>
+        <f t="shared" ref="K54:K73" si="28">G54-$D54</f>
         <v>0</v>
       </c>
       <c r="L54" s="1">
@@ -7929,8 +8517,12 @@
         <f>K54/SUM(K54:K57)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="O54" s="1">
+        <f>SUM(L54:N54)/3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55" s="3" t="s">
         <v>11</v>
       </c>
@@ -7941,43 +8533,38 @@
         <v>22</v>
       </c>
       <c r="D55">
-        <v>2665.29975566542</v>
-      </c>
-      <c r="E55">
-        <v>3980.8085502945</v>
-      </c>
-      <c r="F55">
-        <v>3292.4960847453999</v>
-      </c>
-      <c r="G55">
-        <v>10820.8510192745</v>
+        <v>17.71107679</v>
       </c>
       <c r="I55" s="2">
-        <f t="shared" si="6"/>
-        <v>1315.5087946290801</v>
+        <f t="shared" si="25"/>
+        <v>-17.71107679</v>
       </c>
       <c r="J55" s="2">
-        <f t="shared" si="7"/>
-        <v>627.19632907997993</v>
+        <f t="shared" si="27"/>
+        <v>-17.71107679</v>
       </c>
       <c r="K55" s="2">
-        <f t="shared" si="8"/>
-        <v>8155.5512636090798</v>
+        <f t="shared" si="28"/>
+        <v>-17.71107679</v>
       </c>
       <c r="L55" s="1">
         <f>I55/SUM(I54:I57)</f>
-        <v>0.79757159724043636</v>
+        <v>0.89918935245526366</v>
       </c>
       <c r="M55" s="1">
         <f>J55/SUM(J54:J57)</f>
-        <v>0.79070944014070843</v>
+        <v>0.89918935245526366</v>
       </c>
       <c r="N55" s="1">
         <f>K55/SUM(K54:K57)</f>
-        <v>0.80976703700442687</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
+        <v>0.89918935245526366</v>
+      </c>
+      <c r="O55" s="1">
+        <f t="shared" ref="O55:O61" si="29">SUM(L55:N55)/3</f>
+        <v>0.89918935245526355</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56" s="3" t="s">
         <v>11</v>
       </c>
@@ -7988,43 +8575,38 @@
         <v>23</v>
       </c>
       <c r="D56">
-        <v>299.55375641568997</v>
-      </c>
-      <c r="E56">
-        <v>452.51300344348903</v>
-      </c>
-      <c r="F56">
-        <v>369.57232275599</v>
-      </c>
-      <c r="G56">
-        <v>1248.1796254824601</v>
+        <v>1.3467701133333301</v>
       </c>
       <c r="I56" s="2">
-        <f t="shared" si="6"/>
-        <v>152.95924702779905</v>
+        <f t="shared" si="25"/>
+        <v>-1.3467701133333301</v>
       </c>
       <c r="J56" s="2">
-        <f t="shared" si="7"/>
-        <v>70.018566340300026</v>
+        <f t="shared" si="27"/>
+        <v>-1.3467701133333301</v>
       </c>
       <c r="K56" s="2">
-        <f t="shared" si="8"/>
-        <v>948.62586906677006</v>
+        <f t="shared" si="28"/>
+        <v>-1.3467701133333301</v>
       </c>
       <c r="L56" s="1">
         <f>I56/SUM(I54:I57)</f>
-        <v>9.273670496368977E-2</v>
+        <v>6.8375365341877617E-2</v>
       </c>
       <c r="M56" s="1">
         <f>J56/SUM(J54:J57)</f>
-        <v>8.8272744631025482E-2</v>
+        <v>6.8375365341877617E-2</v>
       </c>
       <c r="N56" s="1">
         <f>K56/SUM(K54:K57)</f>
-        <v>9.4189336120978656E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
+        <v>6.8375365341877617E-2</v>
+      </c>
+      <c r="O56" s="1">
+        <f t="shared" si="29"/>
+        <v>6.8375365341877617E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57" s="3" t="s">
         <v>11</v>
       </c>
@@ -8035,43 +8617,38 @@
         <v>24</v>
       </c>
       <c r="D57">
-        <v>183.72461757723599</v>
-      </c>
-      <c r="E57">
-        <v>364.64930652997799</v>
-      </c>
-      <c r="F57">
-        <v>279.71680587201701</v>
-      </c>
-      <c r="G57">
-        <v>1151.0259360111399</v>
+        <v>0.63886852333333299</v>
       </c>
       <c r="I57" s="2">
-        <f t="shared" si="6"/>
-        <v>180.924688952742</v>
+        <f t="shared" si="25"/>
+        <v>-0.63886852333333299</v>
       </c>
       <c r="J57" s="2">
-        <f t="shared" si="7"/>
-        <v>95.992188294781016</v>
+        <f t="shared" si="27"/>
+        <v>-0.63886852333333299</v>
       </c>
       <c r="K57" s="2">
-        <f t="shared" si="8"/>
-        <v>967.30131843390393</v>
+        <f t="shared" si="28"/>
+        <v>-0.63886852333333299</v>
       </c>
       <c r="L57" s="1">
         <f>I57/SUM(I54:I57)</f>
-        <v>0.10969169779587402</v>
+        <v>3.2435282202858663E-2</v>
       </c>
       <c r="M57" s="1">
         <f>J57/SUM(J54:J57)</f>
-        <v>0.12101781522826606</v>
+        <v>3.2435282202858663E-2</v>
       </c>
       <c r="N57" s="1">
         <f>K57/SUM(K54:K57)</f>
-        <v>9.6043626874594487E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
+        <v>3.2435282202858663E-2</v>
+      </c>
+      <c r="O57" s="1">
+        <f t="shared" si="29"/>
+        <v>3.2435282202858663E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
       <c r="A58" s="3" t="s">
         <v>11</v>
       </c>
@@ -8082,34 +8659,38 @@
         <v>21</v>
       </c>
       <c r="D58">
-        <v>1437.1253260359499</v>
+        <v>7.4184241999999996</v>
       </c>
       <c r="I58" s="2">
-        <f t="shared" si="6"/>
-        <v>-1437.1253260359499</v>
+        <f t="shared" si="25"/>
+        <v>-7.4184241999999996</v>
       </c>
       <c r="J58" s="2">
-        <f t="shared" si="7"/>
-        <v>-1437.1253260359499</v>
+        <f t="shared" si="27"/>
+        <v>-7.4184241999999996</v>
       </c>
       <c r="K58" s="2">
-        <f t="shared" si="8"/>
-        <v>-1437.1253260359499</v>
+        <f t="shared" si="28"/>
+        <v>-7.4184241999999996</v>
       </c>
       <c r="L58" s="1">
         <f>I58/SUM(I58:I61)</f>
-        <v>-0.37123459004366133</v>
+        <v>0.24910054245369137</v>
       </c>
       <c r="M58" s="1">
         <f>J58/SUM(J58:J61)</f>
-        <v>-0.50762194036031305</v>
+        <v>0.24910054245369137</v>
       </c>
       <c r="N58" s="1">
         <f>K58/SUM(K58:K61)</f>
-        <v>-3.8085919845583543E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14">
+        <v>0.24910054245369137</v>
+      </c>
+      <c r="O58" s="1">
+        <f t="shared" si="29"/>
+        <v>0.24910054245369137</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
       <c r="A59" s="3" t="s">
         <v>11</v>
       </c>
@@ -8120,43 +8701,38 @@
         <v>22</v>
       </c>
       <c r="D59">
-        <v>1912.0163274440899</v>
-      </c>
-      <c r="E59">
-        <v>3878.1324619694901</v>
-      </c>
-      <c r="F59">
-        <v>3509.1641614923301</v>
-      </c>
-      <c r="G59">
-        <v>16338.8315783952</v>
+        <v>6.2897941333333298</v>
       </c>
       <c r="I59" s="2">
-        <f t="shared" si="6"/>
-        <v>1966.1161345254002</v>
+        <f t="shared" si="25"/>
+        <v>-6.2897941333333298</v>
       </c>
       <c r="J59" s="2">
-        <f t="shared" si="7"/>
-        <v>1597.1478340482402</v>
+        <f t="shared" si="27"/>
+        <v>-6.2897941333333298</v>
       </c>
       <c r="K59" s="2">
-        <f t="shared" si="8"/>
-        <v>14426.815250951111</v>
+        <f t="shared" si="28"/>
+        <v>-6.2897941333333298</v>
       </c>
       <c r="L59" s="1">
         <f>I59/SUM(I58:I61)</f>
-        <v>0.50788216167064248</v>
+        <v>0.21120268783434873</v>
       </c>
       <c r="M59" s="1">
         <f>J59/SUM(J58:J61)</f>
-        <v>0.564145149955807</v>
+        <v>0.21120268783434873</v>
       </c>
       <c r="N59" s="1">
         <f>K59/SUM(K58:K61)</f>
-        <v>0.38233167234645299</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14">
+        <v>0.21120268783434873</v>
+      </c>
+      <c r="O59" s="1">
+        <f t="shared" si="29"/>
+        <v>0.21120268783434873</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
       <c r="A60" s="3" t="s">
         <v>11</v>
       </c>
@@ -8167,43 +8743,38 @@
         <v>23</v>
       </c>
       <c r="D60">
-        <v>1733.8995602553</v>
-      </c>
-      <c r="E60">
-        <v>3175.83921502673</v>
-      </c>
-      <c r="F60">
-        <v>2856.5052134766802</v>
-      </c>
-      <c r="G60">
-        <v>13219.904450419201</v>
+        <v>8.3409771500000005</v>
       </c>
       <c r="I60" s="2">
-        <f t="shared" si="6"/>
-        <v>1441.93965477143</v>
+        <f t="shared" si="25"/>
+        <v>-8.3409771500000005</v>
       </c>
       <c r="J60" s="2">
-        <f t="shared" si="7"/>
-        <v>1122.6056532213802</v>
+        <f t="shared" si="27"/>
+        <v>-8.3409771500000005</v>
       </c>
       <c r="K60" s="2">
-        <f t="shared" si="8"/>
-        <v>11486.0048901639</v>
+        <f t="shared" si="28"/>
+        <v>-8.3409771500000005</v>
       </c>
       <c r="L60" s="1">
         <f>I60/SUM(I58:I61)</f>
-        <v>0.3724782153017181</v>
+        <v>0.28007860923602146</v>
       </c>
       <c r="M60" s="1">
         <f>J60/SUM(J58:J61)</f>
-        <v>0.396527184946039</v>
+        <v>0.28007860923602146</v>
       </c>
       <c r="N60" s="1">
         <f>K60/SUM(K58:K61)</f>
-        <v>0.30439590317387527</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14">
+        <v>0.28007860923602146</v>
+      </c>
+      <c r="O60" s="1">
+        <f t="shared" si="29"/>
+        <v>0.28007860923602146</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
       <c r="A61" s="3" t="s">
         <v>11</v>
       </c>
@@ -8214,43 +8785,38 @@
         <v>24</v>
       </c>
       <c r="D61">
-        <v>1850.7656633716099</v>
-      </c>
-      <c r="E61">
-        <v>3751.0405365178999</v>
-      </c>
-      <c r="F61">
-        <v>3399.2312980756601</v>
-      </c>
-      <c r="G61">
-        <v>15108.8404897418</v>
+        <v>7.7316477333333298</v>
       </c>
       <c r="I61" s="2">
-        <f t="shared" si="6"/>
-        <v>1900.27487314629</v>
+        <f t="shared" si="25"/>
+        <v>-7.7316477333333298</v>
       </c>
       <c r="J61" s="2">
-        <f t="shared" si="7"/>
-        <v>1548.4656347040502</v>
+        <f t="shared" si="27"/>
+        <v>-7.7316477333333298</v>
       </c>
       <c r="K61" s="2">
-        <f t="shared" si="8"/>
-        <v>13258.07482637019</v>
+        <f t="shared" si="28"/>
+        <v>-7.7316477333333298</v>
       </c>
       <c r="L61" s="1">
         <f>I61/SUM(I58:I61)</f>
-        <v>0.4908742130713008</v>
+        <v>0.25961816047593855</v>
       </c>
       <c r="M61" s="1">
         <f>J61/SUM(J58:J61)</f>
-        <v>0.54694960545846705</v>
+        <v>0.25961816047593855</v>
       </c>
       <c r="N61" s="1">
         <f>K61/SUM(K58:K61)</f>
-        <v>0.35135834432525526</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14">
+        <v>0.25961816047593855</v>
+      </c>
+      <c r="O61" s="1">
+        <f t="shared" si="29"/>
+        <v>0.25961816047593855</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
       <c r="A62" s="3" t="s">
         <v>11</v>
       </c>
@@ -8265,7 +8831,7 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L62" s="1"/>
@@ -8274,8 +8840,12 @@
         <f>K62/SUM(K62:K65)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:14">
+      <c r="O62" s="6">
+        <f>N62</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
       <c r="A63" s="3" t="s">
         <v>11</v>
       </c>
@@ -8286,27 +8856,28 @@
         <v>22</v>
       </c>
       <c r="D63">
-        <v>2776.2315145113698</v>
+        <v>9.9285394999999994</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
-      <c r="G63">
-        <v>17390.673329173602</v>
-      </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2">
-        <f t="shared" si="8"/>
-        <v>14614.441814662232</v>
+        <f t="shared" si="28"/>
+        <v>-9.9285394999999994</v>
       </c>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
       <c r="N63" s="1">
         <f>K63/SUM(K62:K65)</f>
-        <v>0.29039686020406907</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
+        <v>0.22242627804977147</v>
+      </c>
+      <c r="O63" s="6">
+        <f t="shared" ref="O63:O73" si="30">N63</f>
+        <v>0.22242627804977147</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
       <c r="A64" s="3" t="s">
         <v>11</v>
       </c>
@@ -8317,27 +8888,28 @@
         <v>23</v>
       </c>
       <c r="D64">
-        <v>2648.0605451709598</v>
+        <v>13.548768566666601</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
-      <c r="G64">
-        <v>17478.450226044901</v>
-      </c>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2">
-        <f t="shared" si="8"/>
-        <v>14830.389680873941</v>
+        <f t="shared" si="28"/>
+        <v>-13.548768566666601</v>
       </c>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
       <c r="N64" s="1">
         <f>K64/SUM(K62:K65)</f>
-        <v>0.29468786105863015</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14">
+        <v>0.30352925165291322</v>
+      </c>
+      <c r="O64" s="6">
+        <f t="shared" si="30"/>
+        <v>0.30352925165291322</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
       <c r="A65" s="3" t="s">
         <v>11</v>
       </c>
@@ -8348,27 +8920,28 @@
         <v>24</v>
       </c>
       <c r="D65">
-        <v>4265.3844533396496</v>
+        <v>21.1601313</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
-      <c r="G65">
-        <v>25146.309938758099</v>
-      </c>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2">
-        <f t="shared" si="8"/>
-        <v>20880.925485418447</v>
+        <f t="shared" si="28"/>
+        <v>-21.1601313</v>
       </c>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
       <c r="N65" s="1">
         <f>K65/SUM(K62:K65)</f>
-        <v>0.41491527873730083</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14">
+        <v>0.47404447029731539</v>
+      </c>
+      <c r="O65" s="6">
+        <f t="shared" si="30"/>
+        <v>0.47404447029731539</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
       <c r="A66" s="3" t="s">
         <v>11</v>
       </c>
@@ -8383,7 +8956,7 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L66" s="1"/>
@@ -8392,8 +8965,12 @@
         <f>K66/SUM(K66:K69)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:14">
+      <c r="O66" s="6">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
       <c r="A67" s="3" t="s">
         <v>11</v>
       </c>
@@ -8404,27 +8981,28 @@
         <v>22</v>
       </c>
       <c r="D67">
-        <v>3046.8072291071499</v>
+        <v>11.7713416333333</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
-      <c r="G67">
-        <v>23143.659958120901</v>
-      </c>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2">
-        <f t="shared" si="8"/>
-        <v>20096.85272901375</v>
+        <f t="shared" si="28"/>
+        <v>-11.7713416333333</v>
       </c>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
       <c r="N67" s="1">
         <f>K67/SUM(K66:K69)</f>
-        <v>0.25503271729606303</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14">
+        <v>0.17647793498569347</v>
+      </c>
+      <c r="O67" s="6">
+        <f t="shared" si="30"/>
+        <v>0.17647793498569347</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
       <c r="A68" s="3" t="s">
         <v>11</v>
       </c>
@@ -8435,27 +9013,28 @@
         <v>23</v>
       </c>
       <c r="D68">
-        <v>2795.2284845232698</v>
+        <v>15.0971010666666</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
-      <c r="G68">
-        <v>22816.995727606401</v>
-      </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2">
-        <f t="shared" si="8"/>
-        <v>20021.76724308313</v>
+        <f t="shared" si="28"/>
+        <v>-15.0971010666666</v>
       </c>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
       <c r="N68" s="1">
         <f>K68/SUM(K66:K69)</f>
-        <v>0.2540798688195085</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14">
+        <v>0.22633828016434676</v>
+      </c>
+      <c r="O68" s="6">
+        <f t="shared" si="30"/>
+        <v>0.22633828016434676</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
       <c r="A69" s="3" t="s">
         <v>11</v>
       </c>
@@ -8466,27 +9045,28 @@
         <v>24</v>
       </c>
       <c r="D69">
-        <v>6849.0991037536196</v>
+        <v>39.833049666666597</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
-      <c r="G69">
-        <v>45531.555880110398</v>
-      </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2">
-        <f t="shared" si="8"/>
-        <v>38682.456776356776</v>
+        <f t="shared" si="28"/>
+        <v>-39.833049666666597</v>
       </c>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
       <c r="N69" s="1">
         <f>K69/SUM(K66:K69)</f>
-        <v>0.49088741388442836</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14">
+        <v>0.59718378484995971</v>
+      </c>
+      <c r="O69" s="6">
+        <f t="shared" si="30"/>
+        <v>0.59718378484995971</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
       <c r="A70" s="3" t="s">
         <v>11</v>
       </c>
@@ -8501,7 +9081,7 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L70" s="1"/>
@@ -8510,8 +9090,12 @@
         <f>K70/SUM(K70:K73)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:14">
+      <c r="O70" s="6">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
       <c r="A71" s="3" t="s">
         <v>11</v>
       </c>
@@ -8522,27 +9106,28 @@
         <v>22</v>
       </c>
       <c r="D71">
-        <v>3836.8911031993998</v>
+        <v>15.9971258333333</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
-      <c r="G71">
-        <v>31464.8265330295</v>
-      </c>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2">
-        <f t="shared" si="8"/>
-        <v>27627.9354298301</v>
+        <f t="shared" si="28"/>
+        <v>-15.9971258333333</v>
       </c>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
       <c r="N71" s="1">
         <f>K71/SUM(K70:K73)</f>
-        <v>0.24989232054808441</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14">
+        <v>0.16057921079720025</v>
+      </c>
+      <c r="O71" s="6">
+        <f t="shared" si="30"/>
+        <v>0.16057921079720025</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
       <c r="A72" s="3" t="s">
         <v>11</v>
       </c>
@@ -8553,27 +9138,28 @@
         <v>23</v>
       </c>
       <c r="D72">
-        <v>3300.0470468808699</v>
+        <v>18.685675066666601</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
-      <c r="G72">
-        <v>30242.557832135099</v>
-      </c>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2">
-        <f t="shared" si="8"/>
-        <v>26942.510785254228</v>
+        <f t="shared" si="28"/>
+        <v>-18.685675066666601</v>
       </c>
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
       <c r="N72" s="1">
         <f>K72/SUM(K70:K73)</f>
-        <v>0.24369271307365198</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14">
+        <v>0.18756687836798919</v>
+      </c>
+      <c r="O72" s="6">
+        <f t="shared" si="30"/>
+        <v>0.18756687836798919</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
       <c r="A73" s="3" t="s">
         <v>11</v>
       </c>
@@ -8584,24 +9170,25 @@
         <v>24</v>
       </c>
       <c r="D73">
-        <v>9711.1204938189003</v>
+        <v>64.938599366666594</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
-      <c r="G73">
-        <v>65700.035883902106</v>
-      </c>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2">
-        <f t="shared" si="8"/>
-        <v>55988.915390083203</v>
+        <f t="shared" si="28"/>
+        <v>-64.938599366666594</v>
       </c>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
       <c r="N73" s="1">
         <f>K73/SUM(K70:K73)</f>
-        <v>0.50641496637826355</v>
+        <v>0.65185391083481048</v>
+      </c>
+      <c r="O73" s="6">
+        <f t="shared" si="30"/>
+        <v>0.65185391083481048</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_analysis/procurement.xlsx
+++ b/data/data_analysis/procurement.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C8A5C7-21C9-4D25-87B8-D230D85F779B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5FF859-71AC-4308-B70E-1505E9116ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="3" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
   </bookViews>
   <sheets>
     <sheet name="Scaling" sheetId="1" r:id="rId1"/>
     <sheet name="45Q" sheetId="2" r:id="rId2"/>
     <sheet name="Marginal Supply" sheetId="3" r:id="rId3"/>
+    <sheet name="Inputs" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">'45Q'!$D$2:$D$13</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="58">
   <si>
     <t>Scenario</t>
   </si>
@@ -164,11 +165,68 @@
   <si>
     <t>Sum</t>
   </si>
+  <si>
+    <t>500 Mt Baseline</t>
+  </si>
+  <si>
+    <t>1500 Mt Baseline</t>
+  </si>
+  <si>
+    <t>3B Spend</t>
+  </si>
+  <si>
+    <t>Rhodium Spent</t>
+  </si>
+  <si>
+    <t>Scaling Mt</t>
+  </si>
+  <si>
+    <t>3B Mt</t>
+  </si>
+  <si>
+    <t>Rhodium Mt</t>
+  </si>
+  <si>
+    <t>500 Mt</t>
+  </si>
+  <si>
+    <t>1500 Mt</t>
+  </si>
+  <si>
+    <t>Scaling Spend-500 Mt</t>
+  </si>
+  <si>
+    <t>Scaling Spend-1500 Mt</t>
+  </si>
+  <si>
+    <t>Expected Cost Reduction</t>
+  </si>
+  <si>
+    <t>Original Cost</t>
+  </si>
+  <si>
+    <t>3B</t>
+  </si>
+  <si>
+    <t>Rhoidum</t>
+  </si>
+  <si>
+    <t>Expected Average Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500 Mt </t>
+  </si>
+  <si>
+    <t>Expect Mt Procurement</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -226,7 +284,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -237,6 +295,10 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6616,27 +6678,27 @@
         <v>38</v>
       </c>
       <c r="S10">
-        <f>S3</f>
+        <f t="shared" ref="S10:X10" si="12">S3</f>
         <v>2025</v>
       </c>
       <c r="T10">
-        <f>T3</f>
+        <f t="shared" si="12"/>
         <v>2030</v>
       </c>
       <c r="U10">
-        <f>U3</f>
+        <f t="shared" si="12"/>
         <v>2035</v>
       </c>
       <c r="V10">
-        <f>V3</f>
+        <f t="shared" si="12"/>
         <v>2040</v>
       </c>
       <c r="W10">
-        <f>W3</f>
+        <f t="shared" si="12"/>
         <v>2045</v>
       </c>
       <c r="X10">
-        <f>X3</f>
+        <f t="shared" si="12"/>
         <v>2050</v>
       </c>
     </row>
@@ -6971,7 +7033,7 @@
         <v>0.1166881872151129</v>
       </c>
       <c r="O15" s="6">
-        <f t="shared" ref="O15:O25" si="12">N15</f>
+        <f t="shared" ref="O15:O25" si="13">N15</f>
         <v>0.1166881872151129</v>
       </c>
       <c r="S15" s="6">
@@ -6979,23 +7041,23 @@
         <v>1</v>
       </c>
       <c r="T15" s="6">
-        <f t="shared" ref="T15" si="13">SUM(T11:T14)</f>
+        <f t="shared" ref="T15" si="14">SUM(T11:T14)</f>
         <v>1.0000000000000002</v>
       </c>
       <c r="U15" s="6">
-        <f t="shared" ref="U15" si="14">SUM(U11:U14)</f>
+        <f t="shared" ref="U15" si="15">SUM(U11:U14)</f>
         <v>1</v>
       </c>
       <c r="V15" s="6">
-        <f t="shared" ref="V15" si="15">SUM(V11:V14)</f>
+        <f t="shared" ref="V15" si="16">SUM(V11:V14)</f>
         <v>1</v>
       </c>
       <c r="W15" s="6">
-        <f t="shared" ref="W15" si="16">SUM(W11:W14)</f>
+        <f t="shared" ref="W15" si="17">SUM(W11:W14)</f>
         <v>1.0000000000000002</v>
       </c>
       <c r="X15" s="6">
-        <f t="shared" ref="X15" si="17">SUM(X11:X14)</f>
+        <f t="shared" ref="X15" si="18">SUM(X11:X14)</f>
         <v>0.99999999999999978</v>
       </c>
     </row>
@@ -7030,7 +7092,7 @@
         <v>0.22621410870806635</v>
       </c>
       <c r="O16" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.22621410870806635</v>
       </c>
     </row>
@@ -7065,7 +7127,7 @@
         <v>0.26677556737849328</v>
       </c>
       <c r="O17" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.26677556737849328</v>
       </c>
     </row>
@@ -7090,7 +7152,7 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2">
-        <f t="shared" ref="K18:K25" si="18">G18-$D18</f>
+        <f t="shared" ref="K18:K25" si="19">G18-$D18</f>
         <v>131.88621416666598</v>
       </c>
       <c r="L18" s="1"/>
@@ -7100,7 +7162,7 @@
         <v>0.34646965147739606</v>
       </c>
       <c r="O18" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.34646965147739606</v>
       </c>
     </row>
@@ -7125,7 +7187,7 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>40.575208666666697</v>
       </c>
       <c r="L19" s="1"/>
@@ -7135,7 +7197,7 @@
         <v>0.10659247817665984</v>
       </c>
       <c r="O19" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.10659247817665984</v>
       </c>
     </row>
@@ -7160,7 +7222,7 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>78.49470969999939</v>
       </c>
       <c r="L20" s="1"/>
@@ -7170,7 +7232,7 @@
         <v>0.20620832044060539</v>
       </c>
       <c r="O20" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.20620832044060539</v>
       </c>
     </row>
@@ -7195,7 +7257,7 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>129.7012024</v>
       </c>
       <c r="L21" s="1"/>
@@ -7205,7 +7267,7 @@
         <v>0.34072954990533866</v>
       </c>
       <c r="O21" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.34072954990533866</v>
       </c>
     </row>
@@ -7230,7 +7292,7 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>91.110957666666991</v>
       </c>
       <c r="L22" s="1"/>
@@ -7240,7 +7302,7 @@
         <v>0.19206759514842348</v>
       </c>
       <c r="O22" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.19206759514842348</v>
       </c>
     </row>
@@ -7265,7 +7327,7 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>69.535326666666407</v>
       </c>
       <c r="L23" s="1"/>
@@ -7275,7 +7337,7 @@
         <v>0.14658481606118351</v>
       </c>
       <c r="O23" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.14658481606118351</v>
       </c>
     </row>
@@ -7300,7 +7362,7 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>117.00415539999941</v>
       </c>
       <c r="L24" s="1"/>
@@ -7310,7 +7372,7 @@
         <v>0.2466520748499603</v>
       </c>
       <c r="O24" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.2466520748499603</v>
       </c>
     </row>
@@ -7335,7 +7397,7 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>196.71879259999997</v>
       </c>
       <c r="L25" s="1"/>
@@ -7345,7 +7407,7 @@
         <v>0.41469551394043275</v>
       </c>
       <c r="O25" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.41469551394043275</v>
       </c>
     </row>
@@ -7403,11 +7465,11 @@
       </c>
       <c r="G27" s="2"/>
       <c r="I27" s="2">
-        <f t="shared" ref="I27:J37" si="19">E27-$D27</f>
+        <f t="shared" ref="I27:J37" si="20">E27-$D27</f>
         <v>8.451918749999999</v>
       </c>
       <c r="J27" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.1206363333400589E-2</v>
       </c>
       <c r="K27" s="2"/>
@@ -7421,7 +7483,7 @@
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1">
-        <f t="shared" ref="O27:O29" si="20">SUM(L27:N27)/2</f>
+        <f t="shared" ref="O27:O29" si="21">SUM(L27:N27)/2</f>
         <v>1.1046840333110053</v>
       </c>
     </row>
@@ -7446,11 +7508,11 @@
       </c>
       <c r="G28" s="2"/>
       <c r="I28" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.50086640999999987</v>
       </c>
       <c r="J28" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-1.4435336666667076E-2</v>
       </c>
       <c r="K28" s="2"/>
@@ -7464,7 +7526,7 @@
       </c>
       <c r="N28" s="1"/>
       <c r="O28" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-8.7905321380154999E-2</v>
       </c>
     </row>
@@ -7489,11 +7551,11 @@
       </c>
       <c r="G29" s="2"/>
       <c r="I29" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.28197671333333296</v>
       </c>
       <c r="J29" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-4.0217099999999839E-3</v>
       </c>
       <c r="K29" s="2"/>
@@ -7507,7 +7569,7 @@
       </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-1.6778711930850287E-2</v>
       </c>
     </row>
@@ -7534,15 +7596,15 @@
         <v>30.969142233333301</v>
       </c>
       <c r="I30" s="2">
-        <f t="shared" ref="I30:J37" si="21">E30-$D30</f>
+        <f t="shared" ref="I30:J37" si="22">E30-$D30</f>
         <v>3.1967540733332989</v>
       </c>
       <c r="J30" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1.3077564866666993</v>
       </c>
       <c r="K30" s="2">
-        <f t="shared" ref="K30:K49" si="22">G30-$D30</f>
+        <f t="shared" ref="K30:K49" si="23">G30-$D30</f>
         <v>20.122300660000001</v>
       </c>
       <c r="L30" s="1">
@@ -7585,15 +7647,15 @@
         <v>59.723357540000002</v>
       </c>
       <c r="I31" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>6.7003835433332988</v>
       </c>
       <c r="J31" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3.1119920333332978</v>
       </c>
       <c r="K31" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>39.850773966666701</v>
       </c>
       <c r="L31" s="1">
@@ -7609,7 +7671,7 @@
         <v>0.5885341231136757</v>
       </c>
       <c r="O31" s="1">
-        <f t="shared" ref="O31:O37" si="23">SUM(L31:N31)/3</f>
+        <f t="shared" ref="O31:O37" si="24">SUM(L31:N31)/3</f>
         <v>0.59718983726713759</v>
       </c>
     </row>
@@ -7636,15 +7698,15 @@
         <v>6.8402470766666603</v>
       </c>
       <c r="I32" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.79996674999999984</v>
       </c>
       <c r="J32" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.37579457666666993</v>
       </c>
       <c r="K32" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4.5948511033333297</v>
       </c>
       <c r="L32" s="1">
@@ -7660,7 +7722,7 @@
         <v>6.7858824202514739E-2</v>
       </c>
       <c r="O32" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.0774412070130452E-2</v>
       </c>
     </row>
@@ -7687,15 +7749,15 @@
         <v>4.4015445833333304</v>
       </c>
       <c r="I33" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.59424915</v>
       </c>
       <c r="J33" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.30920435333332996</v>
       </c>
       <c r="K33" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>3.1439917300000007</v>
       </c>
       <c r="L33" s="1">
@@ -7711,7 +7773,7 @@
         <v>4.6431881534846134E-2</v>
       </c>
       <c r="O33" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5.3210830637341631E-2</v>
       </c>
     </row>
@@ -7738,15 +7800,15 @@
         <v>128.53779913333301</v>
       </c>
       <c r="I34" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7.0038580333334011</v>
       </c>
       <c r="J34" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4.3877771666667016</v>
       </c>
       <c r="K34" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>78.015727166666409</v>
       </c>
       <c r="L34" s="1">
@@ -7762,7 +7824,7 @@
         <v>0.49492086132824242</v>
       </c>
       <c r="O34" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.46823589811557143</v>
       </c>
     </row>
@@ -7789,15 +7851,15 @@
         <v>30.917709349999999</v>
       </c>
       <c r="I35" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.7368415166666988</v>
       </c>
       <c r="J35" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1.1457209499999994</v>
       </c>
       <c r="K35" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>20.815231433333398</v>
       </c>
       <c r="L35" s="1">
@@ -7813,7 +7875,7 @@
         <v>0.13204891685139269</v>
       </c>
       <c r="O35" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.12113894109271006</v>
       </c>
     </row>
@@ -7840,15 +7902,15 @@
         <v>44.909156233333299</v>
       </c>
       <c r="I36" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.3108711899999985</v>
       </c>
       <c r="J36" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2.4800577266665993</v>
       </c>
       <c r="K36" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>30.7995309233333</v>
       </c>
       <c r="L36" s="1">
@@ -7864,7 +7926,7 @@
         <v>0.19538791634303879</v>
       </c>
       <c r="O36" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.22200081594740231</v>
       </c>
     </row>
@@ -7891,15 +7953,15 @@
         <v>41.950605400000001</v>
       </c>
       <c r="I37" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.8022464799999991</v>
       </c>
       <c r="J37" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1.9980797466667006</v>
       </c>
       <c r="K37" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>28.002241813333399</v>
       </c>
       <c r="L37" s="1">
@@ -7915,7 +7977,7 @@
         <v>0.17764230547732618</v>
       </c>
       <c r="O37" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.1886243448443162</v>
       </c>
     </row>
@@ -7940,7 +8002,7 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>63.335395566666008</v>
       </c>
       <c r="L38" s="1"/>
@@ -7975,7 +8037,7 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>34.464338333333302</v>
       </c>
       <c r="L39" s="1"/>
@@ -7985,7 +8047,7 @@
         <v>0.14170714506974419</v>
       </c>
       <c r="O39" s="6">
-        <f t="shared" ref="O39:O49" si="24">N39</f>
+        <f t="shared" ref="O39:O49" si="25">N39</f>
         <v>0.14170714506974419</v>
       </c>
     </row>
@@ -8010,7 +8072,7 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>70.204037200000002</v>
       </c>
       <c r="L40" s="1"/>
@@ -8020,7 +8082,7 @@
         <v>0.28865819467539838</v>
       </c>
       <c r="O40" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.28865819467539838</v>
       </c>
     </row>
@@ -8045,7 +8107,7 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>75.204419399999409</v>
       </c>
       <c r="L41" s="1"/>
@@ -8055,7 +8117,7 @@
         <v>0.30921828432418608</v>
       </c>
       <c r="O41" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.30921828432418608</v>
       </c>
     </row>
@@ -8080,7 +8142,7 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>58.164087666666973</v>
       </c>
       <c r="L42" s="1"/>
@@ -8090,7 +8152,7 @@
         <v>0.15285316937789162</v>
       </c>
       <c r="O42" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.15285316937789162</v>
       </c>
     </row>
@@ -8115,7 +8177,7 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>55.774228399999991</v>
       </c>
       <c r="L43" s="1"/>
@@ -8125,7 +8187,7 @@
         <v>0.14657270357963723</v>
       </c>
       <c r="O43" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.14657270357963723</v>
       </c>
     </row>
@@ -8150,7 +8212,7 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>117.2195210999997</v>
       </c>
       <c r="L44" s="1"/>
@@ -8160,7 +8222,7 @@
         <v>0.30804876396886721</v>
       </c>
       <c r="O44" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.30804876396886721</v>
       </c>
     </row>
@@ -8185,7 +8247,7 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>149.364777466666</v>
       </c>
       <c r="L45" s="1"/>
@@ -8195,7 +8257,7 @@
         <v>0.39252536307360403</v>
       </c>
       <c r="O45" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.39252536307360403</v>
       </c>
     </row>
@@ -8220,7 +8282,7 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>37.581367999999998</v>
       </c>
       <c r="L46" s="1"/>
@@ -8230,7 +8292,7 @@
         <v>7.9254516693036001E-2</v>
       </c>
       <c r="O46" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>7.9254516693036001E-2</v>
       </c>
     </row>
@@ -8255,7 +8317,7 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>91.321723166666999</v>
       </c>
       <c r="L47" s="1"/>
@@ -8265,7 +8327,7 @@
         <v>0.19258636442264218</v>
       </c>
       <c r="O47" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.19258636442264218</v>
       </c>
     </row>
@@ -8290,7 +8352,7 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>173.20538766666601</v>
       </c>
       <c r="L48" s="1"/>
@@ -8300,7 +8362,7 @@
         <v>0.36526901543742513</v>
       </c>
       <c r="O48" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.36526901543742513</v>
       </c>
     </row>
@@ -8325,7 +8387,7 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>172.07734133333292</v>
       </c>
       <c r="L49" s="1"/>
@@ -8335,7 +8397,7 @@
         <v>0.36289010344689659</v>
       </c>
       <c r="O49" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.36289010344689659</v>
       </c>
     </row>
@@ -8387,11 +8449,11 @@
       </c>
       <c r="G51" s="2"/>
       <c r="I51" s="2">
-        <f t="shared" ref="I51:J61" si="25">E51-$D51</f>
+        <f t="shared" ref="I51:J61" si="26">E51-$D51</f>
         <v>-12.3143563033333</v>
       </c>
       <c r="J51" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-12.3143563033333</v>
       </c>
       <c r="K51" s="2"/>
@@ -8405,7 +8467,7 @@
       </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1">
-        <f t="shared" ref="O51:O53" si="26">SUM(L51:N51)/2</f>
+        <f t="shared" ref="O51:O53" si="27">SUM(L51:N51)/2</f>
         <v>0.92925269976099745</v>
       </c>
     </row>
@@ -8424,11 +8486,11 @@
       </c>
       <c r="G52" s="2"/>
       <c r="I52" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-0.75909940333333303</v>
       </c>
       <c r="J52" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-0.75909940333333303</v>
       </c>
       <c r="K52" s="2"/>
@@ -8442,7 +8504,7 @@
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>5.7282342053357901E-2</v>
       </c>
     </row>
@@ -8461,11 +8523,11 @@
       </c>
       <c r="G53" s="2"/>
       <c r="I53" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-0.17843617000000001</v>
       </c>
       <c r="J53" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-0.17843617000000001</v>
       </c>
       <c r="K53" s="2"/>
@@ -8479,7 +8541,7 @@
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1.3464958185644634E-2</v>
       </c>
     </row>
@@ -8494,15 +8556,15 @@
         <v>21</v>
       </c>
       <c r="I54" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="J54" s="2">
-        <f t="shared" ref="J54:J61" si="27">F54-$D54</f>
+        <f t="shared" ref="J54:J61" si="28">F54-$D54</f>
         <v>0</v>
       </c>
       <c r="K54" s="2">
-        <f t="shared" ref="K54:K73" si="28">G54-$D54</f>
+        <f t="shared" ref="K54:K73" si="29">G54-$D54</f>
         <v>0</v>
       </c>
       <c r="L54" s="1">
@@ -8536,15 +8598,15 @@
         <v>17.71107679</v>
       </c>
       <c r="I55" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-17.71107679</v>
       </c>
       <c r="J55" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-17.71107679</v>
       </c>
       <c r="K55" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-17.71107679</v>
       </c>
       <c r="L55" s="1">
@@ -8560,7 +8622,7 @@
         <v>0.89918935245526366</v>
       </c>
       <c r="O55" s="1">
-        <f t="shared" ref="O55:O61" si="29">SUM(L55:N55)/3</f>
+        <f t="shared" ref="O55:O61" si="30">SUM(L55:N55)/3</f>
         <v>0.89918935245526355</v>
       </c>
     </row>
@@ -8578,15 +8640,15 @@
         <v>1.3467701133333301</v>
       </c>
       <c r="I56" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-1.3467701133333301</v>
       </c>
       <c r="J56" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-1.3467701133333301</v>
       </c>
       <c r="K56" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-1.3467701133333301</v>
       </c>
       <c r="L56" s="1">
@@ -8602,7 +8664,7 @@
         <v>6.8375365341877617E-2</v>
       </c>
       <c r="O56" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>6.8375365341877617E-2</v>
       </c>
     </row>
@@ -8620,15 +8682,15 @@
         <v>0.63886852333333299</v>
       </c>
       <c r="I57" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-0.63886852333333299</v>
       </c>
       <c r="J57" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-0.63886852333333299</v>
       </c>
       <c r="K57" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-0.63886852333333299</v>
       </c>
       <c r="L57" s="1">
@@ -8644,7 +8706,7 @@
         <v>3.2435282202858663E-2</v>
       </c>
       <c r="O57" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3.2435282202858663E-2</v>
       </c>
     </row>
@@ -8662,15 +8724,15 @@
         <v>7.4184241999999996</v>
       </c>
       <c r="I58" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-7.4184241999999996</v>
       </c>
       <c r="J58" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-7.4184241999999996</v>
       </c>
       <c r="K58" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-7.4184241999999996</v>
       </c>
       <c r="L58" s="1">
@@ -8686,7 +8748,7 @@
         <v>0.24910054245369137</v>
       </c>
       <c r="O58" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.24910054245369137</v>
       </c>
     </row>
@@ -8704,15 +8766,15 @@
         <v>6.2897941333333298</v>
       </c>
       <c r="I59" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-6.2897941333333298</v>
       </c>
       <c r="J59" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-6.2897941333333298</v>
       </c>
       <c r="K59" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-6.2897941333333298</v>
       </c>
       <c r="L59" s="1">
@@ -8728,7 +8790,7 @@
         <v>0.21120268783434873</v>
       </c>
       <c r="O59" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.21120268783434873</v>
       </c>
     </row>
@@ -8746,15 +8808,15 @@
         <v>8.3409771500000005</v>
       </c>
       <c r="I60" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-8.3409771500000005</v>
       </c>
       <c r="J60" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-8.3409771500000005</v>
       </c>
       <c r="K60" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-8.3409771500000005</v>
       </c>
       <c r="L60" s="1">
@@ -8770,7 +8832,7 @@
         <v>0.28007860923602146</v>
       </c>
       <c r="O60" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.28007860923602146</v>
       </c>
     </row>
@@ -8788,15 +8850,15 @@
         <v>7.7316477333333298</v>
       </c>
       <c r="I61" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-7.7316477333333298</v>
       </c>
       <c r="J61" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-7.7316477333333298</v>
       </c>
       <c r="K61" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-7.7316477333333298</v>
       </c>
       <c r="L61" s="1">
@@ -8812,7 +8874,7 @@
         <v>0.25961816047593855</v>
       </c>
       <c r="O61" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.25961816047593855</v>
       </c>
     </row>
@@ -8831,7 +8893,7 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L62" s="1"/>
@@ -8863,7 +8925,7 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-9.9285394999999994</v>
       </c>
       <c r="L63" s="1"/>
@@ -8873,7 +8935,7 @@
         <v>0.22242627804977147</v>
       </c>
       <c r="O63" s="6">
-        <f t="shared" ref="O63:O73" si="30">N63</f>
+        <f t="shared" ref="O63:O73" si="31">N63</f>
         <v>0.22242627804977147</v>
       </c>
     </row>
@@ -8895,7 +8957,7 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-13.548768566666601</v>
       </c>
       <c r="L64" s="1"/>
@@ -8905,7 +8967,7 @@
         <v>0.30352925165291322</v>
       </c>
       <c r="O64" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.30352925165291322</v>
       </c>
     </row>
@@ -8927,7 +8989,7 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-21.1601313</v>
       </c>
       <c r="L65" s="1"/>
@@ -8937,7 +8999,7 @@
         <v>0.47404447029731539</v>
       </c>
       <c r="O65" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.47404447029731539</v>
       </c>
     </row>
@@ -8956,7 +9018,7 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L66" s="1"/>
@@ -8966,7 +9028,7 @@
         <v>0</v>
       </c>
       <c r="O66" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
@@ -8988,7 +9050,7 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-11.7713416333333</v>
       </c>
       <c r="L67" s="1"/>
@@ -8998,7 +9060,7 @@
         <v>0.17647793498569347</v>
       </c>
       <c r="O67" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.17647793498569347</v>
       </c>
     </row>
@@ -9020,7 +9082,7 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-15.0971010666666</v>
       </c>
       <c r="L68" s="1"/>
@@ -9030,7 +9092,7 @@
         <v>0.22633828016434676</v>
       </c>
       <c r="O68" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.22633828016434676</v>
       </c>
     </row>
@@ -9052,7 +9114,7 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-39.833049666666597</v>
       </c>
       <c r="L69" s="1"/>
@@ -9062,7 +9124,7 @@
         <v>0.59718378484995971</v>
       </c>
       <c r="O69" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.59718378484995971</v>
       </c>
     </row>
@@ -9081,7 +9143,7 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L70" s="1"/>
@@ -9091,7 +9153,7 @@
         <v>0</v>
       </c>
       <c r="O70" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
@@ -9113,7 +9175,7 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-15.9971258333333</v>
       </c>
       <c r="L71" s="1"/>
@@ -9123,7 +9185,7 @@
         <v>0.16057921079720025</v>
       </c>
       <c r="O71" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.16057921079720025</v>
       </c>
     </row>
@@ -9145,7 +9207,7 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-18.685675066666601</v>
       </c>
       <c r="L72" s="1"/>
@@ -9155,7 +9217,7 @@
         <v>0.18756687836798919</v>
       </c>
       <c r="O72" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.18756687836798919</v>
       </c>
     </row>
@@ -9177,7 +9239,7 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-64.938599366666594</v>
       </c>
       <c r="L73" s="1"/>
@@ -9187,11 +9249,836 @@
         <v>0.65185391083481048</v>
       </c>
       <c r="O73" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.65185391083481048</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{421118D0-4821-4939-83D8-1E9651E01371}">
+  <dimension ref="A1:R34"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18">
+      <c r="A1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>45</v>
+      </c>
+      <c r="R1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2">
+        <v>2025</v>
+      </c>
+      <c r="B2" s="2">
+        <v>279.34412401828746</v>
+      </c>
+      <c r="C2" s="2">
+        <v>279.34416753372324</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2">
+        <f>B2*K2</f>
+        <v>13.967206200914374</v>
+      </c>
+      <c r="F2" s="2">
+        <f>C2*P2</f>
+        <v>13.967208376686163</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0.05</v>
+      </c>
+      <c r="L2" s="2">
+        <f>G2/$B2</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="2">
+        <f>H2/$B2</f>
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0.05</v>
+      </c>
+      <c r="Q2" s="2">
+        <f>G2/$C2</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="2">
+        <f>H2/$C2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3">
+        <v>2030</v>
+      </c>
+      <c r="B3" s="2">
+        <v>232.38733035426884</v>
+      </c>
+      <c r="C3" s="2">
+        <v>232.67467939439376</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2">
+        <f t="shared" ref="E3:E7" si="0">B3*K3</f>
+        <v>1161.9366517713443</v>
+      </c>
+      <c r="F3" s="2">
+        <f t="shared" ref="F3:F7" si="1">C3*P3</f>
+        <v>1163.3733969719688</v>
+      </c>
+      <c r="G3">
+        <v>3300</v>
+      </c>
+      <c r="H3">
+        <v>20000</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3" s="2">
+        <f t="shared" ref="L3:M7" si="2">G3/$B3</f>
+        <v>14.200429924338948</v>
+      </c>
+      <c r="M3" s="2">
+        <f t="shared" si="2"/>
+        <v>86.063211662660294</v>
+      </c>
+      <c r="P3">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="2">
+        <f t="shared" ref="Q3:R7" si="3">G3/$C3</f>
+        <v>14.18289264903791</v>
+      </c>
+      <c r="R3" s="2">
+        <f t="shared" si="3"/>
+        <v>85.956925145684309</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4">
+        <v>2035</v>
+      </c>
+      <c r="B4" s="2">
+        <v>205.02811328263422</v>
+      </c>
+      <c r="C4" s="2">
+        <v>205.58835604353231</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2">
+        <f t="shared" si="0"/>
+        <v>2050.2811328263424</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" si="1"/>
+        <v>2055.883560435323</v>
+      </c>
+      <c r="G4">
+        <v>3300</v>
+      </c>
+      <c r="H4">
+        <v>35000</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+      <c r="L4" s="2">
+        <f t="shared" si="2"/>
+        <v>16.095353691573518</v>
+      </c>
+      <c r="M4" s="2">
+        <f t="shared" si="2"/>
+        <v>170.70829672881004</v>
+      </c>
+      <c r="P4">
+        <v>10</v>
+      </c>
+      <c r="Q4" s="2">
+        <f t="shared" si="3"/>
+        <v>16.051492718299869</v>
+      </c>
+      <c r="R4" s="2">
+        <f t="shared" si="3"/>
+        <v>170.24310458802893</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5">
+        <v>2040</v>
+      </c>
+      <c r="B5" s="2">
+        <v>188.42537131411288</v>
+      </c>
+      <c r="C5" s="2">
+        <v>190.99635856601432</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>50000</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
+        <f t="shared" si="2"/>
+        <v>265.35704640670673</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R5" s="2">
+        <f t="shared" si="3"/>
+        <v>261.78509567091265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6">
+        <v>2045</v>
+      </c>
+      <c r="B6" s="2">
+        <v>172.34962171587082</v>
+      </c>
+      <c r="C6" s="2">
+        <v>183.98987579660619</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>75000</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
+        <f t="shared" si="2"/>
+        <v>435.1619646931527</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
+        <f t="shared" si="3"/>
+        <v>407.63112467617321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7">
+        <v>2050</v>
+      </c>
+      <c r="B7" s="2">
+        <v>161.88185562991737</v>
+      </c>
+      <c r="C7" s="2">
+        <v>200.02112692237375</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>100000</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <f t="shared" si="2"/>
+        <v>617.73445585287084</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
+        <f t="shared" si="3"/>
+        <v>499.9471882728119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="B11" s="8">
+        <v>1.452462703007266E-3</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="B12" s="8">
+        <v>5.2834255744793446E-2</v>
+      </c>
+      <c r="C12" s="8">
+        <v>8.2558409986148301E-2</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.1383767815890895</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="B13" s="8">
+        <v>8.1938836503967882E-2</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0.10389919717415493</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0.16928290688878872</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="B14" s="8">
+        <v>8.1938836503967744E-2</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0.10389919717415487</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0.18857209957880355</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="B15" s="8">
+        <v>8.1938836503967785E-2</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0.10389919717415484</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0.20434010167735797</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="B16" s="8">
+        <v>8.1938836503967813E-2</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.10389919717415486</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0.21704925001897787</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="F18" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="B20" s="2">
+        <f>$B2*(1-B11)</f>
+        <v>278.93838709684667</v>
+      </c>
+      <c r="C20" s="2">
+        <f t="shared" ref="C20:D20" si="4">$B2*(1-C11)</f>
+        <v>279.34412401828746</v>
+      </c>
+      <c r="D20" s="2">
+        <f t="shared" si="4"/>
+        <v>279.34412401828746</v>
+      </c>
+      <c r="F20" s="2">
+        <f>$C2*(1-B11)</f>
+        <v>278.93843054907791</v>
+      </c>
+      <c r="G20" s="2">
+        <f t="shared" ref="G20:H25" si="5">$C2*(1-C11)</f>
+        <v>279.34416753372324</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="5"/>
+        <v>279.34416753372324</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="B21" s="2">
+        <f t="shared" ref="B21:D25" si="6">$B3*(1-B12)</f>
+        <v>220.1093187104816</v>
+      </c>
+      <c r="C21" s="2">
+        <f t="shared" si="6"/>
+        <v>213.20180185929465</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" si="6"/>
+        <v>200.23031949776458</v>
+      </c>
+      <c r="F21" s="2">
+        <f t="shared" ref="F21:F25" si="7">$C3*(1-B12)</f>
+        <v>220.38148587793256</v>
+      </c>
+      <c r="G21" s="2">
+        <f t="shared" si="5"/>
+        <v>213.4654278195558</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="5"/>
+        <v>200.47790610252432</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="B22" s="2">
+        <f t="shared" si="6"/>
+        <v>188.22834822965143</v>
+      </c>
+      <c r="C22" s="2">
+        <f t="shared" si="6"/>
+        <v>183.72585691443683</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="6"/>
+        <v>170.32035827222603</v>
+      </c>
+      <c r="F22" s="2">
+        <f t="shared" si="7"/>
+        <v>188.74268535056177</v>
+      </c>
+      <c r="G22" s="2">
+        <f t="shared" si="5"/>
+        <v>184.22789090225498</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="5"/>
+        <v>170.78576150999589</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="B23" s="2">
+        <f t="shared" si="6"/>
+        <v>172.98601562080637</v>
+      </c>
+      <c r="C23" s="2">
+        <f t="shared" si="6"/>
+        <v>168.84812650733451</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="6"/>
+        <v>152.89360343149494</v>
+      </c>
+      <c r="F23" s="2">
+        <f t="shared" si="7"/>
+        <v>175.34633916862049</v>
+      </c>
+      <c r="G23" s="2">
+        <f t="shared" si="5"/>
+        <v>171.15199024781842</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="5"/>
+        <v>154.97977421931498</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="B24" s="2">
+        <f t="shared" si="6"/>
+        <v>158.22749424057338</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" si="6"/>
+        <v>154.44263438632257</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="6"/>
+        <v>137.1316824903956</v>
+      </c>
+      <c r="F24" s="2">
+        <f t="shared" si="7"/>
+        <v>168.91395944532272</v>
+      </c>
+      <c r="G24" s="2">
+        <f t="shared" si="5"/>
+        <v>164.87347541316635</v>
+      </c>
+      <c r="H24" s="2">
+        <f t="shared" si="5"/>
+        <v>146.39336586872321</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="B25" s="2">
+        <f t="shared" si="6"/>
+        <v>148.61744472849864</v>
+      </c>
+      <c r="C25" s="2">
+        <f t="shared" si="6"/>
+        <v>145.06246079290651</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="6"/>
+        <v>126.74552027376335</v>
+      </c>
+      <c r="F25" s="2">
+        <f t="shared" si="7"/>
+        <v>183.63162850614196</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" si="5"/>
+        <v>179.23909241726938</v>
+      </c>
+      <c r="H25" s="2">
+        <f t="shared" si="5"/>
+        <v>156.60669133592174</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="F27" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="B29" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="C29" s="2">
+        <f>G2/C20</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
+        <f>H2/D20</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="G29" s="2">
+        <f>G2/G20</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
+        <f>H2/H20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="B30" s="2">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2">
+        <f t="shared" ref="C30:D34" si="8">G3/C21</f>
+        <v>15.478293200251088</v>
+      </c>
+      <c r="D30" s="2">
+        <f t="shared" si="8"/>
+        <v>99.884972716248825</v>
+      </c>
+      <c r="F30" s="2">
+        <v>5</v>
+      </c>
+      <c r="G30" s="2">
+        <f t="shared" ref="G30:H34" si="9">G3/G21</f>
+        <v>15.459177786810139</v>
+      </c>
+      <c r="H30" s="2">
+        <f t="shared" si="9"/>
+        <v>99.761616573209864</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="B31" s="2">
+        <v>10</v>
+      </c>
+      <c r="C31" s="2">
+        <f t="shared" si="8"/>
+        <v>17.961543657607468</v>
+      </c>
+      <c r="D31" s="2">
+        <f t="shared" si="8"/>
+        <v>205.49510554727041</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2">
+        <f t="shared" si="9"/>
+        <v>17.912597185139937</v>
+      </c>
+      <c r="H31" s="2">
+        <f t="shared" si="9"/>
+        <v>204.93511690054731</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="B32" s="2">
+        <f t="shared" ref="B30:B34" si="10">B23*K5</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <f t="shared" si="8"/>
+        <v>327.02479945410442</v>
+      </c>
+      <c r="F32" s="2">
+        <f t="shared" ref="F32:F34" si="11">F23*O5</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <f t="shared" si="9"/>
+        <v>322.62274385071692</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <f t="shared" si="8"/>
+        <v>546.9195640128811</v>
+      </c>
+      <c r="F33" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="2">
+        <f t="shared" si="9"/>
+        <v>512.31829772433468</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="2">
+        <f t="shared" si="8"/>
+        <v>788.98252012383159</v>
+      </c>
+      <c r="F34" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="2">
+        <f t="shared" si="9"/>
+        <v>638.54231991594634</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="F27:H27"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/data_analysis/procurement.xlsx
+++ b/data/data_analysis/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5FF859-71AC-4308-B70E-1505E9116ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD3D96C-3519-4BA0-83AB-6AC8BC56C820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="3" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
   </bookViews>

--- a/data/data_analysis/procurement.xlsx
+++ b/data/data_analysis/procurement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD3D96C-3519-4BA0-83AB-6AC8BC56C820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC36D37D-B449-4704-A25D-3B205B3D084F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="3" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{4A617452-901D-46F6-B294-E017C63BDF58}"/>
   </bookViews>
   <sheets>
     <sheet name="Scaling" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="58">
   <si>
     <t>Scenario</t>
   </si>
@@ -225,7 +225,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -295,7 +295,7 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -389,162 +389,102 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Scaling!$D$2:$D$25</c:f>
+              <c:f>Scaling!$D$2:$D$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>22.65</c:v>
+                  <c:v>43.279331480251088</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38.921038279999998</c:v>
+                  <c:v>75.213227297607474</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>72.201683639999999</c:v>
+                  <c:v>127.68601099624883</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>95.181038279999996</c:v>
+                  <c:v>262.74678918727039</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>215.76168364</c:v>
+                  <c:v>444.92526225410444</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>364.81046279999998</c:v>
+                  <c:v>789.71625141288109</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>648.96668739999996</c:v>
+                  <c:v>1288.9825201238316</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1078.26</c:v>
+                  <c:v>50.091791316810138</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>22.65</c:v>
+                  <c:v>106.75836904513994</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>45.752613529999998</c:v>
+                  <c:v>134.39423010320985</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>103.69577185999999</c:v>
+                  <c:v>293.78088876054733</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>102.04261353</c:v>
+                  <c:v>550.54580175071692</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>246.34577186000001</c:v>
+                  <c:v>1097.0272738243348</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>470.9930579</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>965.18897609999999</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1974.19</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>22.65</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>30.40962717</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>44.244627790000003</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>82.319627170000004</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>180.40462779000001</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>275.22833609000003</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>461.17875827</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>691.29</c:v>
+                  <c:v>2138.5423199159463</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Scaling!$H$2:$H$25</c:f>
+              <c:f>Scaling!$H$2:$H$23</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>6.0606060606060606E-4</c:v>
+                  <c:v>-0.14212121212121212</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.0909090909090905E-3</c:v>
+                  <c:v>-0.31393939393939396</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2.2121212121212121E-2</c:v>
+                  <c:v>8.7800000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.7499999999999999E-3</c:v>
+                  <c:v>-0.20100000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.7371428571428571E-2</c:v>
+                  <c:v>0.20044000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.1939999999999998E-2</c:v>
+                  <c:v>0.2898</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.4799999999999999E-2</c:v>
+                  <c:v>0.45656000000000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-2.3140000000000001E-2</c:v>
+                  <c:v>-0.18878787878787878</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.0606060606060606E-4</c:v>
+                  <c:v>-0.49484848484848487</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.090909090909091E-2</c:v>
+                  <c:v>0.10155</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-2.0909090909090908E-2</c:v>
+                  <c:v>0.10357142857142858</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.3499999999999998E-3</c:v>
+                  <c:v>0.2525</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.3771428571428572E-2</c:v>
+                  <c:v>0.30621333333333334</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.11934</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.16401333333333334</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.10825</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>-3.0303030303030303E-4</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>-7.575757575757576E-3</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.17303030303030303</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>-2.15E-3</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>7.8085714285714286E-2</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>6.4999999999999997E-3</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>5.0680000000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.10559</c:v>
+                  <c:v>0.17591000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -923,36 +863,36 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Scaling!$E$2:$E$25</c:f>
+              <c:f>Scaling!$E$2:$E$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>13.5</c:v>
+                  <c:v>27.80103828</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>57.251683640000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>27.80103828</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>57.251683640000003</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>27.80103828</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>57.251683640000003</c:v>
+                  <c:v>117.9004628</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>117.9004628</c:v>
+                  <c:v>242.7966874</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>242.7966874</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>500</c:v>
+                  <c:v>34.63261353</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>13.5</c:v>
+                  <c:v>88.845771859999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>34.63261353</c:v>
@@ -961,124 +901,64 @@
                   <c:v>88.845771859999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>34.63261353</c:v>
+                  <c:v>227.9230579</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>88.845771859999999</c:v>
+                  <c:v>584.70897609999997</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>227.9230579</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>584.70897609999997</c:v>
-                </c:pt>
-                <c:pt idx="15">
                   <c:v>1500</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>13.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>20.149627169999999</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>30.074627790000001</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20.149627169999999</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>30.074627790000001</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>44.888336090000003</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>66.998758269999996</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Scaling!$H$2:$H$25</c:f>
+              <c:f>Scaling!$H$2:$H$23</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>6.0606060606060606E-4</c:v>
+                  <c:v>-0.14212121212121212</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.0909090909090905E-3</c:v>
+                  <c:v>-0.31393939393939396</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2.2121212121212121E-2</c:v>
+                  <c:v>8.7800000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.7499999999999999E-3</c:v>
+                  <c:v>-0.20100000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.7371428571428571E-2</c:v>
+                  <c:v>0.20044000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.1939999999999998E-2</c:v>
+                  <c:v>0.2898</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.4799999999999999E-2</c:v>
+                  <c:v>0.45656000000000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-2.3140000000000001E-2</c:v>
+                  <c:v>-0.18878787878787878</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.0606060606060606E-4</c:v>
+                  <c:v>-0.49484848484848487</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.090909090909091E-2</c:v>
+                  <c:v>0.10155</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-2.0909090909090908E-2</c:v>
+                  <c:v>0.10357142857142858</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.3499999999999998E-3</c:v>
+                  <c:v>0.2525</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.3771428571428572E-2</c:v>
+                  <c:v>0.30621333333333334</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.11934</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.16401333333333334</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.10825</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>-3.0303030303030303E-4</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>-7.575757575757576E-3</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.17303030303030303</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>-2.15E-3</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>7.8085714285714286E-2</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>6.4999999999999997E-3</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>5.0680000000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.10559</c:v>
+                  <c:v>0.17591000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1462,162 +1342,102 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Scaling!$G$2:$G$25</c:f>
+              <c:f>Scaling!$G$2:$G$23</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>0.40397350993377479</c:v>
+                  <c:v>0.35763706764541942</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.28570666383569043</c:v>
+                  <c:v>0.23880830942855746</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.20705888348173698</c:v>
+                  <c:v>0.78227028894483408</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.70791410996992965</c:v>
+                  <c:v>0.78210320355544138</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.73465314751842192</c:v>
+                  <c:v>0.73501063481384199</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.67681721106601989</c:v>
+                  <c:v>0.69255199324363337</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.62587187892072993</c:v>
+                  <c:v>0.61209714469055376</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.53628994862092627</c:v>
+                  <c:v>0.30861698854083991</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.40397350993377479</c:v>
+                  <c:v>0.16778635104069525</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.24304622494862749</c:v>
+                  <c:v>0.74230580060317009</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.14320738187907053</c:v>
+                  <c:v>0.69757810919955465</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.66060636500829928</c:v>
+                  <c:v>0.5860052748105381</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.63934525366852379</c:v>
+                  <c:v>0.46700598056997034</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.51607979337055954</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.3942025959904662</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.24019471276827462</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.40397350993377479</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.33739315324858032</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.32026487073765486</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.75522693842637822</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.83329347944993759</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.83690510676443775</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.85472280093443687</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.85534290963271564</c:v>
+                  <c:v>0.29858764728165105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Scaling!$H$2:$H$25</c:f>
+              <c:f>Scaling!$H$2:$H$23</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>6.0606060606060606E-4</c:v>
+                  <c:v>-0.14212121212121212</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.0909090909090905E-3</c:v>
+                  <c:v>-0.31393939393939396</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2.2121212121212121E-2</c:v>
+                  <c:v>8.7800000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.7499999999999999E-3</c:v>
+                  <c:v>-0.20100000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.7371428571428571E-2</c:v>
+                  <c:v>0.20044000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.1939999999999998E-2</c:v>
+                  <c:v>0.2898</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.4799999999999999E-2</c:v>
+                  <c:v>0.45656000000000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-2.3140000000000001E-2</c:v>
+                  <c:v>-0.18878787878787878</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.0606060606060606E-4</c:v>
+                  <c:v>-0.49484848484848487</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.090909090909091E-2</c:v>
+                  <c:v>0.10155</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-2.0909090909090908E-2</c:v>
+                  <c:v>0.10357142857142858</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.3499999999999998E-3</c:v>
+                  <c:v>0.2525</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.3771428571428572E-2</c:v>
+                  <c:v>0.30621333333333334</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.11934</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.16401333333333334</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.10825</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>-3.0303030303030303E-4</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>-7.575757575757576E-3</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.17303030303030303</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>-2.15E-3</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>7.8085714285714286E-2</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>6.4999999999999997E-3</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>5.0680000000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.10559</c:v>
+                  <c:v>0.17591000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4229,13 +4049,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>33337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>109537</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4265,13 +4085,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>33337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>109537</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4301,13 +4121,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4738,14 +4558,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B537AA0D-F5C4-4357-8465-DF25FED59988}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -4785,34 +4610,34 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C2">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:D25" si="0">E2+F2</f>
-        <v>22.65</v>
+        <f t="shared" ref="D2:D15" si="0">E2+F2</f>
+        <v>43.279331480251088</v>
       </c>
       <c r="E2">
-        <v>13.5</v>
+        <v>27.80103828</v>
       </c>
       <c r="F2">
-        <v>9.15</v>
+        <v>15.478293200251088</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G25" si="1">(D2-E2)/D2</f>
-        <v>0.40397350993377479</v>
+        <f t="shared" ref="G2:G15" si="1">(D2-E2)/D2</f>
+        <v>0.35763706764541942</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H25" si="2">(J2-I2)/I2</f>
-        <v>6.0606060606060606E-4</v>
+        <f t="shared" ref="H2:H15" si="2">(J2-I2)/I2</f>
+        <v>-0.14212121212121212</v>
       </c>
       <c r="I2">
         <v>3300</v>
       </c>
       <c r="J2">
-        <v>3302</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4820,69 +4645,69 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C3">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="D3">
         <f t="shared" si="0"/>
-        <v>38.921038279999998</v>
+        <v>75.213227297607474</v>
       </c>
       <c r="E3">
-        <v>27.80103828</v>
+        <v>57.251683640000003</v>
       </c>
       <c r="F3">
-        <v>11.12</v>
+        <v>17.961543657607468</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" si="1"/>
-        <v>0.28570666383569043</v>
+        <v>0.23880830942855746</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" si="2"/>
-        <v>9.0909090909090905E-3</v>
+        <v>-0.31393939393939396</v>
       </c>
       <c r="I3">
         <v>3300</v>
       </c>
       <c r="J3">
-        <v>3330</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C4">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>72.201683639999999</v>
+        <v>127.68601099624883</v>
       </c>
       <c r="E4">
-        <v>57.251683640000003</v>
+        <v>27.80103828</v>
       </c>
       <c r="F4">
-        <v>14.95</v>
+        <v>99.884972716248825</v>
       </c>
       <c r="G4" s="1">
         <f t="shared" si="1"/>
-        <v>0.20705888348173698</v>
+        <v>0.78227028894483408</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="2"/>
-        <v>-2.2121212121212121E-2</v>
+        <v>8.7800000000000003E-2</v>
       </c>
       <c r="I4">
-        <v>3300</v>
+        <v>20000</v>
       </c>
       <c r="J4">
-        <v>3227</v>
+        <v>21756</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4890,34 +4715,34 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C5">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>95.181038279999996</v>
+        <v>262.74678918727039</v>
       </c>
       <c r="E5">
-        <v>27.80103828</v>
+        <v>57.251683640000003</v>
       </c>
       <c r="F5">
-        <v>67.38</v>
+        <v>205.49510554727041</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" si="1"/>
-        <v>0.70791410996992965</v>
+        <v>0.78210320355544138</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="2"/>
-        <v>7.7499999999999999E-3</v>
+        <v>-0.20100000000000001</v>
       </c>
       <c r="I5">
-        <v>20000</v>
+        <v>35000</v>
       </c>
       <c r="J5">
-        <v>20155</v>
+        <v>27965</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4925,34 +4750,34 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C6">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>215.76168364</v>
+        <v>444.92526225410444</v>
       </c>
       <c r="E6">
-        <v>57.251683640000003</v>
+        <v>117.9004628</v>
       </c>
       <c r="F6">
-        <v>158.51</v>
+        <v>327.02479945410442</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="1"/>
-        <v>0.73465314751842192</v>
+        <v>0.73501063481384199</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="2"/>
-        <v>2.7371428571428571E-2</v>
+        <v>0.20044000000000001</v>
       </c>
       <c r="I6">
-        <v>35000</v>
+        <v>50000</v>
       </c>
       <c r="J6">
-        <v>35958</v>
+        <v>60022</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4960,34 +4785,34 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C7">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>364.81046279999998</v>
+        <v>789.71625141288109</v>
       </c>
       <c r="E7">
-        <v>117.9004628</v>
+        <v>242.7966874</v>
       </c>
       <c r="F7">
-        <v>246.91</v>
+        <v>546.9195640128811</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="1"/>
-        <v>0.67681721106601989</v>
+        <v>0.69255199324363337</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="2"/>
-        <v>4.1939999999999998E-2</v>
+        <v>0.2898</v>
       </c>
       <c r="I7">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="J7">
-        <v>52097</v>
+        <v>96735</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -4995,69 +4820,69 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C8">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>648.96668739999996</v>
+        <v>1288.9825201238316</v>
       </c>
       <c r="E8">
-        <v>242.7966874</v>
+        <v>500</v>
       </c>
       <c r="F8">
-        <v>406.17</v>
+        <v>788.98252012383159</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="1"/>
-        <v>0.62587187892072993</v>
+        <v>0.61209714469055376</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="2"/>
-        <v>2.4799999999999999E-2</v>
+        <v>0.45656000000000002</v>
       </c>
       <c r="I8">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="J8">
-        <v>76860</v>
+        <v>145656</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="C9">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>1078.26</v>
+        <v>50.091791316810138</v>
       </c>
       <c r="E9">
-        <v>500</v>
+        <v>34.63261353</v>
       </c>
       <c r="F9">
-        <v>578.26</v>
+        <v>15.459177786810139</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="1"/>
-        <v>0.53628994862092627</v>
+        <v>0.30861698854083991</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="2"/>
-        <v>-2.3140000000000001E-2</v>
+        <v>-0.18878787878787878</v>
       </c>
       <c r="I9">
-        <v>100000</v>
+        <v>3300</v>
       </c>
       <c r="J9">
-        <v>97686</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -5065,104 +4890,104 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C10">
-        <v>2025</v>
+        <v>2035</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>22.65</v>
+        <v>106.75836904513994</v>
       </c>
       <c r="E10">
-        <v>13.5</v>
+        <v>88.845771859999999</v>
       </c>
       <c r="F10">
-        <v>9.15</v>
+        <v>17.912597185139937</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="1"/>
-        <v>0.40397350993377479</v>
+        <v>0.16778635104069525</v>
       </c>
       <c r="H10" s="4">
         <f t="shared" si="2"/>
-        <v>6.0606060606060606E-4</v>
+        <v>-0.49484848484848487</v>
       </c>
       <c r="I10">
         <v>3300</v>
       </c>
       <c r="J10">
-        <v>3302</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C11">
         <v>2030</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>45.752613529999998</v>
+        <v>134.39423010320985</v>
       </c>
       <c r="E11">
         <v>34.63261353</v>
       </c>
       <c r="F11">
-        <v>11.12</v>
+        <v>99.761616573209864</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="1"/>
-        <v>0.24304622494862749</v>
+        <v>0.74230580060317009</v>
       </c>
       <c r="H11" s="4">
         <f t="shared" si="2"/>
-        <v>1.090909090909091E-2</v>
+        <v>0.10155</v>
       </c>
       <c r="I11">
-        <v>3300</v>
+        <v>20000</v>
       </c>
       <c r="J11">
-        <v>3336</v>
+        <v>22031</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C12">
         <v>2035</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>103.69577185999999</v>
+        <v>293.78088876054733</v>
       </c>
       <c r="E12">
         <v>88.845771859999999</v>
       </c>
       <c r="F12">
-        <v>14.85</v>
+        <v>204.93511690054731</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="1"/>
-        <v>0.14320738187907053</v>
+        <v>0.69757810919955465</v>
       </c>
       <c r="H12" s="4">
         <f t="shared" si="2"/>
-        <v>-2.0909090909090908E-2</v>
+        <v>0.10357142857142858</v>
       </c>
       <c r="I12">
-        <v>3300</v>
+        <v>35000</v>
       </c>
       <c r="J12">
-        <v>3231</v>
+        <v>38625</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5170,34 +4995,34 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C13">
-        <v>2030</v>
+        <v>2040</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>102.04261353</v>
+        <v>550.54580175071692</v>
       </c>
       <c r="E13">
-        <v>34.63261353</v>
+        <v>227.9230579</v>
       </c>
       <c r="F13">
-        <v>67.41</v>
+        <v>322.62274385071692</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" si="1"/>
-        <v>0.66060636500829928</v>
+        <v>0.5860052748105381</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="2"/>
-        <v>8.3499999999999998E-3</v>
+        <v>0.2525</v>
       </c>
       <c r="I13">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="J13">
-        <v>20167</v>
+        <v>62625</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -5205,34 +5030,34 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C14">
-        <v>2035</v>
+        <v>2045</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>246.34577186000001</v>
+        <v>1097.0272738243348</v>
       </c>
       <c r="E14">
-        <v>88.845771859999999</v>
+        <v>584.70897609999997</v>
       </c>
       <c r="F14">
-        <v>157.5</v>
+        <v>512.31829772433468</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="1"/>
-        <v>0.63934525366852379</v>
+        <v>0.46700598056997034</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="2"/>
-        <v>4.3771428571428572E-2</v>
+        <v>0.30621333333333334</v>
       </c>
       <c r="I14">
-        <v>35000</v>
+        <v>75000</v>
       </c>
       <c r="J14">
-        <v>36532</v>
+        <v>97966</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -5240,385 +5065,67 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C15">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="D15">
         <f t="shared" si="0"/>
-        <v>470.9930579</v>
+        <v>2138.5423199159463</v>
       </c>
       <c r="E15">
-        <v>227.9230579</v>
+        <v>1500</v>
       </c>
       <c r="F15">
-        <v>243.07</v>
+        <v>638.54231991594634</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="1"/>
-        <v>0.51607979337055954</v>
+        <v>0.29858764728165105</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="2"/>
-        <v>0.11934</v>
+        <v>0.17591000000000001</v>
       </c>
       <c r="I15">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="J15">
-        <v>55967</v>
+        <v>117591</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16">
-        <v>2045</v>
-      </c>
-      <c r="D16">
-        <f t="shared" si="0"/>
-        <v>965.18897609999999</v>
-      </c>
-      <c r="E16">
-        <v>584.70897609999997</v>
-      </c>
-      <c r="F16">
-        <v>380.48</v>
-      </c>
-      <c r="G16" s="1">
-        <f t="shared" si="1"/>
-        <v>0.3942025959904662</v>
-      </c>
-      <c r="H16" s="4">
-        <f t="shared" si="2"/>
-        <v>0.16401333333333334</v>
-      </c>
-      <c r="I16">
-        <v>75000</v>
-      </c>
-      <c r="J16">
-        <v>87301</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17">
-        <v>2050</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="0"/>
-        <v>1974.19</v>
-      </c>
-      <c r="E17">
-        <v>1500</v>
-      </c>
-      <c r="F17">
-        <v>474.19</v>
-      </c>
-      <c r="G17" s="1">
-        <f t="shared" si="1"/>
-        <v>0.24019471276827462</v>
-      </c>
-      <c r="H17" s="4">
-        <f t="shared" si="2"/>
-        <v>0.10825</v>
-      </c>
-      <c r="I17">
-        <v>100000</v>
-      </c>
-      <c r="J17">
-        <v>110825</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18">
-        <v>2025</v>
-      </c>
-      <c r="D18">
-        <f t="shared" si="0"/>
-        <v>22.65</v>
-      </c>
-      <c r="E18">
-        <v>13.5</v>
-      </c>
-      <c r="F18">
-        <v>9.15</v>
-      </c>
-      <c r="G18" s="1">
-        <f t="shared" si="1"/>
-        <v>0.40397350993377479</v>
-      </c>
-      <c r="H18" s="4">
-        <f t="shared" si="2"/>
-        <v>-3.0303030303030303E-4</v>
-      </c>
-      <c r="I18">
-        <v>3300</v>
-      </c>
-      <c r="J18">
-        <v>3299</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19">
-        <v>2030</v>
-      </c>
-      <c r="D19">
-        <f t="shared" si="0"/>
-        <v>30.40962717</v>
-      </c>
-      <c r="E19">
-        <v>20.149627169999999</v>
-      </c>
-      <c r="F19">
-        <v>10.26</v>
-      </c>
-      <c r="G19" s="1">
-        <f t="shared" si="1"/>
-        <v>0.33739315324858032</v>
-      </c>
-      <c r="H19" s="4">
-        <f t="shared" si="2"/>
-        <v>-7.575757575757576E-3</v>
-      </c>
-      <c r="I19">
-        <v>3300</v>
-      </c>
-      <c r="J19">
-        <v>3275</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20">
-        <v>2035</v>
-      </c>
-      <c r="D20">
-        <f t="shared" si="0"/>
-        <v>44.244627790000003</v>
-      </c>
-      <c r="E20">
-        <v>30.074627790000001</v>
-      </c>
-      <c r="F20">
-        <v>14.17</v>
-      </c>
-      <c r="G20" s="1">
-        <f t="shared" si="1"/>
-        <v>0.32026487073765486</v>
-      </c>
-      <c r="H20" s="4">
-        <f t="shared" si="2"/>
-        <v>0.17303030303030303</v>
-      </c>
-      <c r="I20">
-        <v>3300</v>
-      </c>
-      <c r="J20">
-        <v>3871</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21">
-        <v>2030</v>
-      </c>
-      <c r="D21">
-        <f t="shared" si="0"/>
-        <v>82.319627170000004</v>
-      </c>
-      <c r="E21">
-        <v>20.149627169999999</v>
-      </c>
-      <c r="F21">
-        <v>62.17</v>
-      </c>
-      <c r="G21" s="1">
-        <f t="shared" si="1"/>
-        <v>0.75522693842637822</v>
-      </c>
-      <c r="H21" s="4">
-        <f t="shared" si="2"/>
-        <v>-2.15E-3</v>
-      </c>
-      <c r="I21">
-        <v>20000</v>
-      </c>
-      <c r="J21">
-        <v>19957</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22">
-        <v>2035</v>
-      </c>
-      <c r="D22">
-        <f t="shared" si="0"/>
-        <v>180.40462779000001</v>
-      </c>
-      <c r="E22">
-        <v>30.074627790000001</v>
-      </c>
-      <c r="F22">
-        <v>150.33000000000001</v>
-      </c>
-      <c r="G22" s="1">
-        <f t="shared" si="1"/>
-        <v>0.83329347944993759</v>
-      </c>
-      <c r="H22" s="4">
-        <f t="shared" si="2"/>
-        <v>7.8085714285714286E-2</v>
-      </c>
-      <c r="I22">
-        <v>35000</v>
-      </c>
-      <c r="J22">
-        <v>37733</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23">
-        <v>2040</v>
-      </c>
-      <c r="D23">
-        <f t="shared" si="0"/>
-        <v>275.22833609000003</v>
-      </c>
-      <c r="E23">
-        <v>44.888336090000003</v>
-      </c>
-      <c r="F23">
-        <v>230.34</v>
-      </c>
-      <c r="G23" s="1">
-        <f t="shared" si="1"/>
-        <v>0.83690510676443775</v>
-      </c>
-      <c r="H23" s="4">
-        <f t="shared" si="2"/>
-        <v>6.4999999999999997E-3</v>
-      </c>
-      <c r="I23">
-        <v>50000</v>
-      </c>
-      <c r="J23">
-        <v>50325</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24">
-        <v>2045</v>
-      </c>
-      <c r="D24">
-        <f t="shared" si="0"/>
-        <v>461.17875827</v>
-      </c>
-      <c r="E24">
-        <v>66.998758269999996</v>
-      </c>
-      <c r="F24">
-        <v>394.18</v>
-      </c>
-      <c r="G24" s="1">
-        <f t="shared" si="1"/>
-        <v>0.85472280093443687</v>
-      </c>
-      <c r="H24" s="4">
-        <f t="shared" si="2"/>
-        <v>5.0680000000000003E-2</v>
-      </c>
-      <c r="I24">
-        <v>75000</v>
-      </c>
-      <c r="J24">
-        <v>78801</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25">
-        <v>2050</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="0"/>
-        <v>691.29</v>
-      </c>
-      <c r="E25">
-        <v>100</v>
-      </c>
-      <c r="F25">
-        <v>591.29</v>
-      </c>
-      <c r="G25" s="1">
-        <f t="shared" si="1"/>
-        <v>0.85534290963271564</v>
-      </c>
-      <c r="H25" s="4">
-        <f t="shared" si="2"/>
-        <v>0.10559</v>
-      </c>
-      <c r="I25">
-        <v>100000</v>
-      </c>
-      <c r="J25">
-        <v>110559</v>
-      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="7:8">
+      <c r="G17" s="1"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="7:8">
+      <c r="G18" s="1"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="7:8">
+      <c r="G19" s="1"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="7:8">
+      <c r="G20" s="1"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="7:8">
+      <c r="G21" s="1"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="7:8">
+      <c r="G22" s="1"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="7:8">
+      <c r="G23" s="1"/>
+      <c r="H23" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9996,7 +9503,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="B32" s="2">
-        <f t="shared" ref="B30:B34" si="10">B23*K5</f>
+        <f t="shared" ref="B32:B34" si="10">B23*K5</f>
         <v>0</v>
       </c>
       <c r="C32" s="2">
